--- a/const/Binned_Summary.xlsx
+++ b/const/Binned_Summary.xlsx
@@ -351,28 +351,28 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D45"/>
+  <dimension ref="A1:D307"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Common Bin</t>
+          <t>Registered Bin</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Sum_Avg_Registered</t>
+          <t>Weighted Bin</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>Sum_Avg_Weighted</t>
+          <t>Count_Registered_Practices</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>Num_Practices</t>
+          <t>Count_Weighted_Practices</t>
         </is>
       </c>
     </row>
@@ -382,11 +382,13 @@
           <t>0-9</t>
         </is>
       </c>
-      <c r="B2">
-        <v>11.71835093405003</v>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>0-9</t>
+        </is>
       </c>
       <c r="C2">
-        <v>11.99964619039583</v>
+        <v>3</v>
       </c>
       <c r="D2">
         <v>3</v>
@@ -398,11 +400,13 @@
           <t>10-19</t>
         </is>
       </c>
-      <c r="B3">
-        <v>24.23387781365282</v>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>10-19</t>
+        </is>
       </c>
       <c r="C3">
-        <v>26.11541650320992</v>
+        <v>2</v>
       </c>
       <c r="D3">
         <v>2</v>
@@ -411,14 +415,16 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t>30-39</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
           <t>20-29</t>
         </is>
       </c>
-      <c r="B4">
-        <v>33.60037185929648</v>
-      </c>
       <c r="C4">
-        <v>29.63121808200432</v>
+        <v>1</v>
       </c>
       <c r="D4">
         <v>1</v>
@@ -430,30 +436,34 @@
           <t>30-39</t>
         </is>
       </c>
-      <c r="B5">
-        <v>73.24202519487233</v>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>30-39</t>
+        </is>
       </c>
       <c r="C5">
-        <v>77.47592685002411</v>
+        <v>1</v>
       </c>
       <c r="D5">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>30-39</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
           <t>40-49</t>
         </is>
       </c>
-      <c r="B6">
-        <v>136.31240247137</v>
-      </c>
       <c r="C6">
-        <v>138.0959925865372</v>
+        <v>1</v>
       </c>
       <c r="D6">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7">
@@ -462,11 +472,13 @@
           <t>60-69</t>
         </is>
       </c>
-      <c r="B7">
-        <v>69.72021294135727</v>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>130-139</t>
+        </is>
       </c>
       <c r="C7">
-        <v>130.4577629832746</v>
+        <v>1</v>
       </c>
       <c r="D7">
         <v>1</v>
@@ -478,601 +490,5363 @@
           <t>80-89</t>
         </is>
       </c>
-      <c r="B8">
-        <v>455.3760958560491</v>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>110-119</t>
+        </is>
       </c>
       <c r="C8">
-        <v>614.9805971768033</v>
+        <v>1</v>
       </c>
       <c r="D8">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>90-99</t>
-        </is>
-      </c>
-      <c r="B9">
-        <v>1057.423598281621</v>
+          <t>80-89</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>140-149</t>
+        </is>
       </c>
       <c r="C9">
-        <v>1433.635694071274</v>
+        <v>1</v>
       </c>
       <c r="D9">
-        <v>11</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
+          <t>90-99</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
           <t>100-109</t>
         </is>
       </c>
-      <c r="B10">
-        <v>4093.455726608603</v>
-      </c>
       <c r="C10">
-        <v>4784.184153950337</v>
+        <v>1</v>
       </c>
       <c r="D10">
-        <v>38</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>110-119</t>
-        </is>
-      </c>
-      <c r="B11">
-        <v>20284.71161854044</v>
+          <t>90-99</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>120-129</t>
+        </is>
       </c>
       <c r="C11">
-        <v>23301.14385094526</v>
+        <v>4</v>
       </c>
       <c r="D11">
-        <v>174</v>
+        <v>4</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>120-129</t>
-        </is>
-      </c>
-      <c r="B12">
-        <v>53038.58100633866</v>
+          <t>90-99</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>130-139</t>
+        </is>
       </c>
       <c r="C12">
-        <v>57466.38092354535</v>
+        <v>3</v>
       </c>
       <c r="D12">
-        <v>416</v>
+        <v>3</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>130-139</t>
-        </is>
-      </c>
-      <c r="B13">
-        <v>135771.4413134622</v>
+          <t>90-99</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>140-149</t>
+        </is>
       </c>
       <c r="C13">
-        <v>139782.7732094483</v>
+        <v>2</v>
       </c>
       <c r="D13">
-        <v>974</v>
+        <v>2</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>140-149</t>
-        </is>
-      </c>
-      <c r="B14">
-        <v>190489.7269140901</v>
+          <t>100-109</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>80-89</t>
+        </is>
       </c>
       <c r="C14">
-        <v>189130.6945245289</v>
+        <v>1</v>
       </c>
       <c r="D14">
-        <v>1259</v>
+        <v>1</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>150-159</t>
-        </is>
-      </c>
-      <c r="B15">
-        <v>177946.4569099923</v>
+          <t>100-109</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>100-109</t>
+        </is>
       </c>
       <c r="C15">
-        <v>174298.7093482858</v>
+        <v>2</v>
       </c>
       <c r="D15">
-        <v>1098</v>
+        <v>2</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>160-169</t>
-        </is>
-      </c>
-      <c r="B16">
-        <v>124314.5985016489</v>
+          <t>100-109</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>110-119</t>
+        </is>
       </c>
       <c r="C16">
-        <v>120673.2037563888</v>
+        <v>3</v>
       </c>
       <c r="D16">
-        <v>718</v>
+        <v>3</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>170-179</t>
-        </is>
-      </c>
-      <c r="B17">
-        <v>70719.43241130059</v>
+          <t>100-109</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>120-129</t>
+        </is>
       </c>
       <c r="C17">
-        <v>68627.54509376539</v>
+        <v>12</v>
       </c>
       <c r="D17">
-        <v>386</v>
+        <v>12</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>180-189</t>
-        </is>
-      </c>
-      <c r="B18">
-        <v>42093.52665270527</v>
+          <t>100-109</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>130-139</t>
+        </is>
       </c>
       <c r="C18">
-        <v>40758.03418531609</v>
+        <v>10</v>
       </c>
       <c r="D18">
-        <v>216</v>
+        <v>10</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>190-199</t>
-        </is>
-      </c>
-      <c r="B19">
-        <v>33055.81779949558</v>
+          <t>100-109</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>140-149</t>
+        </is>
       </c>
       <c r="C19">
-        <v>31873.77247313512</v>
+        <v>3</v>
       </c>
       <c r="D19">
-        <v>161</v>
+        <v>3</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>200-209</t>
-        </is>
-      </c>
-      <c r="B20">
-        <v>24550.05737943901</v>
+          <t>100-109</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>150-159</t>
+        </is>
       </c>
       <c r="C20">
-        <v>23198.06802875258</v>
+        <v>1</v>
       </c>
       <c r="D20">
-        <v>112</v>
+        <v>1</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>210-219</t>
-        </is>
-      </c>
-      <c r="B21">
-        <v>24073.82123903514</v>
+          <t>110-119</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>100-109</t>
+        </is>
       </c>
       <c r="C21">
-        <v>22658.93437031225</v>
+        <v>2</v>
       </c>
       <c r="D21">
-        <v>104</v>
+        <v>2</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>220-229</t>
-        </is>
-      </c>
-      <c r="B22">
-        <v>21137.98879786815</v>
+          <t>110-119</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>110-119</t>
+        </is>
       </c>
       <c r="C22">
-        <v>19740.44132932785</v>
+        <v>2</v>
       </c>
       <c r="D22">
-        <v>86</v>
+        <v>2</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>230-239</t>
-        </is>
-      </c>
-      <c r="B23">
-        <v>14765.86314886116</v>
+          <t>110-119</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>120-129</t>
+        </is>
       </c>
       <c r="C23">
-        <v>13509.84213793696</v>
+        <v>39</v>
       </c>
       <c r="D23">
-        <v>57</v>
+        <v>39</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>240-249</t>
-        </is>
-      </c>
-      <c r="B24">
-        <v>14385.77255166104</v>
+          <t>110-119</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>130-139</t>
+        </is>
       </c>
       <c r="C24">
-        <v>13101.21705713856</v>
+        <v>71</v>
       </c>
       <c r="D24">
-        <v>53</v>
+        <v>71</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>250-259</t>
-        </is>
-      </c>
-      <c r="B25">
-        <v>10488.27556402529</v>
+          <t>110-119</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>140-149</t>
+        </is>
       </c>
       <c r="C25">
-        <v>9554.961078208278</v>
+        <v>29</v>
       </c>
       <c r="D25">
-        <v>37</v>
+        <v>29</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>260-269</t>
-        </is>
-      </c>
-      <c r="B26">
-        <v>10057.18363429884</v>
+          <t>110-119</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>160-169</t>
+        </is>
       </c>
       <c r="C26">
-        <v>9067.487755586058</v>
+        <v>1</v>
       </c>
       <c r="D26">
-        <v>34</v>
+        <v>1</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>270-279</t>
-        </is>
-      </c>
-      <c r="B27">
-        <v>10973.65097897071</v>
+          <t>120-129</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>100-109</t>
+        </is>
       </c>
       <c r="C27">
-        <v>9740.833214639644</v>
+        <v>1</v>
       </c>
       <c r="D27">
-        <v>35</v>
+        <v>1</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>280-289</t>
-        </is>
-      </c>
-      <c r="B28">
-        <v>13947.83363922819</v>
+          <t>120-129</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>110-119</t>
+        </is>
       </c>
       <c r="C28">
-        <v>12570.10377948128</v>
+        <v>2</v>
       </c>
       <c r="D28">
-        <v>44</v>
+        <v>2</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>290-299</t>
-        </is>
-      </c>
-      <c r="B29">
-        <v>13104.47335090978</v>
+          <t>120-129</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>120-129</t>
+        </is>
       </c>
       <c r="C29">
-        <v>11790.84862592937</v>
+        <v>48</v>
       </c>
       <c r="D29">
-        <v>39</v>
+        <v>48</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>300-309</t>
-        </is>
-      </c>
-      <c r="B30">
-        <v>11420.78108119363</v>
+          <t>120-129</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>130-139</t>
+        </is>
       </c>
       <c r="C30">
-        <v>10081.3180706595</v>
+        <v>136</v>
       </c>
       <c r="D30">
-        <v>33</v>
+        <v>136</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>310-319</t>
-        </is>
-      </c>
-      <c r="B31">
-        <v>12016.4622604408</v>
+          <t>120-129</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>140-149</t>
+        </is>
       </c>
       <c r="C31">
-        <v>10758.63279306994</v>
+        <v>105</v>
       </c>
       <c r="D31">
-        <v>34</v>
+        <v>105</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>320-329</t>
-        </is>
-      </c>
-      <c r="B32">
-        <v>5371.844104576002</v>
+          <t>120-129</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>150-159</t>
+        </is>
       </c>
       <c r="C32">
-        <v>4932.579760603728</v>
+        <v>33</v>
       </c>
       <c r="D32">
-        <v>15</v>
+        <v>33</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>330-339</t>
-        </is>
-      </c>
-      <c r="B33">
-        <v>5362.355979165924</v>
+          <t>120-129</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>160-169</t>
+        </is>
       </c>
       <c r="C33">
-        <v>4747.020651574683</v>
+        <v>10</v>
       </c>
       <c r="D33">
-        <v>14</v>
+        <v>10</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>340-349</t>
-        </is>
-      </c>
-      <c r="B34">
-        <v>4771.960637152401</v>
+          <t>120-129</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>170-179</t>
+        </is>
       </c>
       <c r="C34">
-        <v>4147.727022102634</v>
+        <v>2</v>
       </c>
       <c r="D34">
-        <v>12</v>
+        <v>2</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>350-359</t>
-        </is>
-      </c>
-      <c r="B35">
-        <v>4278.978593425261</v>
+          <t>130-139</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>100-109</t>
+        </is>
       </c>
       <c r="C35">
-        <v>3555.65324106677</v>
+        <v>1</v>
       </c>
       <c r="D35">
-        <v>10</v>
+        <v>1</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>360-369</t>
-        </is>
-      </c>
-      <c r="B36">
-        <v>3735.733086190237</v>
+          <t>130-139</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>110-119</t>
+        </is>
       </c>
       <c r="C36">
-        <v>3510.225146161374</v>
+        <v>1</v>
       </c>
       <c r="D36">
-        <v>9</v>
+        <v>1</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>370-379</t>
-        </is>
-      </c>
-      <c r="B37">
-        <v>2140.397701353575</v>
+          <t>130-139</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>120-129</t>
+        </is>
       </c>
       <c r="C37">
-        <v>1917.550157456931</v>
+        <v>26</v>
       </c>
       <c r="D37">
-        <v>5</v>
+        <v>26</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>380-389</t>
-        </is>
-      </c>
-      <c r="B38">
-        <v>1894.583632681394</v>
+          <t>130-139</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>130-139</t>
+        </is>
       </c>
       <c r="C38">
-        <v>1531.558279736946</v>
+        <v>193</v>
       </c>
       <c r="D38">
-        <v>4</v>
+        <v>193</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>390-399</t>
-        </is>
-      </c>
-      <c r="B39">
-        <v>2077.020365395362</v>
+          <t>130-139</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>140-149</t>
+        </is>
       </c>
       <c r="C39">
-        <v>1997.186804147024</v>
+        <v>287</v>
       </c>
       <c r="D39">
-        <v>5</v>
+        <v>287</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>430-439</t>
-        </is>
-      </c>
-      <c r="B40">
-        <v>624.391641363133</v>
+          <t>130-139</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>150-159</t>
+        </is>
       </c>
       <c r="C40">
-        <v>439.6732835719543</v>
+        <v>145</v>
       </c>
       <c r="D40">
-        <v>1</v>
+        <v>145</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>440-449</t>
-        </is>
-      </c>
-      <c r="B41">
-        <v>932.4975005540782</v>
+          <t>130-139</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>160-169</t>
+        </is>
       </c>
       <c r="C41">
-        <v>886.6537317301867</v>
+        <v>42</v>
       </c>
       <c r="D41">
-        <v>2</v>
+        <v>42</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>460-469</t>
-        </is>
-      </c>
-      <c r="B42">
-        <v>557.0570006071646</v>
+          <t>130-139</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>170-179</t>
+        </is>
       </c>
       <c r="C42">
-        <v>461.8184706356103</v>
+        <v>2</v>
       </c>
       <c r="D42">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>470-479</t>
-        </is>
-      </c>
-      <c r="B43">
-        <v>472.7333023912824</v>
+          <t>130-139</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>180-189</t>
+        </is>
       </c>
       <c r="C43">
-        <v>517.4749681911359</v>
+        <v>2</v>
       </c>
       <c r="D43">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
+          <t>130-139</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>200-209</t>
+        </is>
+      </c>
+      <c r="C44">
+        <v>3</v>
+      </c>
+      <c r="D44">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>140-149</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>110-119</t>
+        </is>
+      </c>
+      <c r="C45">
+        <v>2</v>
+      </c>
+      <c r="D45">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>140-149</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>120-129</t>
+        </is>
+      </c>
+      <c r="C46">
+        <v>12</v>
+      </c>
+      <c r="D46">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>140-149</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>130-139</t>
+        </is>
+      </c>
+      <c r="C47">
+        <v>128</v>
+      </c>
+      <c r="D47">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>140-149</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>140-149</t>
+        </is>
+      </c>
+      <c r="C48">
+        <v>295</v>
+      </c>
+      <c r="D48">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>140-149</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>150-159</t>
+        </is>
+      </c>
+      <c r="C49">
+        <v>308</v>
+      </c>
+      <c r="D49">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>140-149</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>160-169</t>
+        </is>
+      </c>
+      <c r="C50">
+        <v>96</v>
+      </c>
+      <c r="D50">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>140-149</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>170-179</t>
+        </is>
+      </c>
+      <c r="C51">
+        <v>25</v>
+      </c>
+      <c r="D51">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>140-149</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>180-189</t>
+        </is>
+      </c>
+      <c r="C52">
+        <v>4</v>
+      </c>
+      <c r="D52">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>140-149</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>190-199</t>
+        </is>
+      </c>
+      <c r="C53">
+        <v>1</v>
+      </c>
+      <c r="D53">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>150-159</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>120-129</t>
+        </is>
+      </c>
+      <c r="C54">
+        <v>7</v>
+      </c>
+      <c r="D54">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>150-159</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>130-139</t>
+        </is>
+      </c>
+      <c r="C55">
+        <v>71</v>
+      </c>
+      <c r="D55">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>150-159</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>140-149</t>
+        </is>
+      </c>
+      <c r="C56">
+        <v>254</v>
+      </c>
+      <c r="D56">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>150-159</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>150-159</t>
+        </is>
+      </c>
+      <c r="C57">
+        <v>299</v>
+      </c>
+      <c r="D57">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>150-159</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>160-169</t>
+        </is>
+      </c>
+      <c r="C58">
+        <v>201</v>
+      </c>
+      <c r="D58">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>150-159</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>170-179</t>
+        </is>
+      </c>
+      <c r="C59">
+        <v>70</v>
+      </c>
+      <c r="D59">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>150-159</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>180-189</t>
+        </is>
+      </c>
+      <c r="C60">
+        <v>16</v>
+      </c>
+      <c r="D60">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>150-159</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>190-199</t>
+        </is>
+      </c>
+      <c r="C61">
+        <v>1</v>
+      </c>
+      <c r="D61">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>150-159</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>220-229</t>
+        </is>
+      </c>
+      <c r="C62">
+        <v>1</v>
+      </c>
+      <c r="D62">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>160-169</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>130-139</t>
+        </is>
+      </c>
+      <c r="C63">
+        <v>23</v>
+      </c>
+      <c r="D63">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>160-169</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>140-149</t>
+        </is>
+      </c>
+      <c r="C64">
+        <v>141</v>
+      </c>
+      <c r="D64">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>160-169</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>150-159</t>
+        </is>
+      </c>
+      <c r="C65">
+        <v>256</v>
+      </c>
+      <c r="D65">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>160-169</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>160-169</t>
+        </is>
+      </c>
+      <c r="C66">
+        <v>201</v>
+      </c>
+      <c r="D66">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>160-169</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>170-179</t>
+        </is>
+      </c>
+      <c r="C67">
+        <v>112</v>
+      </c>
+      <c r="D67">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>160-169</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>180-189</t>
+        </is>
+      </c>
+      <c r="C68">
+        <v>33</v>
+      </c>
+      <c r="D68">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>160-169</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>190-199</t>
+        </is>
+      </c>
+      <c r="C69">
+        <v>8</v>
+      </c>
+      <c r="D69">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>160-169</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>200-209</t>
+        </is>
+      </c>
+      <c r="C70">
+        <v>2</v>
+      </c>
+      <c r="D70">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>160-169</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>220-229</t>
+        </is>
+      </c>
+      <c r="C71">
+        <v>2</v>
+      </c>
+      <c r="D71">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>170-179</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>130-139</t>
+        </is>
+      </c>
+      <c r="C72">
+        <v>9</v>
+      </c>
+      <c r="D72">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>170-179</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>140-149</t>
+        </is>
+      </c>
+      <c r="C73">
+        <v>42</v>
+      </c>
+      <c r="D73">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>170-179</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>150-159</t>
+        </is>
+      </c>
+      <c r="C74">
+        <v>129</v>
+      </c>
+      <c r="D74">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>170-179</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>160-169</t>
+        </is>
+      </c>
+      <c r="C75">
+        <v>164</v>
+      </c>
+      <c r="D75">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>170-179</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>170-179</t>
+        </is>
+      </c>
+      <c r="C76">
+        <v>121</v>
+      </c>
+      <c r="D76">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>170-179</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>180-189</t>
+        </is>
+      </c>
+      <c r="C77">
+        <v>60</v>
+      </c>
+      <c r="D77">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>170-179</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>190-199</t>
+        </is>
+      </c>
+      <c r="C78">
+        <v>17</v>
+      </c>
+      <c r="D78">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>170-179</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>200-209</t>
+        </is>
+      </c>
+      <c r="C79">
+        <v>2</v>
+      </c>
+      <c r="D79">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>170-179</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>220-229</t>
+        </is>
+      </c>
+      <c r="C80">
+        <v>1</v>
+      </c>
+      <c r="D80">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>180-189</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>130-139</t>
+        </is>
+      </c>
+      <c r="C81">
+        <v>1</v>
+      </c>
+      <c r="D81">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>180-189</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>140-149</t>
+        </is>
+      </c>
+      <c r="C82">
+        <v>18</v>
+      </c>
+      <c r="D82">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>180-189</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>150-159</t>
+        </is>
+      </c>
+      <c r="C83">
+        <v>41</v>
+      </c>
+      <c r="D83">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>180-189</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>160-169</t>
+        </is>
+      </c>
+      <c r="C84">
+        <v>89</v>
+      </c>
+      <c r="D84">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>180-189</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>170-179</t>
+        </is>
+      </c>
+      <c r="C85">
+        <v>78</v>
+      </c>
+      <c r="D85">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>180-189</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>180-189</t>
+        </is>
+      </c>
+      <c r="C86">
+        <v>49</v>
+      </c>
+      <c r="D86">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>180-189</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>190-199</t>
+        </is>
+      </c>
+      <c r="C87">
+        <v>31</v>
+      </c>
+      <c r="D87">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>180-189</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>200-209</t>
+        </is>
+      </c>
+      <c r="C88">
+        <v>10</v>
+      </c>
+      <c r="D88">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>180-189</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>210-219</t>
+        </is>
+      </c>
+      <c r="C89">
+        <v>3</v>
+      </c>
+      <c r="D89">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>180-189</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>220-229</t>
+        </is>
+      </c>
+      <c r="C90">
+        <v>2</v>
+      </c>
+      <c r="D90">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>180-189</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>240-249</t>
+        </is>
+      </c>
+      <c r="C91">
+        <v>1</v>
+      </c>
+      <c r="D91">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>180-189</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>250-259</t>
+        </is>
+      </c>
+      <c r="C92">
+        <v>1</v>
+      </c>
+      <c r="D92">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>190-199</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>140-149</t>
+        </is>
+      </c>
+      <c r="C93">
+        <v>2</v>
+      </c>
+      <c r="D93">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>190-199</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>150-159</t>
+        </is>
+      </c>
+      <c r="C94">
+        <v>16</v>
+      </c>
+      <c r="D94">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>190-199</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>160-169</t>
+        </is>
+      </c>
+      <c r="C95">
+        <v>39</v>
+      </c>
+      <c r="D95">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>190-199</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>170-179</t>
+        </is>
+      </c>
+      <c r="C96">
+        <v>47</v>
+      </c>
+      <c r="D96">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>190-199</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>180-189</t>
+        </is>
+      </c>
+      <c r="C97">
+        <v>51</v>
+      </c>
+      <c r="D97">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>190-199</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>190-199</t>
+        </is>
+      </c>
+      <c r="C98">
+        <v>40</v>
+      </c>
+      <c r="D98">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>190-199</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>200-209</t>
+        </is>
+      </c>
+      <c r="C99">
+        <v>19</v>
+      </c>
+      <c r="D99">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>190-199</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>210-219</t>
+        </is>
+      </c>
+      <c r="C100">
+        <v>9</v>
+      </c>
+      <c r="D100">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>190-199</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>220-229</t>
+        </is>
+      </c>
+      <c r="C101">
+        <v>2</v>
+      </c>
+      <c r="D101">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>190-199</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>230-239</t>
+        </is>
+      </c>
+      <c r="C102">
+        <v>2</v>
+      </c>
+      <c r="D102">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>200-209</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>150-159</t>
+        </is>
+      </c>
+      <c r="C103">
+        <v>5</v>
+      </c>
+      <c r="D103">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>200-209</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>160-169</t>
+        </is>
+      </c>
+      <c r="C104">
+        <v>17</v>
+      </c>
+      <c r="D104">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>200-209</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>170-179</t>
+        </is>
+      </c>
+      <c r="C105">
+        <v>27</v>
+      </c>
+      <c r="D105">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>200-209</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>180-189</t>
+        </is>
+      </c>
+      <c r="C106">
+        <v>25</v>
+      </c>
+      <c r="D106">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>200-209</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>190-199</t>
+        </is>
+      </c>
+      <c r="C107">
+        <v>36</v>
+      </c>
+      <c r="D107">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>200-209</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>200-209</t>
+        </is>
+      </c>
+      <c r="C108">
+        <v>23</v>
+      </c>
+      <c r="D108">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>200-209</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>210-219</t>
+        </is>
+      </c>
+      <c r="C109">
+        <v>11</v>
+      </c>
+      <c r="D109">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>200-209</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>220-229</t>
+        </is>
+      </c>
+      <c r="C110">
+        <v>3</v>
+      </c>
+      <c r="D110">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>200-209</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>230-239</t>
+        </is>
+      </c>
+      <c r="C111">
+        <v>2</v>
+      </c>
+      <c r="D111">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>210-219</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>150-159</t>
+        </is>
+      </c>
+      <c r="C112">
+        <v>2</v>
+      </c>
+      <c r="D112">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>210-219</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>160-169</t>
+        </is>
+      </c>
+      <c r="C113">
+        <v>8</v>
+      </c>
+      <c r="D113">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>210-219</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>170-179</t>
+        </is>
+      </c>
+      <c r="C114">
+        <v>8</v>
+      </c>
+      <c r="D114">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>210-219</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>180-189</t>
+        </is>
+      </c>
+      <c r="C115">
+        <v>14</v>
+      </c>
+      <c r="D115">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>210-219</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>190-199</t>
+        </is>
+      </c>
+      <c r="C116">
+        <v>24</v>
+      </c>
+      <c r="D116">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>210-219</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>200-209</t>
+        </is>
+      </c>
+      <c r="C117">
+        <v>27</v>
+      </c>
+      <c r="D117">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>210-219</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>210-219</t>
+        </is>
+      </c>
+      <c r="C118">
+        <v>17</v>
+      </c>
+      <c r="D118">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>210-219</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>220-229</t>
+        </is>
+      </c>
+      <c r="C119">
+        <v>7</v>
+      </c>
+      <c r="D119">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>210-219</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>230-239</t>
+        </is>
+      </c>
+      <c r="C120">
+        <v>7</v>
+      </c>
+      <c r="D120">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>210-219</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>240-249</t>
+        </is>
+      </c>
+      <c r="C121">
+        <v>1</v>
+      </c>
+      <c r="D121">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>220-229</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>170-179</t>
+        </is>
+      </c>
+      <c r="C122">
+        <v>3</v>
+      </c>
+      <c r="D122">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>220-229</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>180-189</t>
+        </is>
+      </c>
+      <c r="C123">
+        <v>9</v>
+      </c>
+      <c r="D123">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>220-229</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>190-199</t>
+        </is>
+      </c>
+      <c r="C124">
+        <v>11</v>
+      </c>
+      <c r="D124">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>220-229</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>200-209</t>
+        </is>
+      </c>
+      <c r="C125">
+        <v>16</v>
+      </c>
+      <c r="D125">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>220-229</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>210-219</t>
+        </is>
+      </c>
+      <c r="C126">
+        <v>15</v>
+      </c>
+      <c r="D126">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>220-229</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>220-229</t>
+        </is>
+      </c>
+      <c r="C127">
+        <v>12</v>
+      </c>
+      <c r="D127">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>220-229</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>230-239</t>
+        </is>
+      </c>
+      <c r="C128">
+        <v>7</v>
+      </c>
+      <c r="D128">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>220-229</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>240-249</t>
+        </is>
+      </c>
+      <c r="C129">
+        <v>3</v>
+      </c>
+      <c r="D129">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>220-229</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>250-259</t>
+        </is>
+      </c>
+      <c r="C130">
+        <v>1</v>
+      </c>
+      <c r="D130">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>220-229</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>330-339</t>
+        </is>
+      </c>
+      <c r="C131">
+        <v>1</v>
+      </c>
+      <c r="D131">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>230-239</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>160-169</t>
+        </is>
+      </c>
+      <c r="C132">
+        <v>2</v>
+      </c>
+      <c r="D132">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>230-239</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>170-179</t>
+        </is>
+      </c>
+      <c r="C133">
+        <v>1</v>
+      </c>
+      <c r="D133">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>230-239</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>180-189</t>
+        </is>
+      </c>
+      <c r="C134">
+        <v>4</v>
+      </c>
+      <c r="D134">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>230-239</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>190-199</t>
+        </is>
+      </c>
+      <c r="C135">
+        <v>5</v>
+      </c>
+      <c r="D135">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>230-239</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>200-209</t>
+        </is>
+      </c>
+      <c r="C136">
+        <v>10</v>
+      </c>
+      <c r="D136">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>230-239</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>210-219</t>
+        </is>
+      </c>
+      <c r="C137">
+        <v>20</v>
+      </c>
+      <c r="D137">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>230-239</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>220-229</t>
+        </is>
+      </c>
+      <c r="C138">
+        <v>8</v>
+      </c>
+      <c r="D138">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>230-239</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>230-239</t>
+        </is>
+      </c>
+      <c r="C139">
+        <v>8</v>
+      </c>
+      <c r="D139">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>230-239</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>240-249</t>
+        </is>
+      </c>
+      <c r="C140">
+        <v>3</v>
+      </c>
+      <c r="D140">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>230-239</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>250-259</t>
+        </is>
+      </c>
+      <c r="C141">
+        <v>2</v>
+      </c>
+      <c r="D141">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>240-249</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>180-189</t>
+        </is>
+      </c>
+      <c r="C142">
+        <v>1</v>
+      </c>
+      <c r="D142">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>240-249</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>190-199</t>
+        </is>
+      </c>
+      <c r="C143">
+        <v>2</v>
+      </c>
+      <c r="D143">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>240-249</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>200-209</t>
+        </is>
+      </c>
+      <c r="C144">
+        <v>6</v>
+      </c>
+      <c r="D144">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>240-249</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>210-219</t>
+        </is>
+      </c>
+      <c r="C145">
+        <v>16</v>
+      </c>
+      <c r="D145">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>240-249</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>220-229</t>
+        </is>
+      </c>
+      <c r="C146">
+        <v>15</v>
+      </c>
+      <c r="D146">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>240-249</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>230-239</t>
+        </is>
+      </c>
+      <c r="C147">
+        <v>10</v>
+      </c>
+      <c r="D147">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>240-249</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>240-249</t>
+        </is>
+      </c>
+      <c r="C148">
+        <v>2</v>
+      </c>
+      <c r="D148">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>240-249</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>250-259</t>
+        </is>
+      </c>
+      <c r="C149">
+        <v>3</v>
+      </c>
+      <c r="D149">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>240-249</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>260-269</t>
+        </is>
+      </c>
+      <c r="C150">
+        <v>2</v>
+      </c>
+      <c r="D150">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>240-249</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>280-289</t>
+        </is>
+      </c>
+      <c r="C151">
+        <v>1</v>
+      </c>
+      <c r="D151">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>250-259</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>190-199</t>
+        </is>
+      </c>
+      <c r="C152">
+        <v>1</v>
+      </c>
+      <c r="D152">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>250-259</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>200-209</t>
+        </is>
+      </c>
+      <c r="C153">
+        <v>5</v>
+      </c>
+      <c r="D153">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>250-259</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>210-219</t>
+        </is>
+      </c>
+      <c r="C154">
+        <v>8</v>
+      </c>
+      <c r="D154">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>250-259</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>220-229</t>
+        </is>
+      </c>
+      <c r="C155">
+        <v>13</v>
+      </c>
+      <c r="D155">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>250-259</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>230-239</t>
+        </is>
+      </c>
+      <c r="C156">
+        <v>6</v>
+      </c>
+      <c r="D156">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>250-259</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>240-249</t>
+        </is>
+      </c>
+      <c r="C157">
+        <v>8</v>
+      </c>
+      <c r="D157">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>250-259</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>250-259</t>
+        </is>
+      </c>
+      <c r="C158">
+        <v>1</v>
+      </c>
+      <c r="D158">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>250-259</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>260-269</t>
+        </is>
+      </c>
+      <c r="C159">
+        <v>3</v>
+      </c>
+      <c r="D159">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>250-259</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>270-279</t>
+        </is>
+      </c>
+      <c r="C160">
+        <v>1</v>
+      </c>
+      <c r="D160">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>250-259</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>280-289</t>
+        </is>
+      </c>
+      <c r="C161">
+        <v>2</v>
+      </c>
+      <c r="D161">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>260-269</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>170-179</t>
+        </is>
+      </c>
+      <c r="C162">
+        <v>1</v>
+      </c>
+      <c r="D162">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>260-269</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>210-219</t>
+        </is>
+      </c>
+      <c r="C163">
+        <v>3</v>
+      </c>
+      <c r="D163">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>260-269</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>220-229</t>
+        </is>
+      </c>
+      <c r="C164">
+        <v>8</v>
+      </c>
+      <c r="D164">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>260-269</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>230-239</t>
+        </is>
+      </c>
+      <c r="C165">
+        <v>15</v>
+      </c>
+      <c r="D165">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>260-269</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>240-249</t>
+        </is>
+      </c>
+      <c r="C166">
+        <v>9</v>
+      </c>
+      <c r="D166">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>260-269</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>250-259</t>
+        </is>
+      </c>
+      <c r="C167">
+        <v>6</v>
+      </c>
+      <c r="D167">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>260-269</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>260-269</t>
+        </is>
+      </c>
+      <c r="C168">
+        <v>2</v>
+      </c>
+      <c r="D168">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>260-269</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>270-279</t>
+        </is>
+      </c>
+      <c r="C169">
+        <v>1</v>
+      </c>
+      <c r="D169">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>270-279</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>200-209</t>
+        </is>
+      </c>
+      <c r="C170">
+        <v>2</v>
+      </c>
+      <c r="D170">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>270-279</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>210-219</t>
+        </is>
+      </c>
+      <c r="C171">
+        <v>1</v>
+      </c>
+      <c r="D171">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>270-279</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>220-229</t>
+        </is>
+      </c>
+      <c r="C172">
+        <v>8</v>
+      </c>
+      <c r="D172">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>270-279</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>230-239</t>
+        </is>
+      </c>
+      <c r="C173">
+        <v>3</v>
+      </c>
+      <c r="D173">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>270-279</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>240-249</t>
+        </is>
+      </c>
+      <c r="C174">
+        <v>8</v>
+      </c>
+      <c r="D174">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>270-279</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>250-259</t>
+        </is>
+      </c>
+      <c r="C175">
+        <v>4</v>
+      </c>
+      <c r="D175">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>270-279</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>260-269</t>
+        </is>
+      </c>
+      <c r="C176">
+        <v>7</v>
+      </c>
+      <c r="D176">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>270-279</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>270-279</t>
+        </is>
+      </c>
+      <c r="C177">
+        <v>3</v>
+      </c>
+      <c r="D177">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>270-279</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>290-299</t>
+        </is>
+      </c>
+      <c r="C178">
+        <v>1</v>
+      </c>
+      <c r="D178">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>270-279</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>300-309</t>
+        </is>
+      </c>
+      <c r="C179">
+        <v>1</v>
+      </c>
+      <c r="D179">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>270-279</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>330-339</t>
+        </is>
+      </c>
+      <c r="C180">
+        <v>1</v>
+      </c>
+      <c r="D180">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>280-289</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>220-229</t>
+        </is>
+      </c>
+      <c r="C181">
+        <v>2</v>
+      </c>
+      <c r="D181">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>280-289</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>230-239</t>
+        </is>
+      </c>
+      <c r="C182">
+        <v>2</v>
+      </c>
+      <c r="D182">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>280-289</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>240-249</t>
+        </is>
+      </c>
+      <c r="C183">
+        <v>8</v>
+      </c>
+      <c r="D183">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>280-289</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>250-259</t>
+        </is>
+      </c>
+      <c r="C184">
+        <v>5</v>
+      </c>
+      <c r="D184">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>280-289</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>260-269</t>
+        </is>
+      </c>
+      <c r="C185">
+        <v>7</v>
+      </c>
+      <c r="D185">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>280-289</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>270-279</t>
+        </is>
+      </c>
+      <c r="C186">
+        <v>3</v>
+      </c>
+      <c r="D186">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>280-289</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>280-289</t>
+        </is>
+      </c>
+      <c r="C187">
+        <v>5</v>
+      </c>
+      <c r="D187">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>280-289</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>290-299</t>
+        </is>
+      </c>
+      <c r="C188">
+        <v>2</v>
+      </c>
+      <c r="D188">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>290-299</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>220-229</t>
+        </is>
+      </c>
+      <c r="C189">
+        <v>1</v>
+      </c>
+      <c r="D189">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>290-299</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>230-239</t>
+        </is>
+      </c>
+      <c r="C190">
+        <v>4</v>
+      </c>
+      <c r="D190">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>290-299</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>240-249</t>
+        </is>
+      </c>
+      <c r="C191">
+        <v>2</v>
+      </c>
+      <c r="D191">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>290-299</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>250-259</t>
+        </is>
+      </c>
+      <c r="C192">
+        <v>2</v>
+      </c>
+      <c r="D192">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>290-299</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>260-269</t>
+        </is>
+      </c>
+      <c r="C193">
+        <v>2</v>
+      </c>
+      <c r="D193">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>290-299</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>270-279</t>
+        </is>
+      </c>
+      <c r="C194">
+        <v>6</v>
+      </c>
+      <c r="D194">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>290-299</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>280-289</t>
+        </is>
+      </c>
+      <c r="C195">
+        <v>4</v>
+      </c>
+      <c r="D195">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>290-299</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>290-299</t>
+        </is>
+      </c>
+      <c r="C196">
+        <v>1</v>
+      </c>
+      <c r="D196">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>300-309</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>220-229</t>
+        </is>
+      </c>
+      <c r="C197">
+        <v>1</v>
+      </c>
+      <c r="D197">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>300-309</t>
+        </is>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>230-239</t>
+        </is>
+      </c>
+      <c r="C198">
+        <v>2</v>
+      </c>
+      <c r="D198">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>300-309</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>240-249</t>
+        </is>
+      </c>
+      <c r="C199">
+        <v>5</v>
+      </c>
+      <c r="D199">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>300-309</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>250-259</t>
+        </is>
+      </c>
+      <c r="C200">
+        <v>2</v>
+      </c>
+      <c r="D200">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>300-309</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>260-269</t>
+        </is>
+      </c>
+      <c r="C201">
+        <v>4</v>
+      </c>
+      <c r="D201">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>300-309</t>
+        </is>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>270-279</t>
+        </is>
+      </c>
+      <c r="C202">
+        <v>3</v>
+      </c>
+      <c r="D202">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>300-309</t>
+        </is>
+      </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>280-289</t>
+        </is>
+      </c>
+      <c r="C203">
+        <v>7</v>
+      </c>
+      <c r="D203">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>300-309</t>
+        </is>
+      </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>290-299</t>
+        </is>
+      </c>
+      <c r="C204">
+        <v>1</v>
+      </c>
+      <c r="D204">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>300-309</t>
+        </is>
+      </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>300-309</t>
+        </is>
+      </c>
+      <c r="C205">
+        <v>1</v>
+      </c>
+      <c r="D205">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>310-319</t>
+        </is>
+      </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>250-259</t>
+        </is>
+      </c>
+      <c r="C206">
+        <v>4</v>
+      </c>
+      <c r="D206">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>310-319</t>
+        </is>
+      </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>260-269</t>
+        </is>
+      </c>
+      <c r="C207">
+        <v>2</v>
+      </c>
+      <c r="D207">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>310-319</t>
+        </is>
+      </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>270-279</t>
+        </is>
+      </c>
+      <c r="C208">
+        <v>4</v>
+      </c>
+      <c r="D208">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>310-319</t>
+        </is>
+      </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>280-289</t>
+        </is>
+      </c>
+      <c r="C209">
+        <v>6</v>
+      </c>
+      <c r="D209">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>310-319</t>
+        </is>
+      </c>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>290-299</t>
+        </is>
+      </c>
+      <c r="C210">
+        <v>5</v>
+      </c>
+      <c r="D210">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>310-319</t>
+        </is>
+      </c>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>300-309</t>
+        </is>
+      </c>
+      <c r="C211">
+        <v>2</v>
+      </c>
+      <c r="D211">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>310-319</t>
+        </is>
+      </c>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>310-319</t>
+        </is>
+      </c>
+      <c r="C212">
+        <v>1</v>
+      </c>
+      <c r="D212">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>310-319</t>
+        </is>
+      </c>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>320-329</t>
+        </is>
+      </c>
+      <c r="C213">
+        <v>1</v>
+      </c>
+      <c r="D213">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>310-319</t>
+        </is>
+      </c>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t>330-339</t>
+        </is>
+      </c>
+      <c r="C214">
+        <v>1</v>
+      </c>
+      <c r="D214">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>320-329</t>
+        </is>
+      </c>
+      <c r="B215" t="inlineStr">
+        <is>
+          <t>240-249</t>
+        </is>
+      </c>
+      <c r="C215">
+        <v>2</v>
+      </c>
+      <c r="D215">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>320-329</t>
+        </is>
+      </c>
+      <c r="B216" t="inlineStr">
+        <is>
+          <t>260-269</t>
+        </is>
+      </c>
+      <c r="C216">
+        <v>2</v>
+      </c>
+      <c r="D216">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>320-329</t>
+        </is>
+      </c>
+      <c r="B217" t="inlineStr">
+        <is>
+          <t>270-279</t>
+        </is>
+      </c>
+      <c r="C217">
+        <v>3</v>
+      </c>
+      <c r="D217">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>320-329</t>
+        </is>
+      </c>
+      <c r="B218" t="inlineStr">
+        <is>
+          <t>280-289</t>
+        </is>
+      </c>
+      <c r="C218">
+        <v>6</v>
+      </c>
+      <c r="D218">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
+          <t>320-329</t>
+        </is>
+      </c>
+      <c r="B219" t="inlineStr">
+        <is>
+          <t>290-299</t>
+        </is>
+      </c>
+      <c r="C219">
+        <v>2</v>
+      </c>
+      <c r="D219">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>320-329</t>
+        </is>
+      </c>
+      <c r="B220" t="inlineStr">
+        <is>
+          <t>300-309</t>
+        </is>
+      </c>
+      <c r="C220">
+        <v>6</v>
+      </c>
+      <c r="D220">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>320-329</t>
+        </is>
+      </c>
+      <c r="B221" t="inlineStr">
+        <is>
+          <t>310-319</t>
+        </is>
+      </c>
+      <c r="C221">
+        <v>6</v>
+      </c>
+      <c r="D221">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="inlineStr">
+        <is>
+          <t>320-329</t>
+        </is>
+      </c>
+      <c r="B222" t="inlineStr">
+        <is>
+          <t>320-329</t>
+        </is>
+      </c>
+      <c r="C222">
+        <v>1</v>
+      </c>
+      <c r="D222">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="inlineStr">
+        <is>
+          <t>320-329</t>
+        </is>
+      </c>
+      <c r="B223" t="inlineStr">
+        <is>
+          <t>330-339</t>
+        </is>
+      </c>
+      <c r="C223">
+        <v>1</v>
+      </c>
+      <c r="D223">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="inlineStr">
+        <is>
+          <t>320-329</t>
+        </is>
+      </c>
+      <c r="B224" t="inlineStr">
+        <is>
+          <t>360-369</t>
+        </is>
+      </c>
+      <c r="C224">
+        <v>1</v>
+      </c>
+      <c r="D224">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="inlineStr">
+        <is>
+          <t>330-339</t>
+        </is>
+      </c>
+      <c r="B225" t="inlineStr">
+        <is>
+          <t>250-259</t>
+        </is>
+      </c>
+      <c r="C225">
+        <v>2</v>
+      </c>
+      <c r="D225">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="inlineStr">
+        <is>
+          <t>330-339</t>
+        </is>
+      </c>
+      <c r="B226" t="inlineStr">
+        <is>
+          <t>260-269</t>
+        </is>
+      </c>
+      <c r="C226">
+        <v>3</v>
+      </c>
+      <c r="D226">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="inlineStr">
+        <is>
+          <t>330-339</t>
+        </is>
+      </c>
+      <c r="B227" t="inlineStr">
+        <is>
+          <t>270-279</t>
+        </is>
+      </c>
+      <c r="C227">
+        <v>2</v>
+      </c>
+      <c r="D227">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="inlineStr">
+        <is>
+          <t>330-339</t>
+        </is>
+      </c>
+      <c r="B228" t="inlineStr">
+        <is>
+          <t>280-289</t>
+        </is>
+      </c>
+      <c r="C228">
+        <v>4</v>
+      </c>
+      <c r="D228">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="inlineStr">
+        <is>
+          <t>330-339</t>
+        </is>
+      </c>
+      <c r="B229" t="inlineStr">
+        <is>
+          <t>290-299</t>
+        </is>
+      </c>
+      <c r="C229">
+        <v>7</v>
+      </c>
+      <c r="D229">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="inlineStr">
+        <is>
+          <t>330-339</t>
+        </is>
+      </c>
+      <c r="B230" t="inlineStr">
+        <is>
+          <t>300-309</t>
+        </is>
+      </c>
+      <c r="C230">
+        <v>5</v>
+      </c>
+      <c r="D230">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="inlineStr">
+        <is>
+          <t>330-339</t>
+        </is>
+      </c>
+      <c r="B231" t="inlineStr">
+        <is>
+          <t>310-319</t>
+        </is>
+      </c>
+      <c r="C231">
+        <v>3</v>
+      </c>
+      <c r="D231">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="inlineStr">
+        <is>
+          <t>330-339</t>
+        </is>
+      </c>
+      <c r="B232" t="inlineStr">
+        <is>
+          <t>320-329</t>
+        </is>
+      </c>
+      <c r="C232">
+        <v>2</v>
+      </c>
+      <c r="D232">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="inlineStr">
+        <is>
+          <t>330-339</t>
+        </is>
+      </c>
+      <c r="B233" t="inlineStr">
+        <is>
+          <t>380-389</t>
+        </is>
+      </c>
+      <c r="C233">
+        <v>1</v>
+      </c>
+      <c r="D233">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="inlineStr">
+        <is>
+          <t>340-349</t>
+        </is>
+      </c>
+      <c r="B234" t="inlineStr">
+        <is>
+          <t>260-269</t>
+        </is>
+      </c>
+      <c r="C234">
+        <v>1</v>
+      </c>
+      <c r="D234">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="inlineStr">
+        <is>
+          <t>340-349</t>
+        </is>
+      </c>
+      <c r="B235" t="inlineStr">
+        <is>
+          <t>270-279</t>
+        </is>
+      </c>
+      <c r="C235">
+        <v>3</v>
+      </c>
+      <c r="D235">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="inlineStr">
+        <is>
+          <t>340-349</t>
+        </is>
+      </c>
+      <c r="B236" t="inlineStr">
+        <is>
+          <t>280-289</t>
+        </is>
+      </c>
+      <c r="C236">
+        <v>2</v>
+      </c>
+      <c r="D236">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="inlineStr">
+        <is>
+          <t>340-349</t>
+        </is>
+      </c>
+      <c r="B237" t="inlineStr">
+        <is>
+          <t>290-299</t>
+        </is>
+      </c>
+      <c r="C237">
+        <v>8</v>
+      </c>
+      <c r="D237">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="inlineStr">
+        <is>
+          <t>340-349</t>
+        </is>
+      </c>
+      <c r="B238" t="inlineStr">
+        <is>
+          <t>300-309</t>
+        </is>
+      </c>
+      <c r="C238">
+        <v>3</v>
+      </c>
+      <c r="D238">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="inlineStr">
+        <is>
+          <t>340-349</t>
+        </is>
+      </c>
+      <c r="B239" t="inlineStr">
+        <is>
+          <t>310-319</t>
+        </is>
+      </c>
+      <c r="C239">
+        <v>5</v>
+      </c>
+      <c r="D239">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="inlineStr">
+        <is>
+          <t>340-349</t>
+        </is>
+      </c>
+      <c r="B240" t="inlineStr">
+        <is>
+          <t>320-329</t>
+        </is>
+      </c>
+      <c r="C240">
+        <v>1</v>
+      </c>
+      <c r="D240">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="inlineStr">
+        <is>
+          <t>340-349</t>
+        </is>
+      </c>
+      <c r="B241" t="inlineStr">
+        <is>
+          <t>330-339</t>
+        </is>
+      </c>
+      <c r="C241">
+        <v>1</v>
+      </c>
+      <c r="D241">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" t="inlineStr">
+        <is>
+          <t>350-359</t>
+        </is>
+      </c>
+      <c r="B242" t="inlineStr">
+        <is>
+          <t>270-279</t>
+        </is>
+      </c>
+      <c r="C242">
+        <v>2</v>
+      </c>
+      <c r="D242">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="inlineStr">
+        <is>
+          <t>350-359</t>
+        </is>
+      </c>
+      <c r="B243" t="inlineStr">
+        <is>
+          <t>280-289</t>
+        </is>
+      </c>
+      <c r="C243">
+        <v>2</v>
+      </c>
+      <c r="D243">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" t="inlineStr">
+        <is>
+          <t>350-359</t>
+        </is>
+      </c>
+      <c r="B244" t="inlineStr">
+        <is>
+          <t>290-299</t>
+        </is>
+      </c>
+      <c r="C244">
+        <v>6</v>
+      </c>
+      <c r="D244">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" t="inlineStr">
+        <is>
+          <t>350-359</t>
+        </is>
+      </c>
+      <c r="B245" t="inlineStr">
+        <is>
+          <t>300-309</t>
+        </is>
+      </c>
+      <c r="C245">
+        <v>7</v>
+      </c>
+      <c r="D245">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" t="inlineStr">
+        <is>
+          <t>350-359</t>
+        </is>
+      </c>
+      <c r="B246" t="inlineStr">
+        <is>
+          <t>310-319</t>
+        </is>
+      </c>
+      <c r="C246">
+        <v>3</v>
+      </c>
+      <c r="D246">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" t="inlineStr">
+        <is>
+          <t>350-359</t>
+        </is>
+      </c>
+      <c r="B247" t="inlineStr">
+        <is>
+          <t>330-339</t>
+        </is>
+      </c>
+      <c r="C247">
+        <v>1</v>
+      </c>
+      <c r="D247">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" t="inlineStr">
+        <is>
+          <t>350-359</t>
+        </is>
+      </c>
+      <c r="B248" t="inlineStr">
+        <is>
+          <t>340-349</t>
+        </is>
+      </c>
+      <c r="C248">
+        <v>2</v>
+      </c>
+      <c r="D248">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" t="inlineStr">
+        <is>
+          <t>360-369</t>
+        </is>
+      </c>
+      <c r="B249" t="inlineStr">
+        <is>
+          <t>270-279</t>
+        </is>
+      </c>
+      <c r="C249">
+        <v>1</v>
+      </c>
+      <c r="D249">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" t="inlineStr">
+        <is>
+          <t>360-369</t>
+        </is>
+      </c>
+      <c r="B250" t="inlineStr">
+        <is>
+          <t>280-289</t>
+        </is>
+      </c>
+      <c r="C250">
+        <v>2</v>
+      </c>
+      <c r="D250">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" t="inlineStr">
+        <is>
+          <t>360-369</t>
+        </is>
+      </c>
+      <c r="B251" t="inlineStr">
+        <is>
+          <t>290-299</t>
+        </is>
+      </c>
+      <c r="C251">
+        <v>1</v>
+      </c>
+      <c r="D251">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" t="inlineStr">
+        <is>
+          <t>360-369</t>
+        </is>
+      </c>
+      <c r="B252" t="inlineStr">
+        <is>
+          <t>300-309</t>
+        </is>
+      </c>
+      <c r="C252">
+        <v>4</v>
+      </c>
+      <c r="D252">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" t="inlineStr">
+        <is>
+          <t>360-369</t>
+        </is>
+      </c>
+      <c r="B253" t="inlineStr">
+        <is>
+          <t>310-319</t>
+        </is>
+      </c>
+      <c r="C253">
+        <v>4</v>
+      </c>
+      <c r="D253">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" t="inlineStr">
+        <is>
+          <t>360-369</t>
+        </is>
+      </c>
+      <c r="B254" t="inlineStr">
+        <is>
+          <t>320-329</t>
+        </is>
+      </c>
+      <c r="C254">
+        <v>3</v>
+      </c>
+      <c r="D254">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" t="inlineStr">
+        <is>
+          <t>360-369</t>
+        </is>
+      </c>
+      <c r="B255" t="inlineStr">
+        <is>
+          <t>330-339</t>
+        </is>
+      </c>
+      <c r="C255">
+        <v>2</v>
+      </c>
+      <c r="D255">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" t="inlineStr">
+        <is>
+          <t>360-369</t>
+        </is>
+      </c>
+      <c r="B256" t="inlineStr">
+        <is>
+          <t>350-359</t>
+        </is>
+      </c>
+      <c r="C256">
+        <v>1</v>
+      </c>
+      <c r="D256">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" t="inlineStr">
+        <is>
+          <t>360-369</t>
+        </is>
+      </c>
+      <c r="B257" t="inlineStr">
+        <is>
+          <t>400-409</t>
+        </is>
+      </c>
+      <c r="C257">
+        <v>1</v>
+      </c>
+      <c r="D257">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" t="inlineStr">
+        <is>
+          <t>360-369</t>
+        </is>
+      </c>
+      <c r="C258">
+        <v>1</v>
+      </c>
+      <c r="D258">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" t="inlineStr">
+        <is>
+          <t>370-379</t>
+        </is>
+      </c>
+      <c r="B259" t="inlineStr">
+        <is>
+          <t>270-279</t>
+        </is>
+      </c>
+      <c r="C259">
+        <v>1</v>
+      </c>
+      <c r="D259">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" t="inlineStr">
+        <is>
+          <t>370-379</t>
+        </is>
+      </c>
+      <c r="B260" t="inlineStr">
+        <is>
+          <t>290-299</t>
+        </is>
+      </c>
+      <c r="C260">
+        <v>2</v>
+      </c>
+      <c r="D260">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" t="inlineStr">
+        <is>
+          <t>370-379</t>
+        </is>
+      </c>
+      <c r="B261" t="inlineStr">
+        <is>
+          <t>300-309</t>
+        </is>
+      </c>
+      <c r="C261">
+        <v>2</v>
+      </c>
+      <c r="D261">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" t="inlineStr">
+        <is>
+          <t>370-379</t>
+        </is>
+      </c>
+      <c r="B262" t="inlineStr">
+        <is>
+          <t>320-329</t>
+        </is>
+      </c>
+      <c r="C262">
+        <v>4</v>
+      </c>
+      <c r="D262">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" t="inlineStr">
+        <is>
+          <t>370-379</t>
+        </is>
+      </c>
+      <c r="B263" t="inlineStr">
+        <is>
+          <t>330-339</t>
+        </is>
+      </c>
+      <c r="C263">
+        <v>1</v>
+      </c>
+      <c r="D263">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" t="inlineStr">
+        <is>
+          <t>370-379</t>
+        </is>
+      </c>
+      <c r="B264" t="inlineStr">
+        <is>
+          <t>350-359</t>
+        </is>
+      </c>
+      <c r="C264">
+        <v>1</v>
+      </c>
+      <c r="D264">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" t="inlineStr">
+        <is>
+          <t>370-379</t>
+        </is>
+      </c>
+      <c r="B265" t="inlineStr">
+        <is>
+          <t>410-419</t>
+        </is>
+      </c>
+      <c r="C265">
+        <v>1</v>
+      </c>
+      <c r="D265">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" t="inlineStr">
+        <is>
+          <t>380-389</t>
+        </is>
+      </c>
+      <c r="B266" t="inlineStr">
+        <is>
+          <t>270-279</t>
+        </is>
+      </c>
+      <c r="C266">
+        <v>1</v>
+      </c>
+      <c r="D266">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" t="inlineStr">
+        <is>
+          <t>380-389</t>
+        </is>
+      </c>
+      <c r="B267" t="inlineStr">
+        <is>
+          <t>310-319</t>
+        </is>
+      </c>
+      <c r="C267">
+        <v>3</v>
+      </c>
+      <c r="D267">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" t="inlineStr">
+        <is>
+          <t>380-389</t>
+        </is>
+      </c>
+      <c r="B268" t="inlineStr">
+        <is>
+          <t>330-339</t>
+        </is>
+      </c>
+      <c r="C268">
+        <v>2</v>
+      </c>
+      <c r="D268">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" t="inlineStr">
+        <is>
+          <t>380-389</t>
+        </is>
+      </c>
+      <c r="B269" t="inlineStr">
+        <is>
+          <t>340-349</t>
+        </is>
+      </c>
+      <c r="C269">
+        <v>3</v>
+      </c>
+      <c r="D269">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" t="inlineStr">
+        <is>
+          <t>390-399</t>
+        </is>
+      </c>
+      <c r="B270" t="inlineStr">
+        <is>
+          <t>310-319</t>
+        </is>
+      </c>
+      <c r="C270">
+        <v>1</v>
+      </c>
+      <c r="D270">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" t="inlineStr">
+        <is>
+          <t>390-399</t>
+        </is>
+      </c>
+      <c r="B271" t="inlineStr">
+        <is>
+          <t>320-329</t>
+        </is>
+      </c>
+      <c r="C271">
+        <v>1</v>
+      </c>
+      <c r="D271">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" t="inlineStr">
+        <is>
+          <t>390-399</t>
+        </is>
+      </c>
+      <c r="B272" t="inlineStr">
+        <is>
+          <t>330-339</t>
+        </is>
+      </c>
+      <c r="C272">
+        <v>2</v>
+      </c>
+      <c r="D272">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" t="inlineStr">
+        <is>
+          <t>390-399</t>
+        </is>
+      </c>
+      <c r="B273" t="inlineStr">
+        <is>
+          <t>340-349</t>
+        </is>
+      </c>
+      <c r="C273">
+        <v>2</v>
+      </c>
+      <c r="D273">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" t="inlineStr">
+        <is>
+          <t>390-399</t>
+        </is>
+      </c>
+      <c r="B274" t="inlineStr">
+        <is>
+          <t>360-369</t>
+        </is>
+      </c>
+      <c r="C274">
+        <v>1</v>
+      </c>
+      <c r="D274">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" t="inlineStr">
+        <is>
+          <t>390-399</t>
+        </is>
+      </c>
+      <c r="B275" t="inlineStr">
+        <is>
+          <t>390-399</t>
+        </is>
+      </c>
+      <c r="C275">
+        <v>1</v>
+      </c>
+      <c r="D275">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" t="inlineStr">
+        <is>
+          <t>400-409</t>
+        </is>
+      </c>
+      <c r="B276" t="inlineStr">
+        <is>
+          <t>300-309</t>
+        </is>
+      </c>
+      <c r="C276">
+        <v>2</v>
+      </c>
+      <c r="D276">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" t="inlineStr">
+        <is>
+          <t>400-409</t>
+        </is>
+      </c>
+      <c r="B277" t="inlineStr">
+        <is>
+          <t>310-319</t>
+        </is>
+      </c>
+      <c r="C277">
+        <v>1</v>
+      </c>
+      <c r="D277">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" t="inlineStr">
+        <is>
+          <t>400-409</t>
+        </is>
+      </c>
+      <c r="B278" t="inlineStr">
+        <is>
+          <t>330-339</t>
+        </is>
+      </c>
+      <c r="C278">
+        <v>2</v>
+      </c>
+      <c r="D278">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" t="inlineStr">
+        <is>
+          <t>400-409</t>
+        </is>
+      </c>
+      <c r="B279" t="inlineStr">
+        <is>
+          <t>340-349</t>
+        </is>
+      </c>
+      <c r="C279">
+        <v>1</v>
+      </c>
+      <c r="D279">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" t="inlineStr">
+        <is>
+          <t>400-409</t>
+        </is>
+      </c>
+      <c r="B280" t="inlineStr">
+        <is>
+          <t>360-369</t>
+        </is>
+      </c>
+      <c r="C280">
+        <v>1</v>
+      </c>
+      <c r="D280">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" t="inlineStr">
+        <is>
+          <t>400-409</t>
+        </is>
+      </c>
+      <c r="B281" t="inlineStr">
+        <is>
+          <t>370-379</t>
+        </is>
+      </c>
+      <c r="C281">
+        <v>1</v>
+      </c>
+      <c r="D281">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" t="inlineStr">
+        <is>
+          <t>410-419</t>
+        </is>
+      </c>
+      <c r="B282" t="inlineStr">
+        <is>
+          <t>310-319</t>
+        </is>
+      </c>
+      <c r="C282">
+        <v>2</v>
+      </c>
+      <c r="D282">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" t="inlineStr">
+        <is>
+          <t>410-419</t>
+        </is>
+      </c>
+      <c r="B283" t="inlineStr">
+        <is>
+          <t>330-339</t>
+        </is>
+      </c>
+      <c r="C283">
+        <v>1</v>
+      </c>
+      <c r="D283">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" t="inlineStr">
+        <is>
+          <t>410-419</t>
+        </is>
+      </c>
+      <c r="B284" t="inlineStr">
+        <is>
+          <t>340-349</t>
+        </is>
+      </c>
+      <c r="C284">
+        <v>1</v>
+      </c>
+      <c r="D284">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" t="inlineStr">
+        <is>
+          <t>410-419</t>
+        </is>
+      </c>
+      <c r="B285" t="inlineStr">
+        <is>
+          <t>350-359</t>
+        </is>
+      </c>
+      <c r="C285">
+        <v>1</v>
+      </c>
+      <c r="D285">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" t="inlineStr">
+        <is>
+          <t>410-419</t>
+        </is>
+      </c>
+      <c r="B286" t="inlineStr">
+        <is>
+          <t>390-399</t>
+        </is>
+      </c>
+      <c r="C286">
+        <v>1</v>
+      </c>
+      <c r="D286">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" t="inlineStr">
+        <is>
+          <t>420-429</t>
+        </is>
+      </c>
+      <c r="B287" t="inlineStr">
+        <is>
+          <t>330-339</t>
+        </is>
+      </c>
+      <c r="C287">
+        <v>1</v>
+      </c>
+      <c r="D287">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" t="inlineStr">
+        <is>
+          <t>420-429</t>
+        </is>
+      </c>
+      <c r="B288" t="inlineStr">
+        <is>
+          <t>340-349</t>
+        </is>
+      </c>
+      <c r="C288">
+        <v>2</v>
+      </c>
+      <c r="D288">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" t="inlineStr">
+        <is>
+          <t>420-429</t>
+        </is>
+      </c>
+      <c r="B289" t="inlineStr">
+        <is>
+          <t>350-359</t>
+        </is>
+      </c>
+      <c r="C289">
+        <v>2</v>
+      </c>
+      <c r="D289">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" t="inlineStr">
+        <is>
+          <t>420-429</t>
+        </is>
+      </c>
+      <c r="B290" t="inlineStr">
+        <is>
+          <t>370-379</t>
+        </is>
+      </c>
+      <c r="C290">
+        <v>1</v>
+      </c>
+      <c r="D290">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" t="inlineStr">
+        <is>
+          <t>430-439</t>
+        </is>
+      </c>
+      <c r="B291" t="inlineStr">
+        <is>
+          <t>360-369</t>
+        </is>
+      </c>
+      <c r="C291">
+        <v>1</v>
+      </c>
+      <c r="D291">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" t="inlineStr">
+        <is>
+          <t>430-439</t>
+        </is>
+      </c>
+      <c r="B292" t="inlineStr">
+        <is>
+          <t>380-389</t>
+        </is>
+      </c>
+      <c r="C292">
+        <v>1</v>
+      </c>
+      <c r="D292">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" t="inlineStr">
+        <is>
+          <t>440-449</t>
+        </is>
+      </c>
+      <c r="B293" t="inlineStr">
+        <is>
+          <t>360-369</t>
+        </is>
+      </c>
+      <c r="C293">
+        <v>1</v>
+      </c>
+      <c r="D293">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" t="inlineStr">
+        <is>
+          <t>450-459</t>
+        </is>
+      </c>
+      <c r="B294" t="inlineStr">
+        <is>
+          <t>340-349</t>
+        </is>
+      </c>
+      <c r="C294">
+        <v>1</v>
+      </c>
+      <c r="D294">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" t="inlineStr">
+        <is>
+          <t>450-459</t>
+        </is>
+      </c>
+      <c r="B295" t="inlineStr">
+        <is>
+          <t>350-359</t>
+        </is>
+      </c>
+      <c r="C295">
+        <v>2</v>
+      </c>
+      <c r="D295">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" t="inlineStr">
+        <is>
+          <t>450-459</t>
+        </is>
+      </c>
+      <c r="B296" t="inlineStr">
+        <is>
+          <t>360-369</t>
+        </is>
+      </c>
+      <c r="C296">
+        <v>2</v>
+      </c>
+      <c r="D296">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" t="inlineStr">
+        <is>
+          <t>450-459</t>
+        </is>
+      </c>
+      <c r="B297" t="inlineStr">
+        <is>
+          <t>380-389</t>
+        </is>
+      </c>
+      <c r="C297">
+        <v>1</v>
+      </c>
+      <c r="D297">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" t="inlineStr">
+        <is>
+          <t>450-459</t>
+        </is>
+      </c>
+      <c r="B298" t="inlineStr">
+        <is>
+          <t>440-449</t>
+        </is>
+      </c>
+      <c r="C298">
+        <v>1</v>
+      </c>
+      <c r="D298">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" t="inlineStr">
+        <is>
+          <t>460-469</t>
+        </is>
+      </c>
+      <c r="B299" t="inlineStr">
+        <is>
+          <t>370-379</t>
+        </is>
+      </c>
+      <c r="C299">
+        <v>1</v>
+      </c>
+      <c r="D299">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" t="inlineStr">
+        <is>
+          <t>460-469</t>
+        </is>
+      </c>
+      <c r="B300" t="inlineStr">
+        <is>
+          <t>390-399</t>
+        </is>
+      </c>
+      <c r="C300">
+        <v>1</v>
+      </c>
+      <c r="D300">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" t="inlineStr">
+        <is>
+          <t>470-479</t>
+        </is>
+      </c>
+      <c r="B301" t="inlineStr">
+        <is>
+          <t>440-449</t>
+        </is>
+      </c>
+      <c r="C301">
+        <v>1</v>
+      </c>
+      <c r="D301">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" t="inlineStr">
+        <is>
+          <t>490-499</t>
+        </is>
+      </c>
+      <c r="B302" t="inlineStr">
+        <is>
+          <t>380-389</t>
+        </is>
+      </c>
+      <c r="C302">
+        <v>1</v>
+      </c>
+      <c r="D302">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="303">
+      <c r="B303" t="inlineStr">
+        <is>
+          <t>380-389</t>
+        </is>
+      </c>
+      <c r="C303">
+        <v>1</v>
+      </c>
+      <c r="D303">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="304">
+      <c r="B304" t="inlineStr">
+        <is>
+          <t>430-439</t>
+        </is>
+      </c>
+      <c r="C304">
+        <v>1</v>
+      </c>
+      <c r="D304">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="305">
+      <c r="B305" t="inlineStr">
+        <is>
+          <t>460-469</t>
+        </is>
+      </c>
+      <c r="C305">
+        <v>1</v>
+      </c>
+      <c r="D305">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="306">
+      <c r="B306" t="inlineStr">
+        <is>
           <t>480-489</t>
         </is>
       </c>
-      <c r="B44">
-        <v>624.0195430475837</v>
-      </c>
-      <c r="C44">
-        <v>488.5441867476865</v>
-      </c>
-      <c r="D44">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="45">
-      <c r="B45">
-        <v>8456.405623486477</v>
-      </c>
-      <c r="C45">
-        <v>8794.134989834782</v>
-      </c>
-      <c r="D45">
-        <v>11</v>
+      <c r="C306">
+        <v>1</v>
+      </c>
+      <c r="D306">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="307">
+      <c r="C307">
+        <v>8</v>
+      </c>
+      <c r="D307">
+        <v>8</v>
       </c>
     </row>
   </sheetData>

--- a/const/Binned_Summary.xlsx
+++ b/const/Binned_Summary.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D307"/>
+  <dimension ref="A1:D308"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -415,61 +415,61 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>30-39</t>
+          <t>100-109</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>20-29</t>
+          <t>100-109</t>
         </is>
       </c>
       <c r="C4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D4">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>30-39</t>
+          <t>100-109</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>30-39</t>
+          <t>110-119</t>
         </is>
       </c>
       <c r="C5">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D5">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>30-39</t>
+          <t>100-109</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>40-49</t>
+          <t>120-129</t>
         </is>
       </c>
       <c r="C6">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="D6">
-        <v>1</v>
+        <v>12</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>60-69</t>
+          <t>100-109</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -478,39 +478,39 @@
         </is>
       </c>
       <c r="C7">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="D7">
-        <v>1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>80-89</t>
+          <t>100-109</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>110-119</t>
+          <t>140-149</t>
         </is>
       </c>
       <c r="C8">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D8">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>80-89</t>
+          <t>100-109</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>140-149</t>
+          <t>150-159</t>
         </is>
       </c>
       <c r="C9">
@@ -523,12 +523,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>90-99</t>
+          <t>100-109</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>100-109</t>
+          <t>80-89</t>
         </is>
       </c>
       <c r="C10">
@@ -541,282 +541,282 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>90-99</t>
+          <t>110-119</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>120-129</t>
+          <t>100-109</t>
         </is>
       </c>
       <c r="C11">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D11">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>90-99</t>
+          <t>110-119</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>130-139</t>
+          <t>110-119</t>
         </is>
       </c>
       <c r="C12">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D12">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>90-99</t>
+          <t>110-119</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>140-149</t>
+          <t>120-129</t>
         </is>
       </c>
       <c r="C13">
-        <v>2</v>
+        <v>39</v>
       </c>
       <c r="D13">
-        <v>2</v>
+        <v>39</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>100-109</t>
+          <t>110-119</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>80-89</t>
+          <t>130-139</t>
         </is>
       </c>
       <c r="C14">
-        <v>1</v>
+        <v>71</v>
       </c>
       <c r="D14">
-        <v>1</v>
+        <v>71</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>100-109</t>
+          <t>110-119</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>100-109</t>
+          <t>140-149</t>
         </is>
       </c>
       <c r="C15">
-        <v>2</v>
+        <v>29</v>
       </c>
       <c r="D15">
-        <v>2</v>
+        <v>29</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>100-109</t>
+          <t>110-119</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>110-119</t>
+          <t>160-169</t>
         </is>
       </c>
       <c r="C16">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D16">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
+          <t>120-129</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
           <t>100-109</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>120-129</t>
-        </is>
-      </c>
       <c r="C17">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="D17">
-        <v>12</v>
+        <v>1</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>100-109</t>
+          <t>120-129</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>130-139</t>
+          <t>110-119</t>
         </is>
       </c>
       <c r="C18">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="D18">
-        <v>10</v>
+        <v>2</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>100-109</t>
+          <t>120-129</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>140-149</t>
+          <t>120-129</t>
         </is>
       </c>
       <c r="C19">
-        <v>3</v>
+        <v>48</v>
       </c>
       <c r="D19">
-        <v>3</v>
+        <v>48</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>100-109</t>
+          <t>120-129</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>150-159</t>
+          <t>130-139</t>
         </is>
       </c>
       <c r="C20">
-        <v>1</v>
+        <v>136</v>
       </c>
       <c r="D20">
-        <v>1</v>
+        <v>136</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>110-119</t>
+          <t>120-129</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>100-109</t>
+          <t>140-149</t>
         </is>
       </c>
       <c r="C21">
-        <v>2</v>
+        <v>105</v>
       </c>
       <c r="D21">
-        <v>2</v>
+        <v>105</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>110-119</t>
+          <t>120-129</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>110-119</t>
+          <t>150-159</t>
         </is>
       </c>
       <c r="C22">
-        <v>2</v>
+        <v>33</v>
       </c>
       <c r="D22">
-        <v>2</v>
+        <v>33</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>110-119</t>
+          <t>120-129</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>120-129</t>
+          <t>160-169</t>
         </is>
       </c>
       <c r="C23">
-        <v>39</v>
+        <v>10</v>
       </c>
       <c r="D23">
-        <v>39</v>
+        <v>10</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>110-119</t>
+          <t>120-129</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>130-139</t>
+          <t>170-179</t>
         </is>
       </c>
       <c r="C24">
-        <v>71</v>
+        <v>2</v>
       </c>
       <c r="D24">
-        <v>71</v>
+        <v>2</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>110-119</t>
+          <t>130-139</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>140-149</t>
+          <t>100-109</t>
         </is>
       </c>
       <c r="C25">
-        <v>29</v>
+        <v>1</v>
       </c>
       <c r="D25">
-        <v>29</v>
+        <v>1</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
+          <t>130-139</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
           <t>110-119</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>160-169</t>
         </is>
       </c>
       <c r="C26">
@@ -829,961 +829,961 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
+          <t>130-139</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
           <t>120-129</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>100-109</t>
-        </is>
-      </c>
       <c r="C27">
-        <v>1</v>
+        <v>26</v>
       </c>
       <c r="D27">
-        <v>1</v>
+        <v>26</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>120-129</t>
+          <t>130-139</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>110-119</t>
+          <t>130-139</t>
         </is>
       </c>
       <c r="C28">
-        <v>2</v>
+        <v>193</v>
       </c>
       <c r="D28">
-        <v>2</v>
+        <v>193</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>120-129</t>
+          <t>130-139</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>120-129</t>
+          <t>140-149</t>
         </is>
       </c>
       <c r="C29">
-        <v>48</v>
+        <v>287</v>
       </c>
       <c r="D29">
-        <v>48</v>
+        <v>287</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>120-129</t>
+          <t>130-139</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>130-139</t>
+          <t>150-159</t>
         </is>
       </c>
       <c r="C30">
-        <v>136</v>
+        <v>145</v>
       </c>
       <c r="D30">
-        <v>136</v>
+        <v>145</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>120-129</t>
+          <t>130-139</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>140-149</t>
+          <t>160-169</t>
         </is>
       </c>
       <c r="C31">
-        <v>105</v>
+        <v>42</v>
       </c>
       <c r="D31">
-        <v>105</v>
+        <v>42</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>120-129</t>
+          <t>130-139</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>150-159</t>
+          <t>170-179</t>
         </is>
       </c>
       <c r="C32">
-        <v>33</v>
+        <v>2</v>
       </c>
       <c r="D32">
-        <v>33</v>
+        <v>2</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>120-129</t>
+          <t>130-139</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>160-169</t>
+          <t>180-189</t>
         </is>
       </c>
       <c r="C33">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="D33">
-        <v>10</v>
+        <v>2</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>120-129</t>
+          <t>130-139</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>170-179</t>
+          <t>200-209</t>
         </is>
       </c>
       <c r="C34">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D34">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>130-139</t>
+          <t>140-149</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>100-109</t>
+          <t>110-119</t>
         </is>
       </c>
       <c r="C35">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D35">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>130-139</t>
+          <t>140-149</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>110-119</t>
+          <t>120-129</t>
         </is>
       </c>
       <c r="C36">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="D36">
-        <v>1</v>
+        <v>12</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
+          <t>140-149</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
           <t>130-139</t>
         </is>
       </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>120-129</t>
-        </is>
-      </c>
       <c r="C37">
-        <v>26</v>
+        <v>128</v>
       </c>
       <c r="D37">
-        <v>26</v>
+        <v>128</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>130-139</t>
+          <t>140-149</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>130-139</t>
+          <t>140-149</t>
         </is>
       </c>
       <c r="C38">
-        <v>193</v>
+        <v>295</v>
       </c>
       <c r="D38">
-        <v>193</v>
+        <v>295</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>130-139</t>
+          <t>140-149</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>140-149</t>
+          <t>150-159</t>
         </is>
       </c>
       <c r="C39">
-        <v>287</v>
+        <v>308</v>
       </c>
       <c r="D39">
-        <v>287</v>
+        <v>308</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>130-139</t>
+          <t>140-149</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>150-159</t>
+          <t>160-169</t>
         </is>
       </c>
       <c r="C40">
-        <v>145</v>
+        <v>96</v>
       </c>
       <c r="D40">
-        <v>145</v>
+        <v>96</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>130-139</t>
+          <t>140-149</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>160-169</t>
+          <t>170-179</t>
         </is>
       </c>
       <c r="C41">
-        <v>42</v>
+        <v>25</v>
       </c>
       <c r="D41">
-        <v>42</v>
+        <v>25</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>130-139</t>
+          <t>140-149</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>170-179</t>
+          <t>180-189</t>
         </is>
       </c>
       <c r="C42">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D42">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>130-139</t>
+          <t>140-149</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>180-189</t>
+          <t>190-199</t>
         </is>
       </c>
       <c r="C43">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D43">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>130-139</t>
+          <t>150-159</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>200-209</t>
+          <t>120-129</t>
         </is>
       </c>
       <c r="C44">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="D44">
-        <v>3</v>
+        <v>7</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>140-149</t>
+          <t>150-159</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>110-119</t>
+          <t>130-139</t>
         </is>
       </c>
       <c r="C45">
-        <v>2</v>
+        <v>71</v>
       </c>
       <c r="D45">
-        <v>2</v>
+        <v>71</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
+          <t>150-159</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
           <t>140-149</t>
         </is>
       </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>120-129</t>
-        </is>
-      </c>
       <c r="C46">
-        <v>12</v>
+        <v>254</v>
       </c>
       <c r="D46">
-        <v>12</v>
+        <v>254</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>140-149</t>
+          <t>150-159</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>130-139</t>
+          <t>150-159</t>
         </is>
       </c>
       <c r="C47">
-        <v>128</v>
+        <v>299</v>
       </c>
       <c r="D47">
-        <v>128</v>
+        <v>299</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>140-149</t>
+          <t>150-159</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>140-149</t>
+          <t>160-169</t>
         </is>
       </c>
       <c r="C48">
-        <v>295</v>
+        <v>201</v>
       </c>
       <c r="D48">
-        <v>295</v>
+        <v>201</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>140-149</t>
+          <t>150-159</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>150-159</t>
+          <t>170-179</t>
         </is>
       </c>
       <c r="C49">
-        <v>308</v>
+        <v>70</v>
       </c>
       <c r="D49">
-        <v>308</v>
+        <v>70</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>140-149</t>
+          <t>150-159</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>160-169</t>
+          <t>180-189</t>
         </is>
       </c>
       <c r="C50">
-        <v>96</v>
+        <v>16</v>
       </c>
       <c r="D50">
-        <v>96</v>
+        <v>16</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>140-149</t>
+          <t>150-159</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>170-179</t>
+          <t>190-199</t>
         </is>
       </c>
       <c r="C51">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="D51">
-        <v>25</v>
+        <v>1</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>140-149</t>
+          <t>150-159</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>180-189</t>
+          <t>220-229</t>
         </is>
       </c>
       <c r="C52">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D52">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>140-149</t>
+          <t>160-169</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>190-199</t>
+          <t>130-139</t>
         </is>
       </c>
       <c r="C53">
-        <v>1</v>
+        <v>23</v>
       </c>
       <c r="D53">
-        <v>1</v>
+        <v>23</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>150-159</t>
+          <t>160-169</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>120-129</t>
+          <t>140-149</t>
         </is>
       </c>
       <c r="C54">
-        <v>7</v>
+        <v>141</v>
       </c>
       <c r="D54">
-        <v>7</v>
+        <v>141</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
+          <t>160-169</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
           <t>150-159</t>
         </is>
       </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>130-139</t>
-        </is>
-      </c>
       <c r="C55">
-        <v>71</v>
+        <v>256</v>
       </c>
       <c r="D55">
-        <v>71</v>
+        <v>256</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>150-159</t>
+          <t>160-169</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>140-149</t>
+          <t>160-169</t>
         </is>
       </c>
       <c r="C56">
-        <v>254</v>
+        <v>201</v>
       </c>
       <c r="D56">
-        <v>254</v>
+        <v>201</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>150-159</t>
+          <t>160-169</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>150-159</t>
+          <t>170-179</t>
         </is>
       </c>
       <c r="C57">
-        <v>299</v>
+        <v>112</v>
       </c>
       <c r="D57">
-        <v>299</v>
+        <v>112</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>150-159</t>
+          <t>160-169</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>160-169</t>
+          <t>180-189</t>
         </is>
       </c>
       <c r="C58">
-        <v>201</v>
+        <v>33</v>
       </c>
       <c r="D58">
-        <v>201</v>
+        <v>33</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>150-159</t>
+          <t>160-169</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>170-179</t>
+          <t>190-199</t>
         </is>
       </c>
       <c r="C59">
-        <v>70</v>
+        <v>8</v>
       </c>
       <c r="D59">
-        <v>70</v>
+        <v>8</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>150-159</t>
+          <t>160-169</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>180-189</t>
+          <t>200-209</t>
         </is>
       </c>
       <c r="C60">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="D60">
-        <v>16</v>
+        <v>2</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>150-159</t>
+          <t>160-169</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>190-199</t>
+          <t>220-229</t>
         </is>
       </c>
       <c r="C61">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D61">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>150-159</t>
+          <t>170-179</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>220-229</t>
+          <t>130-139</t>
         </is>
       </c>
       <c r="C62">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="D62">
-        <v>1</v>
+        <v>9</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>160-169</t>
+          <t>170-179</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>130-139</t>
+          <t>140-149</t>
         </is>
       </c>
       <c r="C63">
-        <v>23</v>
+        <v>42</v>
       </c>
       <c r="D63">
-        <v>23</v>
+        <v>42</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>160-169</t>
+          <t>170-179</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>140-149</t>
+          <t>150-159</t>
         </is>
       </c>
       <c r="C64">
-        <v>141</v>
+        <v>129</v>
       </c>
       <c r="D64">
-        <v>141</v>
+        <v>129</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
+          <t>170-179</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
           <t>160-169</t>
         </is>
       </c>
-      <c r="B65" t="inlineStr">
-        <is>
-          <t>150-159</t>
-        </is>
-      </c>
       <c r="C65">
-        <v>256</v>
+        <v>164</v>
       </c>
       <c r="D65">
-        <v>256</v>
+        <v>164</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>160-169</t>
+          <t>170-179</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>160-169</t>
+          <t>170-179</t>
         </is>
       </c>
       <c r="C66">
-        <v>201</v>
+        <v>121</v>
       </c>
       <c r="D66">
-        <v>201</v>
+        <v>121</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>160-169</t>
+          <t>170-179</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>170-179</t>
+          <t>180-189</t>
         </is>
       </c>
       <c r="C67">
-        <v>112</v>
+        <v>60</v>
       </c>
       <c r="D67">
-        <v>112</v>
+        <v>60</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>160-169</t>
+          <t>170-179</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>180-189</t>
+          <t>190-199</t>
         </is>
       </c>
       <c r="C68">
-        <v>33</v>
+        <v>17</v>
       </c>
       <c r="D68">
-        <v>33</v>
+        <v>17</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>160-169</t>
+          <t>170-179</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>190-199</t>
+          <t>200-209</t>
         </is>
       </c>
       <c r="C69">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="D69">
-        <v>8</v>
+        <v>2</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>160-169</t>
+          <t>170-179</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>200-209</t>
+          <t>220-229</t>
         </is>
       </c>
       <c r="C70">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D70">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>160-169</t>
+          <t>180-189</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>220-229</t>
+          <t>130-139</t>
         </is>
       </c>
       <c r="C71">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D71">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>170-179</t>
+          <t>180-189</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>130-139</t>
+          <t>140-149</t>
         </is>
       </c>
       <c r="C72">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="D72">
-        <v>9</v>
+        <v>18</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>170-179</t>
+          <t>180-189</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>140-149</t>
+          <t>150-159</t>
         </is>
       </c>
       <c r="C73">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D73">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>170-179</t>
+          <t>180-189</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>150-159</t>
+          <t>160-169</t>
         </is>
       </c>
       <c r="C74">
-        <v>129</v>
+        <v>89</v>
       </c>
       <c r="D74">
-        <v>129</v>
+        <v>89</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
+          <t>180-189</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
           <t>170-179</t>
         </is>
       </c>
-      <c r="B75" t="inlineStr">
-        <is>
-          <t>160-169</t>
-        </is>
-      </c>
       <c r="C75">
-        <v>164</v>
+        <v>78</v>
       </c>
       <c r="D75">
-        <v>164</v>
+        <v>78</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>170-179</t>
+          <t>180-189</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>170-179</t>
+          <t>180-189</t>
         </is>
       </c>
       <c r="C76">
-        <v>121</v>
+        <v>49</v>
       </c>
       <c r="D76">
-        <v>121</v>
+        <v>49</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>170-179</t>
+          <t>180-189</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>180-189</t>
+          <t>190-199</t>
         </is>
       </c>
       <c r="C77">
-        <v>60</v>
+        <v>31</v>
       </c>
       <c r="D77">
-        <v>60</v>
+        <v>31</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>170-179</t>
+          <t>180-189</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>190-199</t>
+          <t>200-209</t>
         </is>
       </c>
       <c r="C78">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="D78">
-        <v>17</v>
+        <v>10</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>170-179</t>
+          <t>180-189</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>200-209</t>
+          <t>210-219</t>
         </is>
       </c>
       <c r="C79">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D79">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>170-179</t>
+          <t>180-189</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -1792,10 +1792,10 @@
         </is>
       </c>
       <c r="C80">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D80">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="81">
@@ -1806,7 +1806,7 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>130-139</t>
+          <t>240-249</t>
         </is>
       </c>
       <c r="C81">
@@ -1824,349 +1824,349 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>140-149</t>
+          <t>250-259</t>
         </is>
       </c>
       <c r="C82">
-        <v>18</v>
+        <v>1</v>
       </c>
       <c r="D82">
-        <v>18</v>
+        <v>1</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>180-189</t>
+          <t>190-199</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>150-159</t>
+          <t>140-149</t>
         </is>
       </c>
       <c r="C83">
-        <v>41</v>
+        <v>2</v>
       </c>
       <c r="D83">
-        <v>41</v>
+        <v>2</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>180-189</t>
+          <t>190-199</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>160-169</t>
+          <t>150-159</t>
         </is>
       </c>
       <c r="C84">
-        <v>89</v>
+        <v>16</v>
       </c>
       <c r="D84">
-        <v>89</v>
+        <v>16</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>180-189</t>
+          <t>190-199</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>170-179</t>
+          <t>160-169</t>
         </is>
       </c>
       <c r="C85">
-        <v>78</v>
+        <v>39</v>
       </c>
       <c r="D85">
-        <v>78</v>
+        <v>39</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>180-189</t>
+          <t>190-199</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>180-189</t>
+          <t>170-179</t>
         </is>
       </c>
       <c r="C86">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="D86">
-        <v>49</v>
+        <v>47</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
+          <t>190-199</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
           <t>180-189</t>
         </is>
       </c>
-      <c r="B87" t="inlineStr">
-        <is>
-          <t>190-199</t>
-        </is>
-      </c>
       <c r="C87">
-        <v>31</v>
+        <v>51</v>
       </c>
       <c r="D87">
-        <v>31</v>
+        <v>51</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>180-189</t>
+          <t>190-199</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>200-209</t>
+          <t>190-199</t>
         </is>
       </c>
       <c r="C88">
-        <v>10</v>
+        <v>40</v>
       </c>
       <c r="D88">
-        <v>10</v>
+        <v>40</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>180-189</t>
+          <t>190-199</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>210-219</t>
+          <t>200-209</t>
         </is>
       </c>
       <c r="C89">
-        <v>3</v>
+        <v>19</v>
       </c>
       <c r="D89">
-        <v>3</v>
+        <v>19</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>180-189</t>
+          <t>190-199</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>220-229</t>
+          <t>210-219</t>
         </is>
       </c>
       <c r="C90">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="D90">
-        <v>2</v>
+        <v>9</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>180-189</t>
+          <t>190-199</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>240-249</t>
+          <t>220-229</t>
         </is>
       </c>
       <c r="C91">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D91">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>180-189</t>
+          <t>190-199</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>250-259</t>
+          <t>230-239</t>
         </is>
       </c>
       <c r="C92">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D92">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>190-199</t>
+          <t>200-209</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>140-149</t>
+          <t>150-159</t>
         </is>
       </c>
       <c r="C93">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D93">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>190-199</t>
+          <t>200-209</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>150-159</t>
+          <t>160-169</t>
         </is>
       </c>
       <c r="C94">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D94">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>190-199</t>
+          <t>200-209</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>160-169</t>
+          <t>170-179</t>
         </is>
       </c>
       <c r="C95">
-        <v>39</v>
+        <v>27</v>
       </c>
       <c r="D95">
-        <v>39</v>
+        <v>27</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>190-199</t>
+          <t>200-209</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>170-179</t>
+          <t>180-189</t>
         </is>
       </c>
       <c r="C96">
-        <v>47</v>
+        <v>25</v>
       </c>
       <c r="D96">
-        <v>47</v>
+        <v>25</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
+          <t>200-209</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
           <t>190-199</t>
         </is>
       </c>
-      <c r="B97" t="inlineStr">
-        <is>
-          <t>180-189</t>
-        </is>
-      </c>
       <c r="C97">
-        <v>51</v>
+        <v>36</v>
       </c>
       <c r="D97">
-        <v>51</v>
+        <v>36</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>190-199</t>
+          <t>200-209</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>190-199</t>
+          <t>200-209</t>
         </is>
       </c>
       <c r="C98">
-        <v>40</v>
+        <v>23</v>
       </c>
       <c r="D98">
-        <v>40</v>
+        <v>23</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>190-199</t>
+          <t>200-209</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>200-209</t>
+          <t>210-219</t>
         </is>
       </c>
       <c r="C99">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="D99">
-        <v>19</v>
+        <v>11</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>190-199</t>
+          <t>200-209</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>210-219</t>
+          <t>220-229</t>
         </is>
       </c>
       <c r="C100">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="D100">
-        <v>9</v>
+        <v>3</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>190-199</t>
+          <t>200-209</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>220-229</t>
+          <t>230-239</t>
         </is>
       </c>
       <c r="C101">
@@ -2179,12 +2179,12 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>190-199</t>
+          <t>210-219</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>230-239</t>
+          <t>150-159</t>
         </is>
       </c>
       <c r="C102">
@@ -2197,336 +2197,336 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>200-209</t>
+          <t>210-219</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>150-159</t>
+          <t>160-169</t>
         </is>
       </c>
       <c r="C103">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D103">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>200-209</t>
+          <t>210-219</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>160-169</t>
+          <t>170-179</t>
         </is>
       </c>
       <c r="C104">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="D104">
-        <v>17</v>
+        <v>8</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>200-209</t>
+          <t>210-219</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>170-179</t>
+          <t>180-189</t>
         </is>
       </c>
       <c r="C105">
-        <v>27</v>
+        <v>14</v>
       </c>
       <c r="D105">
-        <v>27</v>
+        <v>14</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>200-209</t>
+          <t>210-219</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>180-189</t>
+          <t>190-199</t>
         </is>
       </c>
       <c r="C106">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D106">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
+          <t>210-219</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
           <t>200-209</t>
         </is>
       </c>
-      <c r="B107" t="inlineStr">
-        <is>
-          <t>190-199</t>
-        </is>
-      </c>
       <c r="C107">
-        <v>36</v>
+        <v>27</v>
       </c>
       <c r="D107">
-        <v>36</v>
+        <v>27</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>200-209</t>
+          <t>210-219</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>200-209</t>
+          <t>210-219</t>
         </is>
       </c>
       <c r="C108">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="D108">
-        <v>23</v>
+        <v>17</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>200-209</t>
+          <t>210-219</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>210-219</t>
+          <t>220-229</t>
         </is>
       </c>
       <c r="C109">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D109">
-        <v>11</v>
+        <v>7</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>200-209</t>
+          <t>210-219</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>220-229</t>
+          <t>230-239</t>
         </is>
       </c>
       <c r="C110">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="D110">
-        <v>3</v>
+        <v>7</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>200-209</t>
+          <t>210-219</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>230-239</t>
+          <t>240-249</t>
         </is>
       </c>
       <c r="C111">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D111">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>210-219</t>
+          <t>220-229</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>150-159</t>
+          <t>170-179</t>
         </is>
       </c>
       <c r="C112">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D112">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>210-219</t>
+          <t>220-229</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>160-169</t>
+          <t>180-189</t>
         </is>
       </c>
       <c r="C113">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D113">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>210-219</t>
+          <t>220-229</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>170-179</t>
+          <t>190-199</t>
         </is>
       </c>
       <c r="C114">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="D114">
-        <v>8</v>
+        <v>11</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>210-219</t>
+          <t>220-229</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>180-189</t>
+          <t>200-209</t>
         </is>
       </c>
       <c r="C115">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D115">
-        <v>14</v>
+        <v>16</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
+          <t>220-229</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
           <t>210-219</t>
         </is>
       </c>
-      <c r="B116" t="inlineStr">
-        <is>
-          <t>190-199</t>
-        </is>
-      </c>
       <c r="C116">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="D116">
-        <v>24</v>
+        <v>15</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>210-219</t>
+          <t>220-229</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>200-209</t>
+          <t>220-229</t>
         </is>
       </c>
       <c r="C117">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="D117">
-        <v>27</v>
+        <v>12</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>210-219</t>
+          <t>220-229</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>210-219</t>
+          <t>230-239</t>
         </is>
       </c>
       <c r="C118">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="D118">
-        <v>17</v>
+        <v>7</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>210-219</t>
+          <t>220-229</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>220-229</t>
+          <t>240-249</t>
         </is>
       </c>
       <c r="C119">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="D119">
-        <v>7</v>
+        <v>3</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>210-219</t>
+          <t>220-229</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>230-239</t>
+          <t>250-259</t>
         </is>
       </c>
       <c r="C120">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="D120">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>210-219</t>
+          <t>220-229</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>240-249</t>
+          <t>330-339</t>
         </is>
       </c>
       <c r="C121">
@@ -2539,372 +2539,372 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>220-229</t>
+          <t>230-239</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>170-179</t>
+          <t>160-169</t>
         </is>
       </c>
       <c r="C122">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D122">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>220-229</t>
+          <t>230-239</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>180-189</t>
+          <t>170-179</t>
         </is>
       </c>
       <c r="C123">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="D123">
-        <v>9</v>
+        <v>1</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>220-229</t>
+          <t>230-239</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>190-199</t>
+          <t>180-189</t>
         </is>
       </c>
       <c r="C124">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="D124">
-        <v>11</v>
+        <v>4</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>220-229</t>
+          <t>230-239</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>200-209</t>
+          <t>190-199</t>
         </is>
       </c>
       <c r="C125">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="D125">
-        <v>16</v>
+        <v>5</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>220-229</t>
+          <t>230-239</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>210-219</t>
+          <t>200-209</t>
         </is>
       </c>
       <c r="C126">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="D126">
-        <v>15</v>
+        <v>10</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>220-229</t>
+          <t>230-239</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>220-229</t>
+          <t>210-219</t>
         </is>
       </c>
       <c r="C127">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="D127">
-        <v>12</v>
+        <v>20</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
+          <t>230-239</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
           <t>220-229</t>
         </is>
       </c>
-      <c r="B128" t="inlineStr">
-        <is>
-          <t>230-239</t>
-        </is>
-      </c>
       <c r="C128">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D128">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>220-229</t>
+          <t>230-239</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>240-249</t>
+          <t>230-239</t>
         </is>
       </c>
       <c r="C129">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="D129">
-        <v>3</v>
+        <v>8</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>220-229</t>
+          <t>230-239</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>250-259</t>
+          <t>240-249</t>
         </is>
       </c>
       <c r="C130">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D130">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>220-229</t>
+          <t>230-239</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>330-339</t>
+          <t>250-259</t>
         </is>
       </c>
       <c r="C131">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D131">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>230-239</t>
+          <t>240-249</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>160-169</t>
+          <t>180-189</t>
         </is>
       </c>
       <c r="C132">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D132">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>230-239</t>
+          <t>240-249</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>170-179</t>
+          <t>190-199</t>
         </is>
       </c>
       <c r="C133">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D133">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>230-239</t>
+          <t>240-249</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>180-189</t>
+          <t>200-209</t>
         </is>
       </c>
       <c r="C134">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D134">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>230-239</t>
+          <t>240-249</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>190-199</t>
+          <t>210-219</t>
         </is>
       </c>
       <c r="C135">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="D135">
-        <v>5</v>
+        <v>16</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>230-239</t>
+          <t>240-249</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>200-209</t>
+          <t>220-229</t>
         </is>
       </c>
       <c r="C136">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="D136">
-        <v>10</v>
+        <v>15</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
+          <t>240-249</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
           <t>230-239</t>
         </is>
       </c>
-      <c r="B137" t="inlineStr">
-        <is>
-          <t>210-219</t>
-        </is>
-      </c>
       <c r="C137">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="D137">
-        <v>20</v>
+        <v>10</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>230-239</t>
+          <t>240-249</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>220-229</t>
+          <t>240-249</t>
         </is>
       </c>
       <c r="C138">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="D138">
-        <v>8</v>
+        <v>2</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>230-239</t>
+          <t>240-249</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>230-239</t>
+          <t>250-259</t>
         </is>
       </c>
       <c r="C139">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="D139">
-        <v>8</v>
+        <v>3</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>230-239</t>
+          <t>240-249</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>240-249</t>
+          <t>260-269</t>
         </is>
       </c>
       <c r="C140">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D140">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>230-239</t>
+          <t>240-249</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>250-259</t>
+          <t>280-289</t>
         </is>
       </c>
       <c r="C141">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D141">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>240-249</t>
+          <t>250-259</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>180-189</t>
+          <t>190-199</t>
         </is>
       </c>
       <c r="C142">
@@ -2917,120 +2917,120 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>240-249</t>
+          <t>250-259</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>190-199</t>
+          <t>200-209</t>
         </is>
       </c>
       <c r="C143">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D143">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>240-249</t>
+          <t>250-259</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>200-209</t>
+          <t>210-219</t>
         </is>
       </c>
       <c r="C144">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D144">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>240-249</t>
+          <t>250-259</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>210-219</t>
+          <t>220-229</t>
         </is>
       </c>
       <c r="C145">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="D145">
-        <v>16</v>
+        <v>13</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>240-249</t>
+          <t>250-259</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>220-229</t>
+          <t>230-239</t>
         </is>
       </c>
       <c r="C146">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="D146">
-        <v>15</v>
+        <v>6</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
+          <t>250-259</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
           <t>240-249</t>
         </is>
       </c>
-      <c r="B147" t="inlineStr">
-        <is>
-          <t>230-239</t>
-        </is>
-      </c>
       <c r="C147">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D147">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>240-249</t>
+          <t>250-259</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>240-249</t>
+          <t>250-259</t>
         </is>
       </c>
       <c r="C148">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D148">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>240-249</t>
+          <t>250-259</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>250-259</t>
+          <t>260-269</t>
         </is>
       </c>
       <c r="C149">
@@ -3043,25 +3043,25 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>240-249</t>
+          <t>250-259</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>260-269</t>
+          <t>270-279</t>
         </is>
       </c>
       <c r="C150">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D150">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>240-249</t>
+          <t>250-259</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -3070,21 +3070,21 @@
         </is>
       </c>
       <c r="C151">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D151">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>250-259</t>
+          <t>260-269</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>190-199</t>
+          <t>170-179</t>
         </is>
       </c>
       <c r="C152">
@@ -3097,30 +3097,30 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>250-259</t>
+          <t>260-269</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>200-209</t>
+          <t>210-219</t>
         </is>
       </c>
       <c r="C153">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D153">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>250-259</t>
+          <t>260-269</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>210-219</t>
+          <t>220-229</t>
         </is>
       </c>
       <c r="C154">
@@ -3133,156 +3133,156 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>250-259</t>
+          <t>260-269</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>220-229</t>
+          <t>230-239</t>
         </is>
       </c>
       <c r="C155">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="D155">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>250-259</t>
+          <t>260-269</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>230-239</t>
+          <t>240-249</t>
         </is>
       </c>
       <c r="C156">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="D156">
-        <v>6</v>
+        <v>9</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
+          <t>260-269</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
           <t>250-259</t>
         </is>
       </c>
-      <c r="B157" t="inlineStr">
-        <is>
-          <t>240-249</t>
-        </is>
-      </c>
       <c r="C157">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D157">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>250-259</t>
+          <t>260-269</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>250-259</t>
+          <t>260-269</t>
         </is>
       </c>
       <c r="C158">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D158">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>250-259</t>
+          <t>260-269</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>260-269</t>
+          <t>270-279</t>
         </is>
       </c>
       <c r="C159">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D159">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>250-259</t>
+          <t>270-279</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>270-279</t>
+          <t>200-209</t>
         </is>
       </c>
       <c r="C160">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D160">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>250-259</t>
+          <t>270-279</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>280-289</t>
+          <t>210-219</t>
         </is>
       </c>
       <c r="C161">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D161">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>260-269</t>
+          <t>270-279</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>170-179</t>
+          <t>220-229</t>
         </is>
       </c>
       <c r="C162">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="D162">
-        <v>1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>260-269</t>
+          <t>270-279</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>210-219</t>
+          <t>230-239</t>
         </is>
       </c>
       <c r="C163">
@@ -3295,12 +3295,12 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>260-269</t>
+          <t>270-279</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>220-229</t>
+          <t>240-249</t>
         </is>
       </c>
       <c r="C164">
@@ -3313,84 +3313,84 @@
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>260-269</t>
+          <t>270-279</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>230-239</t>
+          <t>250-259</t>
         </is>
       </c>
       <c r="C165">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="D165">
-        <v>15</v>
+        <v>4</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
+          <t>270-279</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
           <t>260-269</t>
         </is>
       </c>
-      <c r="B166" t="inlineStr">
-        <is>
-          <t>240-249</t>
-        </is>
-      </c>
       <c r="C166">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D166">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>260-269</t>
+          <t>270-279</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>250-259</t>
+          <t>270-279</t>
         </is>
       </c>
       <c r="C167">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D167">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>260-269</t>
+          <t>270-279</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>260-269</t>
+          <t>290-299</t>
         </is>
       </c>
       <c r="C168">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D168">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>260-269</t>
+          <t>270-279</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>270-279</t>
+          <t>300-309</t>
         </is>
       </c>
       <c r="C169">
@@ -3408,146 +3408,146 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>200-209</t>
+          <t>330-339</t>
         </is>
       </c>
       <c r="C170">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D170">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>270-279</t>
+          <t>280-289</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>210-219</t>
+          <t>220-229</t>
         </is>
       </c>
       <c r="C171">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D171">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>270-279</t>
+          <t>280-289</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>220-229</t>
+          <t>230-239</t>
         </is>
       </c>
       <c r="C172">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="D172">
-        <v>8</v>
+        <v>2</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>270-279</t>
+          <t>280-289</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>230-239</t>
+          <t>240-249</t>
         </is>
       </c>
       <c r="C173">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="D173">
-        <v>3</v>
+        <v>8</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>270-279</t>
+          <t>280-289</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>240-249</t>
+          <t>250-259</t>
         </is>
       </c>
       <c r="C174">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D174">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>270-279</t>
+          <t>280-289</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>250-259</t>
+          <t>260-269</t>
         </is>
       </c>
       <c r="C175">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D175">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
+          <t>280-289</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
           <t>270-279</t>
         </is>
       </c>
-      <c r="B176" t="inlineStr">
-        <is>
-          <t>260-269</t>
-        </is>
-      </c>
       <c r="C176">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="D176">
-        <v>7</v>
+        <v>3</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>270-279</t>
+          <t>280-289</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>270-279</t>
+          <t>280-289</t>
         </is>
       </c>
       <c r="C177">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D177">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>270-279</t>
+          <t>280-289</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -3556,21 +3556,21 @@
         </is>
       </c>
       <c r="C178">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D178">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>270-279</t>
+          <t>290-299</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>300-309</t>
+          <t>220-229</t>
         </is>
       </c>
       <c r="C179">
@@ -3583,30 +3583,30 @@
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>270-279</t>
+          <t>290-299</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>330-339</t>
+          <t>230-239</t>
         </is>
       </c>
       <c r="C180">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D180">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>280-289</t>
+          <t>290-299</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>220-229</t>
+          <t>240-249</t>
         </is>
       </c>
       <c r="C181">
@@ -3619,12 +3619,12 @@
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>280-289</t>
+          <t>290-299</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>230-239</t>
+          <t>250-259</t>
         </is>
       </c>
       <c r="C182">
@@ -3637,120 +3637,120 @@
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>280-289</t>
+          <t>290-299</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>240-249</t>
+          <t>260-269</t>
         </is>
       </c>
       <c r="C183">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="D183">
-        <v>8</v>
+        <v>2</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>280-289</t>
+          <t>290-299</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>250-259</t>
+          <t>270-279</t>
         </is>
       </c>
       <c r="C184">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D184">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
+          <t>290-299</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
           <t>280-289</t>
         </is>
       </c>
-      <c r="B185" t="inlineStr">
-        <is>
-          <t>260-269</t>
-        </is>
-      </c>
       <c r="C185">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="D185">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>280-289</t>
+          <t>290-299</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>270-279</t>
+          <t>290-299</t>
         </is>
       </c>
       <c r="C186">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D186">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>280-289</t>
+          <t>30-39</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>280-289</t>
+          <t>20-29</t>
         </is>
       </c>
       <c r="C187">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D187">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>280-289</t>
+          <t>30-39</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>290-299</t>
+          <t>30-39</t>
         </is>
       </c>
       <c r="C188">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D188">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>290-299</t>
+          <t>30-39</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>220-229</t>
+          <t>40-49</t>
         </is>
       </c>
       <c r="C189">
@@ -3763,30 +3763,30 @@
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>290-299</t>
+          <t>300-309</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>230-239</t>
+          <t>220-229</t>
         </is>
       </c>
       <c r="C190">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D190">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>290-299</t>
+          <t>300-309</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>240-249</t>
+          <t>230-239</t>
         </is>
       </c>
       <c r="C191">
@@ -3799,30 +3799,30 @@
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>290-299</t>
+          <t>300-309</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>250-259</t>
+          <t>240-249</t>
         </is>
       </c>
       <c r="C192">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D192">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>290-299</t>
+          <t>300-309</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>260-269</t>
+          <t>250-259</t>
         </is>
       </c>
       <c r="C193">
@@ -3835,55 +3835,55 @@
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>290-299</t>
+          <t>300-309</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>270-279</t>
+          <t>260-269</t>
         </is>
       </c>
       <c r="C194">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D194">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>290-299</t>
+          <t>300-309</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>280-289</t>
+          <t>270-279</t>
         </is>
       </c>
       <c r="C195">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D195">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>290-299</t>
+          <t>300-309</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>290-299</t>
+          <t>280-289</t>
         </is>
       </c>
       <c r="C196">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="D196">
-        <v>1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="197">
@@ -3894,7 +3894,7 @@
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>220-229</t>
+          <t>290-299</t>
         </is>
       </c>
       <c r="C197">
@@ -3912,43 +3912,43 @@
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>230-239</t>
+          <t>300-309</t>
         </is>
       </c>
       <c r="C198">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D198">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>300-309</t>
+          <t>310-319</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>240-249</t>
+          <t>250-259</t>
         </is>
       </c>
       <c r="C199">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D199">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>300-309</t>
+          <t>310-319</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>250-259</t>
+          <t>260-269</t>
         </is>
       </c>
       <c r="C200">
@@ -3961,12 +3961,12 @@
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>300-309</t>
+          <t>310-319</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>260-269</t>
+          <t>270-279</t>
         </is>
       </c>
       <c r="C201">
@@ -3979,66 +3979,66 @@
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>300-309</t>
+          <t>310-319</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>270-279</t>
+          <t>280-289</t>
         </is>
       </c>
       <c r="C202">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D202">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>300-309</t>
+          <t>310-319</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>280-289</t>
+          <t>290-299</t>
         </is>
       </c>
       <c r="C203">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D203">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
+          <t>310-319</t>
+        </is>
+      </c>
+      <c r="B204" t="inlineStr">
+        <is>
           <t>300-309</t>
         </is>
       </c>
-      <c r="B204" t="inlineStr">
-        <is>
-          <t>290-299</t>
-        </is>
-      </c>
       <c r="C204">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D204">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>300-309</t>
+          <t>310-319</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>300-309</t>
+          <t>310-319</t>
         </is>
       </c>
       <c r="C205">
@@ -4056,14 +4056,14 @@
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>250-259</t>
+          <t>320-329</t>
         </is>
       </c>
       <c r="C206">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D206">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="207">
@@ -4074,140 +4074,140 @@
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>260-269</t>
+          <t>330-339</t>
         </is>
       </c>
       <c r="C207">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D207">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>310-319</t>
+          <t>320-329</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>270-279</t>
+          <t>240-249</t>
         </is>
       </c>
       <c r="C208">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D208">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>310-319</t>
+          <t>320-329</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>280-289</t>
+          <t>260-269</t>
         </is>
       </c>
       <c r="C209">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D209">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>310-319</t>
+          <t>320-329</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>290-299</t>
+          <t>270-279</t>
         </is>
       </c>
       <c r="C210">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D210">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>310-319</t>
+          <t>320-329</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>300-309</t>
+          <t>280-289</t>
         </is>
       </c>
       <c r="C211">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D211">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>310-319</t>
+          <t>320-329</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>310-319</t>
+          <t>290-299</t>
         </is>
       </c>
       <c r="C212">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D212">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>310-319</t>
+          <t>320-329</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>320-329</t>
+          <t>300-309</t>
         </is>
       </c>
       <c r="C213">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D213">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
+          <t>320-329</t>
+        </is>
+      </c>
+      <c r="B214" t="inlineStr">
+        <is>
           <t>310-319</t>
         </is>
       </c>
-      <c r="B214" t="inlineStr">
-        <is>
-          <t>330-339</t>
-        </is>
-      </c>
       <c r="C214">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D214">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="215">
@@ -4218,14 +4218,14 @@
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>240-249</t>
+          <t>320-329</t>
         </is>
       </c>
       <c r="C215">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D215">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="216">
@@ -4236,14 +4236,14 @@
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>260-269</t>
+          <t>330-339</t>
         </is>
       </c>
       <c r="C216">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D216">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="217">
@@ -4254,140 +4254,140 @@
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>270-279</t>
+          <t>360-369</t>
         </is>
       </c>
       <c r="C217">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D217">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>320-329</t>
+          <t>330-339</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>280-289</t>
+          <t>250-259</t>
         </is>
       </c>
       <c r="C218">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D218">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>320-329</t>
+          <t>330-339</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>290-299</t>
+          <t>260-269</t>
         </is>
       </c>
       <c r="C219">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D219">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>320-329</t>
+          <t>330-339</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>300-309</t>
+          <t>270-279</t>
         </is>
       </c>
       <c r="C220">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D220">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>320-329</t>
+          <t>330-339</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>310-319</t>
+          <t>280-289</t>
         </is>
       </c>
       <c r="C221">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D221">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>320-329</t>
+          <t>330-339</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>320-329</t>
+          <t>290-299</t>
         </is>
       </c>
       <c r="C222">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="D222">
-        <v>1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>320-329</t>
+          <t>330-339</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>330-339</t>
+          <t>300-309</t>
         </is>
       </c>
       <c r="C223">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D223">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>320-329</t>
+          <t>330-339</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>360-369</t>
+          <t>310-319</t>
         </is>
       </c>
       <c r="C224">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D224">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="225">
@@ -4398,7 +4398,7 @@
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>250-259</t>
+          <t>320-329</t>
         </is>
       </c>
       <c r="C225">
@@ -4416,97 +4416,97 @@
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>260-269</t>
+          <t>380-389</t>
         </is>
       </c>
       <c r="C226">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D226">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>330-339</t>
+          <t>340-349</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>270-279</t>
+          <t>260-269</t>
         </is>
       </c>
       <c r="C227">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D227">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>330-339</t>
+          <t>340-349</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>280-289</t>
+          <t>270-279</t>
         </is>
       </c>
       <c r="C228">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D228">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>330-339</t>
+          <t>340-349</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>290-299</t>
+          <t>280-289</t>
         </is>
       </c>
       <c r="C229">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="D229">
-        <v>7</v>
+        <v>2</v>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>330-339</t>
+          <t>340-349</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>300-309</t>
+          <t>290-299</t>
         </is>
       </c>
       <c r="C230">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D230">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>330-339</t>
+          <t>340-349</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>310-319</t>
+          <t>300-309</t>
         </is>
       </c>
       <c r="C231">
@@ -4519,30 +4519,30 @@
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>330-339</t>
+          <t>340-349</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>320-329</t>
+          <t>310-319</t>
         </is>
       </c>
       <c r="C232">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D232">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>330-339</t>
+          <t>340-349</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>380-389</t>
+          <t>320-329</t>
         </is>
       </c>
       <c r="C233">
@@ -4560,7 +4560,7 @@
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>260-269</t>
+          <t>330-339</t>
         </is>
       </c>
       <c r="C234">
@@ -4573,7 +4573,7 @@
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>340-349</t>
+          <t>350-359</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
@@ -4582,16 +4582,16 @@
         </is>
       </c>
       <c r="C235">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D235">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>340-349</t>
+          <t>350-359</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
@@ -4609,7 +4609,7 @@
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>340-349</t>
+          <t>350-359</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
@@ -4618,16 +4618,16 @@
         </is>
       </c>
       <c r="C237">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D237">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>340-349</t>
+          <t>350-359</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
@@ -4636,16 +4636,16 @@
         </is>
       </c>
       <c r="C238">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="D238">
-        <v>3</v>
+        <v>7</v>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>340-349</t>
+          <t>350-359</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
@@ -4654,21 +4654,21 @@
         </is>
       </c>
       <c r="C239">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D239">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>340-349</t>
+          <t>350-359</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>320-329</t>
+          <t>330-339</t>
         </is>
       </c>
       <c r="C240">
@@ -4681,25 +4681,25 @@
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
+          <t>350-359</t>
+        </is>
+      </c>
+      <c r="B241" t="inlineStr">
+        <is>
           <t>340-349</t>
         </is>
       </c>
-      <c r="B241" t="inlineStr">
-        <is>
-          <t>330-339</t>
-        </is>
-      </c>
       <c r="C241">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D241">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>350-359</t>
+          <t>360-369</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
@@ -4708,16 +4708,16 @@
         </is>
       </c>
       <c r="C242">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D242">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>350-359</t>
+          <t>360-369</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
@@ -4735,7 +4735,7 @@
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>350-359</t>
+          <t>360-369</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
@@ -4744,16 +4744,16 @@
         </is>
       </c>
       <c r="C244">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D244">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>350-359</t>
+          <t>360-369</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
@@ -4762,16 +4762,16 @@
         </is>
       </c>
       <c r="C245">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="D245">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>350-359</t>
+          <t>360-369</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
@@ -4780,39 +4780,39 @@
         </is>
       </c>
       <c r="C246">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D246">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>350-359</t>
+          <t>360-369</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>330-339</t>
+          <t>320-329</t>
         </is>
       </c>
       <c r="C247">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D247">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>350-359</t>
+          <t>360-369</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>340-349</t>
+          <t>330-339</t>
         </is>
       </c>
       <c r="C248">
@@ -4830,7 +4830,7 @@
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>270-279</t>
+          <t>350-359</t>
         </is>
       </c>
       <c r="C249">
@@ -4848,14 +4848,14 @@
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>280-289</t>
+          <t>400-409</t>
         </is>
       </c>
       <c r="C250">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D250">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="251">
@@ -4866,7 +4866,7 @@
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>290-299</t>
+          <t>500+</t>
         </is>
       </c>
       <c r="C251">
@@ -4879,84 +4879,84 @@
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>360-369</t>
+          <t>370-379</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>300-309</t>
+          <t>270-279</t>
         </is>
       </c>
       <c r="C252">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D252">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>360-369</t>
+          <t>370-379</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>310-319</t>
+          <t>290-299</t>
         </is>
       </c>
       <c r="C253">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D253">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>360-369</t>
+          <t>370-379</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>320-329</t>
+          <t>300-309</t>
         </is>
       </c>
       <c r="C254">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D254">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>360-369</t>
+          <t>370-379</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>330-339</t>
+          <t>320-329</t>
         </is>
       </c>
       <c r="C255">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D255">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>360-369</t>
+          <t>370-379</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>350-359</t>
+          <t>330-339</t>
         </is>
       </c>
       <c r="C256">
@@ -4969,12 +4969,12 @@
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>360-369</t>
+          <t>370-379</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>400-409</t>
+          <t>350-359</t>
         </is>
       </c>
       <c r="C257">
@@ -4987,7 +4987,12 @@
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>360-369</t>
+          <t>370-379</t>
+        </is>
+      </c>
+      <c r="B258" t="inlineStr">
+        <is>
+          <t>410-419</t>
         </is>
       </c>
       <c r="C258">
@@ -5000,7 +5005,7 @@
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>370-379</t>
+          <t>380-389</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
@@ -5018,30 +5023,30 @@
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>370-379</t>
+          <t>380-389</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>290-299</t>
+          <t>310-319</t>
         </is>
       </c>
       <c r="C260">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D260">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>370-379</t>
+          <t>380-389</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>300-309</t>
+          <t>330-339</t>
         </is>
       </c>
       <c r="C261">
@@ -5054,30 +5059,30 @@
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>370-379</t>
+          <t>380-389</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>320-329</t>
+          <t>340-349</t>
         </is>
       </c>
       <c r="C262">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D262">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>370-379</t>
+          <t>390-399</t>
         </is>
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>330-339</t>
+          <t>310-319</t>
         </is>
       </c>
       <c r="C263">
@@ -5090,12 +5095,12 @@
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>370-379</t>
+          <t>390-399</t>
         </is>
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>350-359</t>
+          <t>320-329</t>
         </is>
       </c>
       <c r="C264">
@@ -5108,97 +5113,97 @@
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>370-379</t>
+          <t>390-399</t>
         </is>
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>410-419</t>
+          <t>330-339</t>
         </is>
       </c>
       <c r="C265">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D265">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>380-389</t>
+          <t>390-399</t>
         </is>
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>270-279</t>
+          <t>340-349</t>
         </is>
       </c>
       <c r="C266">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D266">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>380-389</t>
+          <t>390-399</t>
         </is>
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>310-319</t>
+          <t>360-369</t>
         </is>
       </c>
       <c r="C267">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D267">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>380-389</t>
+          <t>390-399</t>
         </is>
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>330-339</t>
+          <t>390-399</t>
         </is>
       </c>
       <c r="C268">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D268">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>380-389</t>
+          <t>400-409</t>
         </is>
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>340-349</t>
+          <t>300-309</t>
         </is>
       </c>
       <c r="C269">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D269">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>390-399</t>
+          <t>400-409</t>
         </is>
       </c>
       <c r="B270" t="inlineStr">
@@ -5216,66 +5221,66 @@
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>390-399</t>
+          <t>400-409</t>
         </is>
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>320-329</t>
+          <t>330-339</t>
         </is>
       </c>
       <c r="C271">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D271">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>390-399</t>
+          <t>400-409</t>
         </is>
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>330-339</t>
+          <t>340-349</t>
         </is>
       </c>
       <c r="C272">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D272">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>390-399</t>
+          <t>400-409</t>
         </is>
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>340-349</t>
+          <t>360-369</t>
         </is>
       </c>
       <c r="C273">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D273">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>390-399</t>
+          <t>400-409</t>
         </is>
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>360-369</t>
+          <t>370-379</t>
         </is>
       </c>
       <c r="C274">
@@ -5288,48 +5293,48 @@
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>390-399</t>
+          <t>410-419</t>
         </is>
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>390-399</t>
+          <t>310-319</t>
         </is>
       </c>
       <c r="C275">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D275">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>400-409</t>
+          <t>410-419</t>
         </is>
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>300-309</t>
+          <t>330-339</t>
         </is>
       </c>
       <c r="C276">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D276">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>400-409</t>
+          <t>410-419</t>
         </is>
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>310-319</t>
+          <t>340-349</t>
         </is>
       </c>
       <c r="C277">
@@ -5342,30 +5347,30 @@
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>400-409</t>
+          <t>410-419</t>
         </is>
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>330-339</t>
+          <t>350-359</t>
         </is>
       </c>
       <c r="C278">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D278">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>400-409</t>
+          <t>410-419</t>
         </is>
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>340-349</t>
+          <t>390-399</t>
         </is>
       </c>
       <c r="C279">
@@ -5378,12 +5383,12 @@
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>400-409</t>
+          <t>420-429</t>
         </is>
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>360-369</t>
+          <t>330-339</t>
         </is>
       </c>
       <c r="C280">
@@ -5396,30 +5401,30 @@
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>400-409</t>
+          <t>420-429</t>
         </is>
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>370-379</t>
+          <t>340-349</t>
         </is>
       </c>
       <c r="C281">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D281">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>410-419</t>
+          <t>420-429</t>
         </is>
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>310-319</t>
+          <t>350-359</t>
         </is>
       </c>
       <c r="C282">
@@ -5432,12 +5437,12 @@
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>410-419</t>
+          <t>420-429</t>
         </is>
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>330-339</t>
+          <t>370-379</t>
         </is>
       </c>
       <c r="C283">
@@ -5450,12 +5455,12 @@
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>410-419</t>
+          <t>430-439</t>
         </is>
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>340-349</t>
+          <t>360-369</t>
         </is>
       </c>
       <c r="C284">
@@ -5468,12 +5473,12 @@
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>410-419</t>
+          <t>430-439</t>
         </is>
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>350-359</t>
+          <t>380-389</t>
         </is>
       </c>
       <c r="C285">
@@ -5486,12 +5491,12 @@
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>410-419</t>
+          <t>440-449</t>
         </is>
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>390-399</t>
+          <t>360-369</t>
         </is>
       </c>
       <c r="C286">
@@ -5504,12 +5509,12 @@
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>420-429</t>
+          <t>450-459</t>
         </is>
       </c>
       <c r="B287" t="inlineStr">
         <is>
-          <t>330-339</t>
+          <t>340-349</t>
         </is>
       </c>
       <c r="C287">
@@ -5522,12 +5527,12 @@
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>420-429</t>
+          <t>450-459</t>
         </is>
       </c>
       <c r="B288" t="inlineStr">
         <is>
-          <t>340-349</t>
+          <t>350-359</t>
         </is>
       </c>
       <c r="C288">
@@ -5540,12 +5545,12 @@
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>420-429</t>
+          <t>450-459</t>
         </is>
       </c>
       <c r="B289" t="inlineStr">
         <is>
-          <t>350-359</t>
+          <t>360-369</t>
         </is>
       </c>
       <c r="C289">
@@ -5558,12 +5563,12 @@
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>420-429</t>
+          <t>450-459</t>
         </is>
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>370-379</t>
+          <t>380-389</t>
         </is>
       </c>
       <c r="C290">
@@ -5576,12 +5581,12 @@
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>430-439</t>
+          <t>450-459</t>
         </is>
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>360-369</t>
+          <t>440-449</t>
         </is>
       </c>
       <c r="C291">
@@ -5594,12 +5599,12 @@
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>430-439</t>
+          <t>460-469</t>
         </is>
       </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t>380-389</t>
+          <t>370-379</t>
         </is>
       </c>
       <c r="C292">
@@ -5612,12 +5617,12 @@
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>440-449</t>
+          <t>460-469</t>
         </is>
       </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t>360-369</t>
+          <t>390-399</t>
         </is>
       </c>
       <c r="C293">
@@ -5630,12 +5635,12 @@
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>450-459</t>
+          <t>470-479</t>
         </is>
       </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t>340-349</t>
+          <t>440-449</t>
         </is>
       </c>
       <c r="C294">
@@ -5648,48 +5653,48 @@
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>450-459</t>
+          <t>490-499</t>
         </is>
       </c>
       <c r="B295" t="inlineStr">
         <is>
-          <t>350-359</t>
+          <t>380-389</t>
         </is>
       </c>
       <c r="C295">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D295">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>450-459</t>
+          <t>500+</t>
         </is>
       </c>
       <c r="B296" t="inlineStr">
         <is>
-          <t>360-369</t>
+          <t>380-389</t>
         </is>
       </c>
       <c r="C296">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D296">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>450-459</t>
+          <t>500+</t>
         </is>
       </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t>380-389</t>
+          <t>430-439</t>
         </is>
       </c>
       <c r="C297">
@@ -5702,12 +5707,12 @@
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>450-459</t>
+          <t>500+</t>
         </is>
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>440-449</t>
+          <t>460-469</t>
         </is>
       </c>
       <c r="C298">
@@ -5720,12 +5725,12 @@
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>460-469</t>
+          <t>500+</t>
         </is>
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>370-379</t>
+          <t>480-489</t>
         </is>
       </c>
       <c r="C299">
@@ -5738,30 +5743,30 @@
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>460-469</t>
+          <t>500+</t>
         </is>
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>390-399</t>
+          <t>500+</t>
         </is>
       </c>
       <c r="C300">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="D300">
-        <v>1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t>470-479</t>
+          <t>60-69</t>
         </is>
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>440-449</t>
+          <t>130-139</t>
         </is>
       </c>
       <c r="C301">
@@ -5774,12 +5779,12 @@
     <row r="302">
       <c r="A302" t="inlineStr">
         <is>
-          <t>490-499</t>
+          <t>80-89</t>
         </is>
       </c>
       <c r="B302" t="inlineStr">
         <is>
-          <t>380-389</t>
+          <t>110-119</t>
         </is>
       </c>
       <c r="C302">
@@ -5790,9 +5795,14 @@
       </c>
     </row>
     <row r="303">
+      <c r="A303" t="inlineStr">
+        <is>
+          <t>80-89</t>
+        </is>
+      </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>380-389</t>
+          <t>140-149</t>
         </is>
       </c>
       <c r="C303">
@@ -5803,9 +5813,14 @@
       </c>
     </row>
     <row r="304">
+      <c r="A304" t="inlineStr">
+        <is>
+          <t>90-99</t>
+        </is>
+      </c>
       <c r="B304" t="inlineStr">
         <is>
-          <t>430-439</t>
+          <t>100-109</t>
         </is>
       </c>
       <c r="C304">
@@ -5816,37 +5831,65 @@
       </c>
     </row>
     <row r="305">
+      <c r="A305" t="inlineStr">
+        <is>
+          <t>90-99</t>
+        </is>
+      </c>
       <c r="B305" t="inlineStr">
         <is>
-          <t>460-469</t>
+          <t>120-129</t>
         </is>
       </c>
       <c r="C305">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D305">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="306">
+      <c r="A306" t="inlineStr">
+        <is>
+          <t>90-99</t>
+        </is>
+      </c>
       <c r="B306" t="inlineStr">
         <is>
-          <t>480-489</t>
+          <t>130-139</t>
         </is>
       </c>
       <c r="C306">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D306">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="307">
+      <c r="A307" t="inlineStr">
+        <is>
+          <t>90-99</t>
+        </is>
+      </c>
+      <c r="B307" t="inlineStr">
+        <is>
+          <t>140-149</t>
+        </is>
+      </c>
       <c r="C307">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="D307">
-        <v>8</v>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="308">
+      <c r="C308">
+        <v>1</v>
+      </c>
+      <c r="D308">
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/const/Binned_Summary.xlsx
+++ b/const/Binned_Summary.xlsx
@@ -351,50 +351,65 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C51"/>
+  <dimension ref="A1:D298"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Bin</t>
+          <t>Registered Bin</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Count_Registered_Bin</t>
+          <t>Weighted Bin</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>Count_Weighted_Bin</t>
+          <t>Count_Registered_Practices</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Count_Weighted_Practices</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>0-9</t>
-        </is>
-      </c>
-      <c r="B2">
-        <v>3</v>
+          <t>90-99</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>120-129</t>
+        </is>
       </c>
       <c r="C2">
-        <v>3</v>
+        <v>1</v>
+      </c>
+      <c r="D2">
+        <v>1</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>10-19</t>
-        </is>
-      </c>
-      <c r="B3">
-        <v>2</v>
+          <t>100-109</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>80-89</t>
+        </is>
       </c>
       <c r="C3">
-        <v>2</v>
+        <v>1</v>
+      </c>
+      <c r="D3">
+        <v>1</v>
       </c>
     </row>
     <row r="4">
@@ -403,616 +418,5302 @@
           <t>100-109</t>
         </is>
       </c>
-      <c r="B4">
-        <v>32</v>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>100-109</t>
+        </is>
       </c>
       <c r="C4">
-        <v>7</v>
+        <v>2</v>
+      </c>
+      <c r="D4">
+        <v>2</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>100-109</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
           <t>110-119</t>
         </is>
       </c>
-      <c r="B5">
-        <v>144</v>
-      </c>
       <c r="C5">
-        <v>11</v>
+        <v>3</v>
+      </c>
+      <c r="D5">
+        <v>3</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>100-109</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
           <t>120-129</t>
         </is>
       </c>
-      <c r="B6">
-        <v>337</v>
-      </c>
       <c r="C6">
-        <v>148</v>
+        <v>14</v>
+      </c>
+      <c r="D6">
+        <v>14</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>100-109</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
           <t>130-139</t>
         </is>
       </c>
-      <c r="B7">
-        <v>702</v>
-      </c>
       <c r="C7">
-        <v>646</v>
+        <v>11</v>
+      </c>
+      <c r="D7">
+        <v>11</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>100-109</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
           <t>140-149</t>
         </is>
       </c>
-      <c r="B8">
-        <v>871</v>
-      </c>
       <c r="C8">
-        <v>1179</v>
+        <v>3</v>
+      </c>
+      <c r="D8">
+        <v>3</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
+          <t>100-109</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
           <t>150-159</t>
         </is>
       </c>
-      <c r="B9">
-        <v>920</v>
-      </c>
       <c r="C9">
-        <v>1235</v>
+        <v>1</v>
+      </c>
+      <c r="D9">
+        <v>1</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>160-169</t>
-        </is>
-      </c>
-      <c r="B10">
-        <v>778</v>
+          <t>110-119</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>100-109</t>
+        </is>
       </c>
       <c r="C10">
-        <v>870</v>
+        <v>2</v>
+      </c>
+      <c r="D10">
+        <v>2</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>170-179</t>
-        </is>
-      </c>
-      <c r="B11">
-        <v>545</v>
+          <t>110-119</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>110-119</t>
+        </is>
       </c>
       <c r="C11">
-        <v>497</v>
+        <v>4</v>
+      </c>
+      <c r="D11">
+        <v>4</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>180-189</t>
-        </is>
-      </c>
-      <c r="B12">
-        <v>324</v>
+          <t>110-119</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>120-129</t>
+        </is>
       </c>
       <c r="C12">
-        <v>268</v>
+        <v>47</v>
+      </c>
+      <c r="D12">
+        <v>47</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>190-199</t>
-        </is>
-      </c>
-      <c r="B13">
-        <v>227</v>
+          <t>110-119</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>130-139</t>
+        </is>
       </c>
       <c r="C13">
-        <v>177</v>
+        <v>76</v>
+      </c>
+      <c r="D13">
+        <v>76</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>20-29</t>
-        </is>
-      </c>
-      <c r="B14">
-        <v>0</v>
+          <t>110-119</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>140-149</t>
+        </is>
       </c>
       <c r="C14">
-        <v>1</v>
+        <v>35</v>
+      </c>
+      <c r="D14">
+        <v>35</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>200-209</t>
-        </is>
-      </c>
-      <c r="B15">
-        <v>149</v>
+          <t>110-119</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>150-159</t>
+        </is>
       </c>
       <c r="C15">
-        <v>125</v>
+        <v>3</v>
+      </c>
+      <c r="D15">
+        <v>3</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>210-219</t>
-        </is>
-      </c>
-      <c r="B16">
-        <v>115</v>
+          <t>110-119</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>160-169</t>
+        </is>
       </c>
       <c r="C16">
-        <v>103</v>
+        <v>2</v>
+      </c>
+      <c r="D16">
+        <v>2</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>220-229</t>
-        </is>
-      </c>
-      <c r="B17">
-        <v>78</v>
+          <t>120-129</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>100-109</t>
+        </is>
       </c>
       <c r="C17">
-        <v>86</v>
+        <v>1</v>
+      </c>
+      <c r="D17">
+        <v>1</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>230-239</t>
-        </is>
-      </c>
-      <c r="B18">
-        <v>63</v>
+          <t>120-129</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>110-119</t>
+        </is>
       </c>
       <c r="C18">
-        <v>68</v>
+        <v>4</v>
+      </c>
+      <c r="D18">
+        <v>4</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>240-249</t>
-        </is>
-      </c>
-      <c r="B19">
-        <v>58</v>
+          <t>120-129</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>120-129</t>
+        </is>
       </c>
       <c r="C19">
-        <v>52</v>
+        <v>56</v>
+      </c>
+      <c r="D19">
+        <v>56</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>250-259</t>
-        </is>
-      </c>
-      <c r="B20">
-        <v>48</v>
+          <t>120-129</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>130-139</t>
+        </is>
       </c>
       <c r="C20">
-        <v>33</v>
+        <v>148</v>
+      </c>
+      <c r="D20">
+        <v>148</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>260-269</t>
-        </is>
-      </c>
-      <c r="B21">
-        <v>45</v>
+          <t>120-129</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>140-149</t>
+        </is>
       </c>
       <c r="C21">
-        <v>35</v>
+        <v>112</v>
+      </c>
+      <c r="D21">
+        <v>112</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>270-279</t>
-        </is>
-      </c>
-      <c r="B22">
-        <v>39</v>
+          <t>120-129</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>150-159</t>
+        </is>
       </c>
       <c r="C22">
-        <v>34</v>
+        <v>37</v>
+      </c>
+      <c r="D22">
+        <v>37</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>280-289</t>
-        </is>
-      </c>
-      <c r="B23">
-        <v>34</v>
+          <t>120-129</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>160-169</t>
+        </is>
       </c>
       <c r="C23">
-        <v>41</v>
+        <v>10</v>
+      </c>
+      <c r="D23">
+        <v>10</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>290-299</t>
-        </is>
-      </c>
-      <c r="B24">
-        <v>22</v>
+          <t>120-129</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>170-179</t>
+        </is>
       </c>
       <c r="C24">
-        <v>36</v>
+        <v>2</v>
+      </c>
+      <c r="D24">
+        <v>2</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>30-39</t>
-        </is>
-      </c>
-      <c r="B25">
-        <v>3</v>
+          <t>130-139</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>100-109</t>
+        </is>
       </c>
       <c r="C25">
+        <v>1</v>
+      </c>
+      <c r="D25">
         <v>1</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>300-309</t>
-        </is>
-      </c>
-      <c r="B26">
-        <v>26</v>
+          <t>130-139</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>110-119</t>
+        </is>
       </c>
       <c r="C26">
-        <v>33</v>
+        <v>1</v>
+      </c>
+      <c r="D26">
+        <v>1</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>310-319</t>
-        </is>
-      </c>
-      <c r="B27">
-        <v>26</v>
+          <t>130-139</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>120-129</t>
+        </is>
       </c>
       <c r="C27">
-        <v>29</v>
+        <v>30</v>
+      </c>
+      <c r="D27">
+        <v>30</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>320-329</t>
-        </is>
-      </c>
-      <c r="B28">
-        <v>30</v>
+          <t>130-139</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>130-139</t>
+        </is>
       </c>
       <c r="C28">
-        <v>13</v>
+        <v>206</v>
+      </c>
+      <c r="D28">
+        <v>206</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>330-339</t>
-        </is>
-      </c>
-      <c r="B29">
-        <v>29</v>
+          <t>130-139</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>140-149</t>
+        </is>
       </c>
       <c r="C29">
-        <v>17</v>
+        <v>311</v>
+      </c>
+      <c r="D29">
+        <v>311</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>340-349</t>
-        </is>
-      </c>
-      <c r="B30">
-        <v>24</v>
+          <t>130-139</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>150-159</t>
+        </is>
       </c>
       <c r="C30">
-        <v>12</v>
+        <v>158</v>
+      </c>
+      <c r="D30">
+        <v>158</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>350-359</t>
-        </is>
-      </c>
-      <c r="B31">
-        <v>23</v>
+          <t>130-139</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>160-169</t>
+        </is>
       </c>
       <c r="C31">
-        <v>7</v>
+        <v>46</v>
+      </c>
+      <c r="D31">
+        <v>46</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>360-369</t>
-        </is>
-      </c>
-      <c r="B32">
-        <v>20</v>
+          <t>130-139</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>170-179</t>
+        </is>
       </c>
       <c r="C32">
-        <v>7</v>
+        <v>3</v>
+      </c>
+      <c r="D32">
+        <v>3</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>370-379</t>
-        </is>
-      </c>
-      <c r="B33">
-        <v>12</v>
+          <t>130-139</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>180-189</t>
+        </is>
       </c>
       <c r="C33">
-        <v>3</v>
+        <v>2</v>
+      </c>
+      <c r="D33">
+        <v>2</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>380-389</t>
-        </is>
-      </c>
-      <c r="B34">
-        <v>9</v>
+          <t>130-139</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>200-209</t>
+        </is>
       </c>
       <c r="C34">
-        <v>5</v>
+        <v>3</v>
+      </c>
+      <c r="D34">
+        <v>3</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>390-399</t>
-        </is>
-      </c>
-      <c r="B35">
-        <v>8</v>
+          <t>140-149</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>110-119</t>
+        </is>
       </c>
       <c r="C35">
-        <v>3</v>
+        <v>2</v>
+      </c>
+      <c r="D35">
+        <v>2</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>40-49</t>
-        </is>
-      </c>
-      <c r="B36">
-        <v>0</v>
+          <t>140-149</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>120-129</t>
+        </is>
       </c>
       <c r="C36">
-        <v>1</v>
+        <v>15</v>
+      </c>
+      <c r="D36">
+        <v>15</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>400-409</t>
-        </is>
-      </c>
-      <c r="B37">
-        <v>8</v>
+          <t>140-149</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>130-139</t>
+        </is>
       </c>
       <c r="C37">
-        <v>1</v>
+        <v>138</v>
+      </c>
+      <c r="D37">
+        <v>138</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>410-419</t>
-        </is>
-      </c>
-      <c r="B38">
-        <v>6</v>
+          <t>140-149</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>140-149</t>
+        </is>
       </c>
       <c r="C38">
-        <v>1</v>
+        <v>321</v>
+      </c>
+      <c r="D38">
+        <v>321</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>420-429</t>
-        </is>
-      </c>
-      <c r="B39">
-        <v>6</v>
+          <t>140-149</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>150-159</t>
+        </is>
       </c>
       <c r="C39">
-        <v>0</v>
+        <v>332</v>
+      </c>
+      <c r="D39">
+        <v>332</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>430-439</t>
-        </is>
-      </c>
-      <c r="B40">
-        <v>2</v>
+          <t>140-149</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>160-169</t>
+        </is>
       </c>
       <c r="C40">
-        <v>1</v>
+        <v>104</v>
+      </c>
+      <c r="D40">
+        <v>104</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>440-449</t>
-        </is>
-      </c>
-      <c r="B41">
-        <v>1</v>
+          <t>140-149</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>170-179</t>
+        </is>
       </c>
       <c r="C41">
-        <v>2</v>
+        <v>26</v>
+      </c>
+      <c r="D41">
+        <v>26</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>450-459</t>
-        </is>
-      </c>
-      <c r="B42">
-        <v>7</v>
+          <t>140-149</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>180-189</t>
+        </is>
       </c>
       <c r="C42">
-        <v>0</v>
+        <v>4</v>
+      </c>
+      <c r="D42">
+        <v>4</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>460-469</t>
-        </is>
-      </c>
-      <c r="B43">
-        <v>2</v>
+          <t>140-149</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>190-199</t>
+        </is>
       </c>
       <c r="C43">
+        <v>1</v>
+      </c>
+      <c r="D43">
         <v>1</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>470-479</t>
-        </is>
-      </c>
-      <c r="B44">
-        <v>1</v>
+          <t>150-159</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>120-129</t>
+        </is>
       </c>
       <c r="C44">
-        <v>0</v>
+        <v>8</v>
+      </c>
+      <c r="D44">
+        <v>8</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>480-489</t>
-        </is>
-      </c>
-      <c r="B45">
-        <v>0</v>
+          <t>150-159</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>130-139</t>
+        </is>
       </c>
       <c r="C45">
-        <v>1</v>
+        <v>76</v>
+      </c>
+      <c r="D45">
+        <v>76</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>490-499</t>
-        </is>
-      </c>
-      <c r="B46">
-        <v>1</v>
+          <t>150-159</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>140-149</t>
+        </is>
       </c>
       <c r="C46">
-        <v>0</v>
+        <v>265</v>
+      </c>
+      <c r="D46">
+        <v>265</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>500+</t>
-        </is>
-      </c>
-      <c r="B47">
-        <v>11</v>
+          <t>150-159</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>150-159</t>
+        </is>
       </c>
       <c r="C47">
-        <v>8</v>
+        <v>318</v>
+      </c>
+      <c r="D47">
+        <v>318</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>60-69</t>
-        </is>
-      </c>
-      <c r="B48">
-        <v>1</v>
+          <t>150-159</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>160-169</t>
+        </is>
       </c>
       <c r="C48">
-        <v>0</v>
+        <v>213</v>
+      </c>
+      <c r="D48">
+        <v>213</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>80-89</t>
-        </is>
-      </c>
-      <c r="B49">
-        <v>2</v>
+          <t>150-159</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>170-179</t>
+        </is>
       </c>
       <c r="C49">
-        <v>1</v>
+        <v>75</v>
+      </c>
+      <c r="D49">
+        <v>75</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>90-99</t>
-        </is>
-      </c>
-      <c r="B50">
+          <t>150-159</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>180-189</t>
+        </is>
+      </c>
+      <c r="C50">
+        <v>18</v>
+      </c>
+      <c r="D50">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>150-159</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>190-199</t>
+        </is>
+      </c>
+      <c r="C51">
+        <v>1</v>
+      </c>
+      <c r="D51">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>150-159</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>220-229</t>
+        </is>
+      </c>
+      <c r="C52">
+        <v>1</v>
+      </c>
+      <c r="D52">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>160-169</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>130-139</t>
+        </is>
+      </c>
+      <c r="C53">
+        <v>24</v>
+      </c>
+      <c r="D53">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>160-169</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>140-149</t>
+        </is>
+      </c>
+      <c r="C54">
+        <v>151</v>
+      </c>
+      <c r="D54">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>160-169</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>150-159</t>
+        </is>
+      </c>
+      <c r="C55">
+        <v>272</v>
+      </c>
+      <c r="D55">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>160-169</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>160-169</t>
+        </is>
+      </c>
+      <c r="C56">
+        <v>218</v>
+      </c>
+      <c r="D56">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>160-169</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>170-179</t>
+        </is>
+      </c>
+      <c r="C57">
+        <v>119</v>
+      </c>
+      <c r="D57">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>160-169</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>180-189</t>
+        </is>
+      </c>
+      <c r="C58">
+        <v>36</v>
+      </c>
+      <c r="D58">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>160-169</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>190-199</t>
+        </is>
+      </c>
+      <c r="C59">
+        <v>9</v>
+      </c>
+      <c r="D59">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>160-169</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>200-209</t>
+        </is>
+      </c>
+      <c r="C60">
+        <v>2</v>
+      </c>
+      <c r="D60">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>160-169</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>220-229</t>
+        </is>
+      </c>
+      <c r="C61">
+        <v>2</v>
+      </c>
+      <c r="D61">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>170-179</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>130-139</t>
+        </is>
+      </c>
+      <c r="C62">
+        <v>11</v>
+      </c>
+      <c r="D62">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>170-179</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>140-149</t>
+        </is>
+      </c>
+      <c r="C63">
+        <v>44</v>
+      </c>
+      <c r="D63">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>170-179</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>150-159</t>
+        </is>
+      </c>
+      <c r="C64">
+        <v>140</v>
+      </c>
+      <c r="D64">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>170-179</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>160-169</t>
+        </is>
+      </c>
+      <c r="C65">
+        <v>176</v>
+      </c>
+      <c r="D65">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>170-179</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>170-179</t>
+        </is>
+      </c>
+      <c r="C66">
+        <v>130</v>
+      </c>
+      <c r="D66">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>170-179</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>180-189</t>
+        </is>
+      </c>
+      <c r="C67">
+        <v>60</v>
+      </c>
+      <c r="D67">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>170-179</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>190-199</t>
+        </is>
+      </c>
+      <c r="C68">
+        <v>20</v>
+      </c>
+      <c r="D68">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>170-179</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>200-209</t>
+        </is>
+      </c>
+      <c r="C69">
+        <v>3</v>
+      </c>
+      <c r="D69">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>170-179</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>220-229</t>
+        </is>
+      </c>
+      <c r="C70">
+        <v>1</v>
+      </c>
+      <c r="D70">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>180-189</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>130-139</t>
+        </is>
+      </c>
+      <c r="C71">
+        <v>1</v>
+      </c>
+      <c r="D71">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>180-189</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>140-149</t>
+        </is>
+      </c>
+      <c r="C72">
+        <v>19</v>
+      </c>
+      <c r="D72">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>180-189</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>150-159</t>
+        </is>
+      </c>
+      <c r="C73">
+        <v>45</v>
+      </c>
+      <c r="D73">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>180-189</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>160-169</t>
+        </is>
+      </c>
+      <c r="C74">
+        <v>93</v>
+      </c>
+      <c r="D74">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>180-189</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>170-179</t>
+        </is>
+      </c>
+      <c r="C75">
+        <v>83</v>
+      </c>
+      <c r="D75">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>180-189</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>180-189</t>
+        </is>
+      </c>
+      <c r="C76">
+        <v>57</v>
+      </c>
+      <c r="D76">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>180-189</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>190-199</t>
+        </is>
+      </c>
+      <c r="C77">
+        <v>33</v>
+      </c>
+      <c r="D77">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>180-189</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>200-209</t>
+        </is>
+      </c>
+      <c r="C78">
+        <v>12</v>
+      </c>
+      <c r="D78">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>180-189</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>210-219</t>
+        </is>
+      </c>
+      <c r="C79">
+        <v>3</v>
+      </c>
+      <c r="D79">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>180-189</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>220-229</t>
+        </is>
+      </c>
+      <c r="C80">
+        <v>2</v>
+      </c>
+      <c r="D80">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>180-189</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>240-249</t>
+        </is>
+      </c>
+      <c r="C81">
+        <v>1</v>
+      </c>
+      <c r="D81">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>180-189</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>250-259</t>
+        </is>
+      </c>
+      <c r="C82">
+        <v>1</v>
+      </c>
+      <c r="D82">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>190-199</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>140-149</t>
+        </is>
+      </c>
+      <c r="C83">
+        <v>3</v>
+      </c>
+      <c r="D83">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>190-199</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>150-159</t>
+        </is>
+      </c>
+      <c r="C84">
+        <v>16</v>
+      </c>
+      <c r="D84">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>190-199</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>160-169</t>
+        </is>
+      </c>
+      <c r="C85">
+        <v>41</v>
+      </c>
+      <c r="D85">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>190-199</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>170-179</t>
+        </is>
+      </c>
+      <c r="C86">
+        <v>51</v>
+      </c>
+      <c r="D86">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>190-199</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>180-189</t>
+        </is>
+      </c>
+      <c r="C87">
+        <v>52</v>
+      </c>
+      <c r="D87">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>190-199</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>190-199</t>
+        </is>
+      </c>
+      <c r="C88">
+        <v>42</v>
+      </c>
+      <c r="D88">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>190-199</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>200-209</t>
+        </is>
+      </c>
+      <c r="C89">
+        <v>20</v>
+      </c>
+      <c r="D89">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>190-199</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>210-219</t>
+        </is>
+      </c>
+      <c r="C90">
+        <v>9</v>
+      </c>
+      <c r="D90">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>190-199</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>220-229</t>
+        </is>
+      </c>
+      <c r="C91">
+        <v>2</v>
+      </c>
+      <c r="D91">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>190-199</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>230-239</t>
+        </is>
+      </c>
+      <c r="C92">
+        <v>2</v>
+      </c>
+      <c r="D92">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>200-209</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>150-159</t>
+        </is>
+      </c>
+      <c r="C93">
+        <v>6</v>
+      </c>
+      <c r="D93">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>200-209</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>160-169</t>
+        </is>
+      </c>
+      <c r="C94">
+        <v>17</v>
+      </c>
+      <c r="D94">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>200-209</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>170-179</t>
+        </is>
+      </c>
+      <c r="C95">
+        <v>29</v>
+      </c>
+      <c r="D95">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>200-209</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>180-189</t>
+        </is>
+      </c>
+      <c r="C96">
+        <v>27</v>
+      </c>
+      <c r="D96">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>200-209</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>190-199</t>
+        </is>
+      </c>
+      <c r="C97">
+        <v>38</v>
+      </c>
+      <c r="D97">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>200-209</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>200-209</t>
+        </is>
+      </c>
+      <c r="C98">
+        <v>26</v>
+      </c>
+      <c r="D98">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>200-209</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>210-219</t>
+        </is>
+      </c>
+      <c r="C99">
+        <v>11</v>
+      </c>
+      <c r="D99">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>200-209</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>220-229</t>
+        </is>
+      </c>
+      <c r="C100">
+        <v>3</v>
+      </c>
+      <c r="D100">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>200-209</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>230-239</t>
+        </is>
+      </c>
+      <c r="C101">
+        <v>2</v>
+      </c>
+      <c r="D101">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>210-219</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>150-159</t>
+        </is>
+      </c>
+      <c r="C102">
+        <v>2</v>
+      </c>
+      <c r="D102">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>210-219</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>160-169</t>
+        </is>
+      </c>
+      <c r="C103">
+        <v>8</v>
+      </c>
+      <c r="D103">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>210-219</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>170-179</t>
+        </is>
+      </c>
+      <c r="C104">
+        <v>8</v>
+      </c>
+      <c r="D104">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>210-219</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>180-189</t>
+        </is>
+      </c>
+      <c r="C105">
+        <v>15</v>
+      </c>
+      <c r="D105">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>210-219</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>190-199</t>
+        </is>
+      </c>
+      <c r="C106">
+        <v>27</v>
+      </c>
+      <c r="D106">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>210-219</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>200-209</t>
+        </is>
+      </c>
+      <c r="C107">
+        <v>29</v>
+      </c>
+      <c r="D107">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>210-219</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>210-219</t>
+        </is>
+      </c>
+      <c r="C108">
+        <v>18</v>
+      </c>
+      <c r="D108">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>210-219</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>220-229</t>
+        </is>
+      </c>
+      <c r="C109">
+        <v>9</v>
+      </c>
+      <c r="D109">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>210-219</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>230-239</t>
+        </is>
+      </c>
+      <c r="C110">
+        <v>8</v>
+      </c>
+      <c r="D110">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>210-219</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>240-249</t>
+        </is>
+      </c>
+      <c r="C111">
+        <v>2</v>
+      </c>
+      <c r="D111">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>220-229</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>170-179</t>
+        </is>
+      </c>
+      <c r="C112">
+        <v>3</v>
+      </c>
+      <c r="D112">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>220-229</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>180-189</t>
+        </is>
+      </c>
+      <c r="C113">
+        <v>9</v>
+      </c>
+      <c r="D113">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>220-229</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>190-199</t>
+        </is>
+      </c>
+      <c r="C114">
+        <v>13</v>
+      </c>
+      <c r="D114">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>220-229</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>200-209</t>
+        </is>
+      </c>
+      <c r="C115">
+        <v>18</v>
+      </c>
+      <c r="D115">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>220-229</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>210-219</t>
+        </is>
+      </c>
+      <c r="C116">
+        <v>16</v>
+      </c>
+      <c r="D116">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>220-229</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>220-229</t>
+        </is>
+      </c>
+      <c r="C117">
+        <v>12</v>
+      </c>
+      <c r="D117">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>220-229</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>230-239</t>
+        </is>
+      </c>
+      <c r="C118">
+        <v>9</v>
+      </c>
+      <c r="D118">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>220-229</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>240-249</t>
+        </is>
+      </c>
+      <c r="C119">
+        <v>4</v>
+      </c>
+      <c r="D119">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>220-229</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>250-259</t>
+        </is>
+      </c>
+      <c r="C120">
+        <v>1</v>
+      </c>
+      <c r="D120">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>220-229</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>270-279</t>
+        </is>
+      </c>
+      <c r="C121">
+        <v>1</v>
+      </c>
+      <c r="D121">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>220-229</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>330-339</t>
+        </is>
+      </c>
+      <c r="C122">
+        <v>1</v>
+      </c>
+      <c r="D122">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>230-239</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>160-169</t>
+        </is>
+      </c>
+      <c r="C123">
+        <v>2</v>
+      </c>
+      <c r="D123">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>230-239</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>170-179</t>
+        </is>
+      </c>
+      <c r="C124">
+        <v>1</v>
+      </c>
+      <c r="D124">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>230-239</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>180-189</t>
+        </is>
+      </c>
+      <c r="C125">
+        <v>4</v>
+      </c>
+      <c r="D125">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>230-239</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>190-199</t>
+        </is>
+      </c>
+      <c r="C126">
+        <v>6</v>
+      </c>
+      <c r="D126">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>230-239</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>200-209</t>
+        </is>
+      </c>
+      <c r="C127">
+        <v>11</v>
+      </c>
+      <c r="D127">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>230-239</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>210-219</t>
+        </is>
+      </c>
+      <c r="C128">
+        <v>21</v>
+      </c>
+      <c r="D128">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>230-239</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>220-229</t>
+        </is>
+      </c>
+      <c r="C129">
+        <v>9</v>
+      </c>
+      <c r="D129">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>230-239</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>230-239</t>
+        </is>
+      </c>
+      <c r="C130">
+        <v>8</v>
+      </c>
+      <c r="D130">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>230-239</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>240-249</t>
+        </is>
+      </c>
+      <c r="C131">
+        <v>3</v>
+      </c>
+      <c r="D131">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>230-239</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>250-259</t>
+        </is>
+      </c>
+      <c r="C132">
+        <v>2</v>
+      </c>
+      <c r="D132">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>240-249</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>180-189</t>
+        </is>
+      </c>
+      <c r="C133">
+        <v>1</v>
+      </c>
+      <c r="D133">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>240-249</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>190-199</t>
+        </is>
+      </c>
+      <c r="C134">
+        <v>2</v>
+      </c>
+      <c r="D134">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>240-249</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>200-209</t>
+        </is>
+      </c>
+      <c r="C135">
+        <v>6</v>
+      </c>
+      <c r="D135">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>240-249</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>210-219</t>
+        </is>
+      </c>
+      <c r="C136">
+        <v>16</v>
+      </c>
+      <c r="D136">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>240-249</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>220-229</t>
+        </is>
+      </c>
+      <c r="C137">
+        <v>17</v>
+      </c>
+      <c r="D137">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>240-249</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>230-239</t>
+        </is>
+      </c>
+      <c r="C138">
+        <v>11</v>
+      </c>
+      <c r="D138">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>240-249</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>240-249</t>
+        </is>
+      </c>
+      <c r="C139">
+        <v>4</v>
+      </c>
+      <c r="D139">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>240-249</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>250-259</t>
+        </is>
+      </c>
+      <c r="C140">
+        <v>3</v>
+      </c>
+      <c r="D140">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>240-249</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>260-269</t>
+        </is>
+      </c>
+      <c r="C141">
+        <v>2</v>
+      </c>
+      <c r="D141">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>240-249</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>280-289</t>
+        </is>
+      </c>
+      <c r="C142">
+        <v>1</v>
+      </c>
+      <c r="D142">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>250-259</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>190-199</t>
+        </is>
+      </c>
+      <c r="C143">
+        <v>1</v>
+      </c>
+      <c r="D143">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>250-259</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>200-209</t>
+        </is>
+      </c>
+      <c r="C144">
+        <v>5</v>
+      </c>
+      <c r="D144">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>250-259</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>210-219</t>
+        </is>
+      </c>
+      <c r="C145">
+        <v>8</v>
+      </c>
+      <c r="D145">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>250-259</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>220-229</t>
+        </is>
+      </c>
+      <c r="C146">
+        <v>13</v>
+      </c>
+      <c r="D146">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>250-259</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>230-239</t>
+        </is>
+      </c>
+      <c r="C147">
+        <v>6</v>
+      </c>
+      <c r="D147">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>250-259</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>240-249</t>
+        </is>
+      </c>
+      <c r="C148">
+        <v>8</v>
+      </c>
+      <c r="D148">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>250-259</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>250-259</t>
+        </is>
+      </c>
+      <c r="C149">
+        <v>1</v>
+      </c>
+      <c r="D149">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>250-259</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>260-269</t>
+        </is>
+      </c>
+      <c r="C150">
+        <v>3</v>
+      </c>
+      <c r="D150">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>250-259</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>270-279</t>
+        </is>
+      </c>
+      <c r="C151">
+        <v>1</v>
+      </c>
+      <c r="D151">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>250-259</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>280-289</t>
+        </is>
+      </c>
+      <c r="C152">
+        <v>2</v>
+      </c>
+      <c r="D152">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>260-269</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>170-179</t>
+        </is>
+      </c>
+      <c r="C153">
+        <v>1</v>
+      </c>
+      <c r="D153">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>260-269</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>200-209</t>
+        </is>
+      </c>
+      <c r="C154">
+        <v>1</v>
+      </c>
+      <c r="D154">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>260-269</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>210-219</t>
+        </is>
+      </c>
+      <c r="C155">
+        <v>4</v>
+      </c>
+      <c r="D155">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>260-269</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>220-229</t>
+        </is>
+      </c>
+      <c r="C156">
+        <v>8</v>
+      </c>
+      <c r="D156">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>260-269</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>230-239</t>
+        </is>
+      </c>
+      <c r="C157">
+        <v>15</v>
+      </c>
+      <c r="D157">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>260-269</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>240-249</t>
+        </is>
+      </c>
+      <c r="C158">
+        <v>9</v>
+      </c>
+      <c r="D158">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>260-269</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>250-259</t>
+        </is>
+      </c>
+      <c r="C159">
+        <v>8</v>
+      </c>
+      <c r="D159">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>260-269</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>260-269</t>
+        </is>
+      </c>
+      <c r="C160">
+        <v>2</v>
+      </c>
+      <c r="D160">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>260-269</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>270-279</t>
+        </is>
+      </c>
+      <c r="C161">
+        <v>1</v>
+      </c>
+      <c r="D161">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>260-269</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>290-299</t>
+        </is>
+      </c>
+      <c r="C162">
+        <v>1</v>
+      </c>
+      <c r="D162">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>270-279</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>200-209</t>
+        </is>
+      </c>
+      <c r="C163">
+        <v>2</v>
+      </c>
+      <c r="D163">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>270-279</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>210-219</t>
+        </is>
+      </c>
+      <c r="C164">
+        <v>1</v>
+      </c>
+      <c r="D164">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>270-279</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>220-229</t>
+        </is>
+      </c>
+      <c r="C165">
+        <v>8</v>
+      </c>
+      <c r="D165">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>270-279</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>230-239</t>
+        </is>
+      </c>
+      <c r="C166">
+        <v>3</v>
+      </c>
+      <c r="D166">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>270-279</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>240-249</t>
+        </is>
+      </c>
+      <c r="C167">
+        <v>8</v>
+      </c>
+      <c r="D167">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>270-279</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>250-259</t>
+        </is>
+      </c>
+      <c r="C168">
+        <v>4</v>
+      </c>
+      <c r="D168">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>270-279</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>260-269</t>
+        </is>
+      </c>
+      <c r="C169">
+        <v>7</v>
+      </c>
+      <c r="D169">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>270-279</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>270-279</t>
+        </is>
+      </c>
+      <c r="C170">
+        <v>3</v>
+      </c>
+      <c r="D170">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>270-279</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>290-299</t>
+        </is>
+      </c>
+      <c r="C171">
+        <v>1</v>
+      </c>
+      <c r="D171">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>270-279</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>300-309</t>
+        </is>
+      </c>
+      <c r="C172">
+        <v>1</v>
+      </c>
+      <c r="D172">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>270-279</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>330-339</t>
+        </is>
+      </c>
+      <c r="C173">
+        <v>1</v>
+      </c>
+      <c r="D173">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>280-289</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>220-229</t>
+        </is>
+      </c>
+      <c r="C174">
+        <v>2</v>
+      </c>
+      <c r="D174">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>280-289</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>230-239</t>
+        </is>
+      </c>
+      <c r="C175">
+        <v>2</v>
+      </c>
+      <c r="D175">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>280-289</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>240-249</t>
+        </is>
+      </c>
+      <c r="C176">
+        <v>9</v>
+      </c>
+      <c r="D176">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>280-289</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>250-259</t>
+        </is>
+      </c>
+      <c r="C177">
+        <v>6</v>
+      </c>
+      <c r="D177">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>280-289</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>260-269</t>
+        </is>
+      </c>
+      <c r="C178">
+        <v>7</v>
+      </c>
+      <c r="D178">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>280-289</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>270-279</t>
+        </is>
+      </c>
+      <c r="C179">
+        <v>3</v>
+      </c>
+      <c r="D179">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>280-289</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>280-289</t>
+        </is>
+      </c>
+      <c r="C180">
+        <v>6</v>
+      </c>
+      <c r="D180">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>280-289</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>290-299</t>
+        </is>
+      </c>
+      <c r="C181">
+        <v>2</v>
+      </c>
+      <c r="D181">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>290-299</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>210-219</t>
+        </is>
+      </c>
+      <c r="C182">
+        <v>1</v>
+      </c>
+      <c r="D182">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>290-299</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>220-229</t>
+        </is>
+      </c>
+      <c r="C183">
+        <v>1</v>
+      </c>
+      <c r="D183">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>290-299</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>230-239</t>
+        </is>
+      </c>
+      <c r="C184">
+        <v>4</v>
+      </c>
+      <c r="D184">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>290-299</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>240-249</t>
+        </is>
+      </c>
+      <c r="C185">
+        <v>2</v>
+      </c>
+      <c r="D185">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>290-299</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>250-259</t>
+        </is>
+      </c>
+      <c r="C186">
+        <v>2</v>
+      </c>
+      <c r="D186">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>290-299</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>260-269</t>
+        </is>
+      </c>
+      <c r="C187">
+        <v>2</v>
+      </c>
+      <c r="D187">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>290-299</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>270-279</t>
+        </is>
+      </c>
+      <c r="C188">
+        <v>6</v>
+      </c>
+      <c r="D188">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>290-299</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>280-289</t>
+        </is>
+      </c>
+      <c r="C189">
+        <v>4</v>
+      </c>
+      <c r="D189">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>290-299</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>290-299</t>
+        </is>
+      </c>
+      <c r="C190">
+        <v>1</v>
+      </c>
+      <c r="D190">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>290-299</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>400-409</t>
+        </is>
+      </c>
+      <c r="C191">
+        <v>1</v>
+      </c>
+      <c r="D191">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>290-299</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>440-449</t>
+        </is>
+      </c>
+      <c r="C192">
+        <v>1</v>
+      </c>
+      <c r="D192">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>300-309</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>220-229</t>
+        </is>
+      </c>
+      <c r="C193">
+        <v>1</v>
+      </c>
+      <c r="D193">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>300-309</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>230-239</t>
+        </is>
+      </c>
+      <c r="C194">
+        <v>3</v>
+      </c>
+      <c r="D194">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>300-309</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>240-249</t>
+        </is>
+      </c>
+      <c r="C195">
+        <v>5</v>
+      </c>
+      <c r="D195">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>300-309</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>250-259</t>
+        </is>
+      </c>
+      <c r="C196">
+        <v>3</v>
+      </c>
+      <c r="D196">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>300-309</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>260-269</t>
+        </is>
+      </c>
+      <c r="C197">
+        <v>4</v>
+      </c>
+      <c r="D197">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>300-309</t>
+        </is>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>270-279</t>
+        </is>
+      </c>
+      <c r="C198">
+        <v>3</v>
+      </c>
+      <c r="D198">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>300-309</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>280-289</t>
+        </is>
+      </c>
+      <c r="C199">
+        <v>8</v>
+      </c>
+      <c r="D199">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>300-309</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>290-299</t>
+        </is>
+      </c>
+      <c r="C200">
+        <v>2</v>
+      </c>
+      <c r="D200">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>300-309</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>300-309</t>
+        </is>
+      </c>
+      <c r="C201">
+        <v>1</v>
+      </c>
+      <c r="D201">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>310-319</t>
+        </is>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>250-259</t>
+        </is>
+      </c>
+      <c r="C202">
+        <v>4</v>
+      </c>
+      <c r="D202">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>310-319</t>
+        </is>
+      </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>260-269</t>
+        </is>
+      </c>
+      <c r="C203">
+        <v>4</v>
+      </c>
+      <c r="D203">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>310-319</t>
+        </is>
+      </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>270-279</t>
+        </is>
+      </c>
+      <c r="C204">
+        <v>4</v>
+      </c>
+      <c r="D204">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>310-319</t>
+        </is>
+      </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>280-289</t>
+        </is>
+      </c>
+      <c r="C205">
+        <v>6</v>
+      </c>
+      <c r="D205">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>310-319</t>
+        </is>
+      </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>290-299</t>
+        </is>
+      </c>
+      <c r="C206">
+        <v>5</v>
+      </c>
+      <c r="D206">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>310-319</t>
+        </is>
+      </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>300-309</t>
+        </is>
+      </c>
+      <c r="C207">
+        <v>2</v>
+      </c>
+      <c r="D207">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>310-319</t>
+        </is>
+      </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>310-319</t>
+        </is>
+      </c>
+      <c r="C208">
+        <v>1</v>
+      </c>
+      <c r="D208">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>310-319</t>
+        </is>
+      </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>320-329</t>
+        </is>
+      </c>
+      <c r="C209">
+        <v>1</v>
+      </c>
+      <c r="D209">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>310-319</t>
+        </is>
+      </c>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>330-339</t>
+        </is>
+      </c>
+      <c r="C210">
+        <v>1</v>
+      </c>
+      <c r="D210">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>320-329</t>
+        </is>
+      </c>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>240-249</t>
+        </is>
+      </c>
+      <c r="C211">
+        <v>2</v>
+      </c>
+      <c r="D211">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>320-329</t>
+        </is>
+      </c>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>250-259</t>
+        </is>
+      </c>
+      <c r="C212">
+        <v>1</v>
+      </c>
+      <c r="D212">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>320-329</t>
+        </is>
+      </c>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>260-269</t>
+        </is>
+      </c>
+      <c r="C213">
+        <v>2</v>
+      </c>
+      <c r="D213">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>320-329</t>
+        </is>
+      </c>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t>270-279</t>
+        </is>
+      </c>
+      <c r="C214">
+        <v>3</v>
+      </c>
+      <c r="D214">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>320-329</t>
+        </is>
+      </c>
+      <c r="B215" t="inlineStr">
+        <is>
+          <t>280-289</t>
+        </is>
+      </c>
+      <c r="C215">
+        <v>6</v>
+      </c>
+      <c r="D215">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>320-329</t>
+        </is>
+      </c>
+      <c r="B216" t="inlineStr">
+        <is>
+          <t>290-299</t>
+        </is>
+      </c>
+      <c r="C216">
+        <v>2</v>
+      </c>
+      <c r="D216">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>320-329</t>
+        </is>
+      </c>
+      <c r="B217" t="inlineStr">
+        <is>
+          <t>300-309</t>
+        </is>
+      </c>
+      <c r="C217">
+        <v>6</v>
+      </c>
+      <c r="D217">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>320-329</t>
+        </is>
+      </c>
+      <c r="B218" t="inlineStr">
+        <is>
+          <t>310-319</t>
+        </is>
+      </c>
+      <c r="C218">
+        <v>6</v>
+      </c>
+      <c r="D218">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
+          <t>320-329</t>
+        </is>
+      </c>
+      <c r="B219" t="inlineStr">
+        <is>
+          <t>320-329</t>
+        </is>
+      </c>
+      <c r="C219">
+        <v>1</v>
+      </c>
+      <c r="D219">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>320-329</t>
+        </is>
+      </c>
+      <c r="B220" t="inlineStr">
+        <is>
+          <t>330-339</t>
+        </is>
+      </c>
+      <c r="C220">
+        <v>1</v>
+      </c>
+      <c r="D220">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>320-329</t>
+        </is>
+      </c>
+      <c r="B221" t="inlineStr">
+        <is>
+          <t>360-369</t>
+        </is>
+      </c>
+      <c r="C221">
+        <v>1</v>
+      </c>
+      <c r="D221">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="inlineStr">
+        <is>
+          <t>330-339</t>
+        </is>
+      </c>
+      <c r="B222" t="inlineStr">
+        <is>
+          <t>250-259</t>
+        </is>
+      </c>
+      <c r="C222">
+        <v>2</v>
+      </c>
+      <c r="D222">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="inlineStr">
+        <is>
+          <t>330-339</t>
+        </is>
+      </c>
+      <c r="B223" t="inlineStr">
+        <is>
+          <t>260-269</t>
+        </is>
+      </c>
+      <c r="C223">
+        <v>3</v>
+      </c>
+      <c r="D223">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="inlineStr">
+        <is>
+          <t>330-339</t>
+        </is>
+      </c>
+      <c r="B224" t="inlineStr">
+        <is>
+          <t>270-279</t>
+        </is>
+      </c>
+      <c r="C224">
+        <v>2</v>
+      </c>
+      <c r="D224">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="inlineStr">
+        <is>
+          <t>330-339</t>
+        </is>
+      </c>
+      <c r="B225" t="inlineStr">
+        <is>
+          <t>280-289</t>
+        </is>
+      </c>
+      <c r="C225">
+        <v>5</v>
+      </c>
+      <c r="D225">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="inlineStr">
+        <is>
+          <t>330-339</t>
+        </is>
+      </c>
+      <c r="B226" t="inlineStr">
+        <is>
+          <t>290-299</t>
+        </is>
+      </c>
+      <c r="C226">
         <v>10</v>
       </c>
-      <c r="C50">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="51">
-      <c r="B51">
-        <v>1</v>
-      </c>
-      <c r="C51">
+      <c r="D226">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="inlineStr">
+        <is>
+          <t>330-339</t>
+        </is>
+      </c>
+      <c r="B227" t="inlineStr">
+        <is>
+          <t>300-309</t>
+        </is>
+      </c>
+      <c r="C227">
+        <v>5</v>
+      </c>
+      <c r="D227">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="inlineStr">
+        <is>
+          <t>330-339</t>
+        </is>
+      </c>
+      <c r="B228" t="inlineStr">
+        <is>
+          <t>310-319</t>
+        </is>
+      </c>
+      <c r="C228">
+        <v>4</v>
+      </c>
+      <c r="D228">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="inlineStr">
+        <is>
+          <t>330-339</t>
+        </is>
+      </c>
+      <c r="B229" t="inlineStr">
+        <is>
+          <t>320-329</t>
+        </is>
+      </c>
+      <c r="C229">
+        <v>2</v>
+      </c>
+      <c r="D229">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="inlineStr">
+        <is>
+          <t>330-339</t>
+        </is>
+      </c>
+      <c r="B230" t="inlineStr">
+        <is>
+          <t>380-389</t>
+        </is>
+      </c>
+      <c r="C230">
+        <v>1</v>
+      </c>
+      <c r="D230">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="inlineStr">
+        <is>
+          <t>340-349</t>
+        </is>
+      </c>
+      <c r="B231" t="inlineStr">
+        <is>
+          <t>260-269</t>
+        </is>
+      </c>
+      <c r="C231">
+        <v>1</v>
+      </c>
+      <c r="D231">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="inlineStr">
+        <is>
+          <t>340-349</t>
+        </is>
+      </c>
+      <c r="B232" t="inlineStr">
+        <is>
+          <t>270-279</t>
+        </is>
+      </c>
+      <c r="C232">
+        <v>3</v>
+      </c>
+      <c r="D232">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="inlineStr">
+        <is>
+          <t>340-349</t>
+        </is>
+      </c>
+      <c r="B233" t="inlineStr">
+        <is>
+          <t>280-289</t>
+        </is>
+      </c>
+      <c r="C233">
+        <v>3</v>
+      </c>
+      <c r="D233">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="inlineStr">
+        <is>
+          <t>340-349</t>
+        </is>
+      </c>
+      <c r="B234" t="inlineStr">
+        <is>
+          <t>290-299</t>
+        </is>
+      </c>
+      <c r="C234">
+        <v>8</v>
+      </c>
+      <c r="D234">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="inlineStr">
+        <is>
+          <t>340-349</t>
+        </is>
+      </c>
+      <c r="B235" t="inlineStr">
+        <is>
+          <t>300-309</t>
+        </is>
+      </c>
+      <c r="C235">
+        <v>3</v>
+      </c>
+      <c r="D235">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="inlineStr">
+        <is>
+          <t>340-349</t>
+        </is>
+      </c>
+      <c r="B236" t="inlineStr">
+        <is>
+          <t>310-319</t>
+        </is>
+      </c>
+      <c r="C236">
+        <v>5</v>
+      </c>
+      <c r="D236">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="inlineStr">
+        <is>
+          <t>340-349</t>
+        </is>
+      </c>
+      <c r="B237" t="inlineStr">
+        <is>
+          <t>320-329</t>
+        </is>
+      </c>
+      <c r="C237">
+        <v>1</v>
+      </c>
+      <c r="D237">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="inlineStr">
+        <is>
+          <t>340-349</t>
+        </is>
+      </c>
+      <c r="B238" t="inlineStr">
+        <is>
+          <t>330-339</t>
+        </is>
+      </c>
+      <c r="C238">
+        <v>1</v>
+      </c>
+      <c r="D238">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="inlineStr">
+        <is>
+          <t>350-359</t>
+        </is>
+      </c>
+      <c r="B239" t="inlineStr">
+        <is>
+          <t>270-279</t>
+        </is>
+      </c>
+      <c r="C239">
+        <v>2</v>
+      </c>
+      <c r="D239">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="inlineStr">
+        <is>
+          <t>350-359</t>
+        </is>
+      </c>
+      <c r="B240" t="inlineStr">
+        <is>
+          <t>280-289</t>
+        </is>
+      </c>
+      <c r="C240">
+        <v>2</v>
+      </c>
+      <c r="D240">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="inlineStr">
+        <is>
+          <t>350-359</t>
+        </is>
+      </c>
+      <c r="B241" t="inlineStr">
+        <is>
+          <t>290-299</t>
+        </is>
+      </c>
+      <c r="C241">
+        <v>6</v>
+      </c>
+      <c r="D241">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" t="inlineStr">
+        <is>
+          <t>350-359</t>
+        </is>
+      </c>
+      <c r="B242" t="inlineStr">
+        <is>
+          <t>300-309</t>
+        </is>
+      </c>
+      <c r="C242">
+        <v>8</v>
+      </c>
+      <c r="D242">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="inlineStr">
+        <is>
+          <t>350-359</t>
+        </is>
+      </c>
+      <c r="B243" t="inlineStr">
+        <is>
+          <t>310-319</t>
+        </is>
+      </c>
+      <c r="C243">
+        <v>3</v>
+      </c>
+      <c r="D243">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" t="inlineStr">
+        <is>
+          <t>350-359</t>
+        </is>
+      </c>
+      <c r="B244" t="inlineStr">
+        <is>
+          <t>330-339</t>
+        </is>
+      </c>
+      <c r="C244">
+        <v>1</v>
+      </c>
+      <c r="D244">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" t="inlineStr">
+        <is>
+          <t>350-359</t>
+        </is>
+      </c>
+      <c r="B245" t="inlineStr">
+        <is>
+          <t>340-349</t>
+        </is>
+      </c>
+      <c r="C245">
+        <v>2</v>
+      </c>
+      <c r="D245">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" t="inlineStr">
+        <is>
+          <t>360-369</t>
+        </is>
+      </c>
+      <c r="B246" t="inlineStr">
+        <is>
+          <t>270-279</t>
+        </is>
+      </c>
+      <c r="C246">
+        <v>1</v>
+      </c>
+      <c r="D246">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" t="inlineStr">
+        <is>
+          <t>360-369</t>
+        </is>
+      </c>
+      <c r="B247" t="inlineStr">
+        <is>
+          <t>280-289</t>
+        </is>
+      </c>
+      <c r="C247">
+        <v>3</v>
+      </c>
+      <c r="D247">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" t="inlineStr">
+        <is>
+          <t>360-369</t>
+        </is>
+      </c>
+      <c r="B248" t="inlineStr">
+        <is>
+          <t>290-299</t>
+        </is>
+      </c>
+      <c r="C248">
+        <v>1</v>
+      </c>
+      <c r="D248">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" t="inlineStr">
+        <is>
+          <t>360-369</t>
+        </is>
+      </c>
+      <c r="B249" t="inlineStr">
+        <is>
+          <t>300-309</t>
+        </is>
+      </c>
+      <c r="C249">
+        <v>4</v>
+      </c>
+      <c r="D249">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" t="inlineStr">
+        <is>
+          <t>360-369</t>
+        </is>
+      </c>
+      <c r="B250" t="inlineStr">
+        <is>
+          <t>310-319</t>
+        </is>
+      </c>
+      <c r="C250">
+        <v>5</v>
+      </c>
+      <c r="D250">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" t="inlineStr">
+        <is>
+          <t>360-369</t>
+        </is>
+      </c>
+      <c r="B251" t="inlineStr">
+        <is>
+          <t>320-329</t>
+        </is>
+      </c>
+      <c r="C251">
+        <v>4</v>
+      </c>
+      <c r="D251">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" t="inlineStr">
+        <is>
+          <t>360-369</t>
+        </is>
+      </c>
+      <c r="B252" t="inlineStr">
+        <is>
+          <t>330-339</t>
+        </is>
+      </c>
+      <c r="C252">
+        <v>2</v>
+      </c>
+      <c r="D252">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" t="inlineStr">
+        <is>
+          <t>360-369</t>
+        </is>
+      </c>
+      <c r="B253" t="inlineStr">
+        <is>
+          <t>350-359</t>
+        </is>
+      </c>
+      <c r="C253">
+        <v>1</v>
+      </c>
+      <c r="D253">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" t="inlineStr">
+        <is>
+          <t>360-369</t>
+        </is>
+      </c>
+      <c r="B254" t="inlineStr">
+        <is>
+          <t>400-409</t>
+        </is>
+      </c>
+      <c r="C254">
+        <v>1</v>
+      </c>
+      <c r="D254">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" t="inlineStr">
+        <is>
+          <t>360-369</t>
+        </is>
+      </c>
+      <c r="C255">
+        <v>1</v>
+      </c>
+      <c r="D255">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" t="inlineStr">
+        <is>
+          <t>370-379</t>
+        </is>
+      </c>
+      <c r="B256" t="inlineStr">
+        <is>
+          <t>270-279</t>
+        </is>
+      </c>
+      <c r="C256">
+        <v>1</v>
+      </c>
+      <c r="D256">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" t="inlineStr">
+        <is>
+          <t>370-379</t>
+        </is>
+      </c>
+      <c r="B257" t="inlineStr">
+        <is>
+          <t>290-299</t>
+        </is>
+      </c>
+      <c r="C257">
+        <v>2</v>
+      </c>
+      <c r="D257">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" t="inlineStr">
+        <is>
+          <t>370-379</t>
+        </is>
+      </c>
+      <c r="B258" t="inlineStr">
+        <is>
+          <t>300-309</t>
+        </is>
+      </c>
+      <c r="C258">
+        <v>2</v>
+      </c>
+      <c r="D258">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" t="inlineStr">
+        <is>
+          <t>370-379</t>
+        </is>
+      </c>
+      <c r="B259" t="inlineStr">
+        <is>
+          <t>320-329</t>
+        </is>
+      </c>
+      <c r="C259">
+        <v>5</v>
+      </c>
+      <c r="D259">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" t="inlineStr">
+        <is>
+          <t>370-379</t>
+        </is>
+      </c>
+      <c r="B260" t="inlineStr">
+        <is>
+          <t>330-339</t>
+        </is>
+      </c>
+      <c r="C260">
+        <v>1</v>
+      </c>
+      <c r="D260">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" t="inlineStr">
+        <is>
+          <t>370-379</t>
+        </is>
+      </c>
+      <c r="B261" t="inlineStr">
+        <is>
+          <t>340-349</t>
+        </is>
+      </c>
+      <c r="C261">
+        <v>1</v>
+      </c>
+      <c r="D261">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" t="inlineStr">
+        <is>
+          <t>370-379</t>
+        </is>
+      </c>
+      <c r="B262" t="inlineStr">
+        <is>
+          <t>350-359</t>
+        </is>
+      </c>
+      <c r="C262">
+        <v>1</v>
+      </c>
+      <c r="D262">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" t="inlineStr">
+        <is>
+          <t>370-379</t>
+        </is>
+      </c>
+      <c r="B263" t="inlineStr">
+        <is>
+          <t>410-419</t>
+        </is>
+      </c>
+      <c r="C263">
+        <v>1</v>
+      </c>
+      <c r="D263">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" t="inlineStr">
+        <is>
+          <t>380-389</t>
+        </is>
+      </c>
+      <c r="B264" t="inlineStr">
+        <is>
+          <t>270-279</t>
+        </is>
+      </c>
+      <c r="C264">
+        <v>1</v>
+      </c>
+      <c r="D264">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" t="inlineStr">
+        <is>
+          <t>380-389</t>
+        </is>
+      </c>
+      <c r="B265" t="inlineStr">
+        <is>
+          <t>310-319</t>
+        </is>
+      </c>
+      <c r="C265">
+        <v>3</v>
+      </c>
+      <c r="D265">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" t="inlineStr">
+        <is>
+          <t>380-389</t>
+        </is>
+      </c>
+      <c r="B266" t="inlineStr">
+        <is>
+          <t>330-339</t>
+        </is>
+      </c>
+      <c r="C266">
+        <v>2</v>
+      </c>
+      <c r="D266">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" t="inlineStr">
+        <is>
+          <t>380-389</t>
+        </is>
+      </c>
+      <c r="B267" t="inlineStr">
+        <is>
+          <t>340-349</t>
+        </is>
+      </c>
+      <c r="C267">
+        <v>3</v>
+      </c>
+      <c r="D267">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" t="inlineStr">
+        <is>
+          <t>390-399</t>
+        </is>
+      </c>
+      <c r="B268" t="inlineStr">
+        <is>
+          <t>310-319</t>
+        </is>
+      </c>
+      <c r="C268">
+        <v>2</v>
+      </c>
+      <c r="D268">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" t="inlineStr">
+        <is>
+          <t>390-399</t>
+        </is>
+      </c>
+      <c r="B269" t="inlineStr">
+        <is>
+          <t>320-329</t>
+        </is>
+      </c>
+      <c r="C269">
+        <v>1</v>
+      </c>
+      <c r="D269">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" t="inlineStr">
+        <is>
+          <t>390-399</t>
+        </is>
+      </c>
+      <c r="B270" t="inlineStr">
+        <is>
+          <t>330-339</t>
+        </is>
+      </c>
+      <c r="C270">
+        <v>2</v>
+      </c>
+      <c r="D270">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" t="inlineStr">
+        <is>
+          <t>390-399</t>
+        </is>
+      </c>
+      <c r="B271" t="inlineStr">
+        <is>
+          <t>340-349</t>
+        </is>
+      </c>
+      <c r="C271">
+        <v>2</v>
+      </c>
+      <c r="D271">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" t="inlineStr">
+        <is>
+          <t>390-399</t>
+        </is>
+      </c>
+      <c r="B272" t="inlineStr">
+        <is>
+          <t>360-369</t>
+        </is>
+      </c>
+      <c r="C272">
+        <v>1</v>
+      </c>
+      <c r="D272">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" t="inlineStr">
+        <is>
+          <t>390-399</t>
+        </is>
+      </c>
+      <c r="B273" t="inlineStr">
+        <is>
+          <t>390-399</t>
+        </is>
+      </c>
+      <c r="C273">
+        <v>1</v>
+      </c>
+      <c r="D273">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" t="inlineStr">
+        <is>
+          <t>390-399</t>
+        </is>
+      </c>
+      <c r="B274" t="inlineStr">
+        <is>
+          <t>420-429</t>
+        </is>
+      </c>
+      <c r="C274">
+        <v>1</v>
+      </c>
+      <c r="D274">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" t="inlineStr">
+        <is>
+          <t>400-409</t>
+        </is>
+      </c>
+      <c r="B275" t="inlineStr">
+        <is>
+          <t>300-309</t>
+        </is>
+      </c>
+      <c r="C275">
+        <v>2</v>
+      </c>
+      <c r="D275">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" t="inlineStr">
+        <is>
+          <t>400-409</t>
+        </is>
+      </c>
+      <c r="B276" t="inlineStr">
+        <is>
+          <t>310-319</t>
+        </is>
+      </c>
+      <c r="C276">
+        <v>1</v>
+      </c>
+      <c r="D276">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" t="inlineStr">
+        <is>
+          <t>400-409</t>
+        </is>
+      </c>
+      <c r="B277" t="inlineStr">
+        <is>
+          <t>330-339</t>
+        </is>
+      </c>
+      <c r="C277">
+        <v>2</v>
+      </c>
+      <c r="D277">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" t="inlineStr">
+        <is>
+          <t>400-409</t>
+        </is>
+      </c>
+      <c r="B278" t="inlineStr">
+        <is>
+          <t>340-349</t>
+        </is>
+      </c>
+      <c r="C278">
+        <v>1</v>
+      </c>
+      <c r="D278">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" t="inlineStr">
+        <is>
+          <t>400-409</t>
+        </is>
+      </c>
+      <c r="B279" t="inlineStr">
+        <is>
+          <t>360-369</t>
+        </is>
+      </c>
+      <c r="C279">
+        <v>1</v>
+      </c>
+      <c r="D279">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" t="inlineStr">
+        <is>
+          <t>400-409</t>
+        </is>
+      </c>
+      <c r="B280" t="inlineStr">
+        <is>
+          <t>370-379</t>
+        </is>
+      </c>
+      <c r="C280">
+        <v>1</v>
+      </c>
+      <c r="D280">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" t="inlineStr">
+        <is>
+          <t>410-419</t>
+        </is>
+      </c>
+      <c r="B281" t="inlineStr">
+        <is>
+          <t>310-319</t>
+        </is>
+      </c>
+      <c r="C281">
+        <v>2</v>
+      </c>
+      <c r="D281">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" t="inlineStr">
+        <is>
+          <t>410-419</t>
+        </is>
+      </c>
+      <c r="B282" t="inlineStr">
+        <is>
+          <t>330-339</t>
+        </is>
+      </c>
+      <c r="C282">
+        <v>1</v>
+      </c>
+      <c r="D282">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" t="inlineStr">
+        <is>
+          <t>410-419</t>
+        </is>
+      </c>
+      <c r="B283" t="inlineStr">
+        <is>
+          <t>340-349</t>
+        </is>
+      </c>
+      <c r="C283">
+        <v>1</v>
+      </c>
+      <c r="D283">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" t="inlineStr">
+        <is>
+          <t>410-419</t>
+        </is>
+      </c>
+      <c r="B284" t="inlineStr">
+        <is>
+          <t>350-359</t>
+        </is>
+      </c>
+      <c r="C284">
+        <v>1</v>
+      </c>
+      <c r="D284">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" t="inlineStr">
+        <is>
+          <t>410-419</t>
+        </is>
+      </c>
+      <c r="B285" t="inlineStr">
+        <is>
+          <t>360-369</t>
+        </is>
+      </c>
+      <c r="C285">
+        <v>1</v>
+      </c>
+      <c r="D285">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" t="inlineStr">
+        <is>
+          <t>410-419</t>
+        </is>
+      </c>
+      <c r="B286" t="inlineStr">
+        <is>
+          <t>390-399</t>
+        </is>
+      </c>
+      <c r="C286">
+        <v>2</v>
+      </c>
+      <c r="D286">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" t="inlineStr">
+        <is>
+          <t>420-429</t>
+        </is>
+      </c>
+      <c r="B287" t="inlineStr">
+        <is>
+          <t>330-339</t>
+        </is>
+      </c>
+      <c r="C287">
+        <v>1</v>
+      </c>
+      <c r="D287">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" t="inlineStr">
+        <is>
+          <t>420-429</t>
+        </is>
+      </c>
+      <c r="B288" t="inlineStr">
+        <is>
+          <t>340-349</t>
+        </is>
+      </c>
+      <c r="C288">
+        <v>2</v>
+      </c>
+      <c r="D288">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" t="inlineStr">
+        <is>
+          <t>420-429</t>
+        </is>
+      </c>
+      <c r="B289" t="inlineStr">
+        <is>
+          <t>350-359</t>
+        </is>
+      </c>
+      <c r="C289">
+        <v>2</v>
+      </c>
+      <c r="D289">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" t="inlineStr">
+        <is>
+          <t>420-429</t>
+        </is>
+      </c>
+      <c r="B290" t="inlineStr">
+        <is>
+          <t>370-379</t>
+        </is>
+      </c>
+      <c r="C290">
+        <v>1</v>
+      </c>
+      <c r="D290">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" t="inlineStr">
+        <is>
+          <t>430-439</t>
+        </is>
+      </c>
+      <c r="B291" t="inlineStr">
+        <is>
+          <t>350-359</t>
+        </is>
+      </c>
+      <c r="C291">
+        <v>1</v>
+      </c>
+      <c r="D291">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" t="inlineStr">
+        <is>
+          <t>430-439</t>
+        </is>
+      </c>
+      <c r="B292" t="inlineStr">
+        <is>
+          <t>360-369</t>
+        </is>
+      </c>
+      <c r="C292">
+        <v>1</v>
+      </c>
+      <c r="D292">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" t="inlineStr">
+        <is>
+          <t>430-439</t>
+        </is>
+      </c>
+      <c r="B293" t="inlineStr">
+        <is>
+          <t>380-389</t>
+        </is>
+      </c>
+      <c r="C293">
+        <v>1</v>
+      </c>
+      <c r="D293">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" t="inlineStr">
+        <is>
+          <t>440-449</t>
+        </is>
+      </c>
+      <c r="B294" t="inlineStr">
+        <is>
+          <t>340-349</t>
+        </is>
+      </c>
+      <c r="C294">
+        <v>1</v>
+      </c>
+      <c r="D294">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" t="inlineStr">
+        <is>
+          <t>440-449</t>
+        </is>
+      </c>
+      <c r="B295" t="inlineStr">
+        <is>
+          <t>360-369</t>
+        </is>
+      </c>
+      <c r="C295">
+        <v>1</v>
+      </c>
+      <c r="D295">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" t="inlineStr">
+        <is>
+          <t>450-459</t>
+        </is>
+      </c>
+      <c r="B296" t="inlineStr">
+        <is>
+          <t>340-349</t>
+        </is>
+      </c>
+      <c r="C296">
+        <v>1</v>
+      </c>
+      <c r="D296">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" t="inlineStr">
+        <is>
+          <t>450-459</t>
+        </is>
+      </c>
+      <c r="B297" t="inlineStr">
+        <is>
+          <t>360-369</t>
+        </is>
+      </c>
+      <c r="C297">
+        <v>1</v>
+      </c>
+      <c r="D297">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" t="inlineStr">
+        <is>
+          <t>450-459</t>
+        </is>
+      </c>
+      <c r="B298" t="inlineStr">
+        <is>
+          <t>380-389</t>
+        </is>
+      </c>
+      <c r="C298">
+        <v>1</v>
+      </c>
+      <c r="D298">
         <v>1</v>
       </c>
     </row>

--- a/const/Binned_Summary.xlsx
+++ b/const/Binned_Summary.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D298"/>
+  <dimension ref="A1:D271"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -379,246 +379,246 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>90-99</t>
+          <t>110-119</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>120-129</t>
+          <t>130-139</t>
         </is>
       </c>
       <c r="C2">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="D2">
-        <v>1</v>
+        <v>11</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>100-109</t>
+          <t>110-119</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>80-89</t>
+          <t>140-149</t>
         </is>
       </c>
       <c r="C3">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="D3">
-        <v>1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>100-109</t>
+          <t>110-119</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>100-109</t>
+          <t>150-159</t>
         </is>
       </c>
       <c r="C4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D4">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>100-109</t>
+          <t>110-119</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>110-119</t>
+          <t>160-169</t>
         </is>
       </c>
       <c r="C5">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D5">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>100-109</t>
+          <t>110-119</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>120-129</t>
+          <t>170-179</t>
         </is>
       </c>
       <c r="C6">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="D6">
-        <v>14</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>100-109</t>
+          <t>120-129</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>130-139</t>
+          <t>110-119</t>
         </is>
       </c>
       <c r="C7">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="D7">
-        <v>11</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>100-109</t>
+          <t>120-129</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>140-149</t>
+          <t>120-129</t>
         </is>
       </c>
       <c r="C8">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="D8">
-        <v>3</v>
+        <v>9</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>100-109</t>
+          <t>120-129</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>150-159</t>
+          <t>130-139</t>
         </is>
       </c>
       <c r="C9">
-        <v>1</v>
+        <v>43</v>
       </c>
       <c r="D9">
-        <v>1</v>
+        <v>43</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>110-119</t>
+          <t>120-129</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>100-109</t>
+          <t>140-149</t>
         </is>
       </c>
       <c r="C10">
-        <v>2</v>
+        <v>88</v>
       </c>
       <c r="D10">
-        <v>2</v>
+        <v>88</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>110-119</t>
+          <t>120-129</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>110-119</t>
+          <t>150-159</t>
         </is>
       </c>
       <c r="C11">
-        <v>4</v>
+        <v>38</v>
       </c>
       <c r="D11">
-        <v>4</v>
+        <v>38</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>110-119</t>
+          <t>120-129</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>120-129</t>
+          <t>160-169</t>
         </is>
       </c>
       <c r="C12">
-        <v>47</v>
+        <v>16</v>
       </c>
       <c r="D12">
-        <v>47</v>
+        <v>16</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>110-119</t>
+          <t>120-129</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>130-139</t>
+          <t>170-179</t>
         </is>
       </c>
       <c r="C13">
-        <v>76</v>
+        <v>3</v>
       </c>
       <c r="D13">
-        <v>76</v>
+        <v>3</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>110-119</t>
+          <t>120-129</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>140-149</t>
+          <t>180-189</t>
         </is>
       </c>
       <c r="C14">
-        <v>35</v>
+        <v>1</v>
       </c>
       <c r="D14">
-        <v>35</v>
+        <v>1</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>110-119</t>
+          <t>130-139</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>150-159</t>
+          <t>120-129</t>
         </is>
       </c>
       <c r="C15">
@@ -631,642 +631,642 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>110-119</t>
+          <t>130-139</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>160-169</t>
+          <t>130-139</t>
         </is>
       </c>
       <c r="C16">
-        <v>2</v>
+        <v>44</v>
       </c>
       <c r="D16">
-        <v>2</v>
+        <v>44</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>120-129</t>
+          <t>130-139</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>100-109</t>
+          <t>140-149</t>
         </is>
       </c>
       <c r="C17">
-        <v>1</v>
+        <v>179</v>
       </c>
       <c r="D17">
-        <v>1</v>
+        <v>179</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>120-129</t>
+          <t>130-139</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>110-119</t>
+          <t>150-159</t>
         </is>
       </c>
       <c r="C18">
-        <v>4</v>
+        <v>132</v>
       </c>
       <c r="D18">
-        <v>4</v>
+        <v>132</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>120-129</t>
+          <t>130-139</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>120-129</t>
+          <t>160-169</t>
         </is>
       </c>
       <c r="C19">
-        <v>56</v>
+        <v>36</v>
       </c>
       <c r="D19">
-        <v>56</v>
+        <v>36</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>120-129</t>
+          <t>130-139</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>130-139</t>
+          <t>170-179</t>
         </is>
       </c>
       <c r="C20">
-        <v>148</v>
+        <v>6</v>
       </c>
       <c r="D20">
-        <v>148</v>
+        <v>6</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>120-129</t>
+          <t>130-139</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>140-149</t>
+          <t>180-189</t>
         </is>
       </c>
       <c r="C21">
-        <v>112</v>
+        <v>1</v>
       </c>
       <c r="D21">
-        <v>112</v>
+        <v>1</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>120-129</t>
+          <t>130-139</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>150-159</t>
+          <t>190-199</t>
         </is>
       </c>
       <c r="C22">
-        <v>37</v>
+        <v>1</v>
       </c>
       <c r="D22">
-        <v>37</v>
+        <v>1</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>120-129</t>
+          <t>130-139</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>160-169</t>
+          <t>210-219</t>
         </is>
       </c>
       <c r="C23">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D23">
-        <v>10</v>
+        <v>1</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
+          <t>140-149</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
           <t>120-129</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>170-179</t>
-        </is>
-      </c>
       <c r="C24">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D24">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
+          <t>140-149</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
           <t>130-139</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>100-109</t>
-        </is>
-      </c>
       <c r="C25">
-        <v>1</v>
+        <v>37</v>
       </c>
       <c r="D25">
-        <v>1</v>
+        <v>37</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>130-139</t>
+          <t>140-149</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>110-119</t>
+          <t>140-149</t>
         </is>
       </c>
       <c r="C26">
-        <v>1</v>
+        <v>169</v>
       </c>
       <c r="D26">
-        <v>1</v>
+        <v>169</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>130-139</t>
+          <t>140-149</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>120-129</t>
+          <t>150-159</t>
         </is>
       </c>
       <c r="C27">
-        <v>30</v>
+        <v>299</v>
       </c>
       <c r="D27">
-        <v>30</v>
+        <v>299</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>130-139</t>
+          <t>140-149</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>130-139</t>
+          <t>160-169</t>
         </is>
       </c>
       <c r="C28">
-        <v>206</v>
+        <v>162</v>
       </c>
       <c r="D28">
-        <v>206</v>
+        <v>162</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>130-139</t>
+          <t>140-149</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>140-149</t>
+          <t>170-179</t>
         </is>
       </c>
       <c r="C29">
-        <v>311</v>
+        <v>38</v>
       </c>
       <c r="D29">
-        <v>311</v>
+        <v>38</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>130-139</t>
+          <t>140-149</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>150-159</t>
+          <t>180-189</t>
         </is>
       </c>
       <c r="C30">
-        <v>158</v>
+        <v>10</v>
       </c>
       <c r="D30">
-        <v>158</v>
+        <v>10</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>130-139</t>
+          <t>140-149</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>160-169</t>
+          <t>190-199</t>
         </is>
       </c>
       <c r="C31">
-        <v>46</v>
+        <v>2</v>
       </c>
       <c r="D31">
-        <v>46</v>
+        <v>2</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>130-139</t>
+          <t>140-149</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>170-179</t>
+          <t>220-229</t>
         </is>
       </c>
       <c r="C32">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D32">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
+          <t>150-159</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
           <t>130-139</t>
         </is>
       </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>180-189</t>
-        </is>
-      </c>
       <c r="C33">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="D33">
-        <v>2</v>
+        <v>10</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>130-139</t>
+          <t>150-159</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>200-209</t>
+          <t>140-149</t>
         </is>
       </c>
       <c r="C34">
-        <v>3</v>
+        <v>123</v>
       </c>
       <c r="D34">
-        <v>3</v>
+        <v>123</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>140-149</t>
+          <t>150-159</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>110-119</t>
+          <t>150-159</t>
         </is>
       </c>
       <c r="C35">
-        <v>2</v>
+        <v>323</v>
       </c>
       <c r="D35">
-        <v>2</v>
+        <v>323</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>140-149</t>
+          <t>150-159</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>120-129</t>
+          <t>160-169</t>
         </is>
       </c>
       <c r="C36">
-        <v>15</v>
+        <v>330</v>
       </c>
       <c r="D36">
-        <v>15</v>
+        <v>330</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>140-149</t>
+          <t>150-159</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>130-139</t>
+          <t>170-179</t>
         </is>
       </c>
       <c r="C37">
-        <v>138</v>
+        <v>100</v>
       </c>
       <c r="D37">
-        <v>138</v>
+        <v>100</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>140-149</t>
+          <t>150-159</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>140-149</t>
+          <t>180-189</t>
         </is>
       </c>
       <c r="C38">
-        <v>321</v>
+        <v>23</v>
       </c>
       <c r="D38">
-        <v>321</v>
+        <v>23</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>140-149</t>
+          <t>150-159</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>150-159</t>
+          <t>190-199</t>
         </is>
       </c>
       <c r="C39">
-        <v>332</v>
+        <v>8</v>
       </c>
       <c r="D39">
-        <v>332</v>
+        <v>8</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>140-149</t>
+          <t>150-159</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>160-169</t>
+          <t>200-209</t>
         </is>
       </c>
       <c r="C40">
-        <v>104</v>
+        <v>3</v>
       </c>
       <c r="D40">
-        <v>104</v>
+        <v>3</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>140-149</t>
+          <t>160-169</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>170-179</t>
+          <t>120-129</t>
         </is>
       </c>
       <c r="C41">
-        <v>26</v>
+        <v>1</v>
       </c>
       <c r="D41">
-        <v>26</v>
+        <v>1</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>140-149</t>
+          <t>160-169</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>180-189</t>
+          <t>130-139</t>
         </is>
       </c>
       <c r="C42">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="D42">
-        <v>4</v>
+        <v>8</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
+          <t>160-169</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
           <t>140-149</t>
         </is>
       </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>190-199</t>
-        </is>
-      </c>
       <c r="C43">
-        <v>1</v>
+        <v>56</v>
       </c>
       <c r="D43">
-        <v>1</v>
+        <v>56</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
+          <t>160-169</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
           <t>150-159</t>
         </is>
       </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>120-129</t>
-        </is>
-      </c>
       <c r="C44">
-        <v>8</v>
+        <v>235</v>
       </c>
       <c r="D44">
-        <v>8</v>
+        <v>235</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>150-159</t>
+          <t>160-169</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>130-139</t>
+          <t>160-169</t>
         </is>
       </c>
       <c r="C45">
-        <v>76</v>
+        <v>328</v>
       </c>
       <c r="D45">
-        <v>76</v>
+        <v>328</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>150-159</t>
+          <t>160-169</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>140-149</t>
+          <t>170-179</t>
         </is>
       </c>
       <c r="C46">
-        <v>265</v>
+        <v>204</v>
       </c>
       <c r="D46">
-        <v>265</v>
+        <v>204</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>150-159</t>
+          <t>160-169</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>150-159</t>
+          <t>180-189</t>
         </is>
       </c>
       <c r="C47">
-        <v>318</v>
+        <v>60</v>
       </c>
       <c r="D47">
-        <v>318</v>
+        <v>60</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>150-159</t>
+          <t>160-169</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>160-169</t>
+          <t>190-199</t>
         </is>
       </c>
       <c r="C48">
-        <v>213</v>
+        <v>11</v>
       </c>
       <c r="D48">
-        <v>213</v>
+        <v>11</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>150-159</t>
+          <t>160-169</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>170-179</t>
+          <t>200-209</t>
         </is>
       </c>
       <c r="C49">
-        <v>75</v>
+        <v>3</v>
       </c>
       <c r="D49">
-        <v>75</v>
+        <v>3</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>150-159</t>
+          <t>160-169</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>180-189</t>
+          <t>210-219</t>
         </is>
       </c>
       <c r="C50">
-        <v>18</v>
+        <v>2</v>
       </c>
       <c r="D50">
-        <v>18</v>
+        <v>2</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>150-159</t>
+          <t>160-169</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>190-199</t>
+          <t>230-239</t>
         </is>
       </c>
       <c r="C51">
@@ -1279,498 +1279,498 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>150-159</t>
+          <t>170-179</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>220-229</t>
+          <t>140-149</t>
         </is>
       </c>
       <c r="C52">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="D52">
-        <v>1</v>
+        <v>16</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>160-169</t>
+          <t>170-179</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>130-139</t>
+          <t>150-159</t>
         </is>
       </c>
       <c r="C53">
-        <v>24</v>
+        <v>136</v>
       </c>
       <c r="D53">
-        <v>24</v>
+        <v>136</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
+          <t>170-179</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
           <t>160-169</t>
         </is>
       </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>140-149</t>
-        </is>
-      </c>
       <c r="C54">
-        <v>151</v>
+        <v>242</v>
       </c>
       <c r="D54">
-        <v>151</v>
+        <v>242</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>160-169</t>
+          <t>170-179</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>150-159</t>
+          <t>170-179</t>
         </is>
       </c>
       <c r="C55">
-        <v>272</v>
+        <v>219</v>
       </c>
       <c r="D55">
-        <v>272</v>
+        <v>219</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>160-169</t>
+          <t>170-179</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>160-169</t>
+          <t>180-189</t>
         </is>
       </c>
       <c r="C56">
-        <v>218</v>
+        <v>100</v>
       </c>
       <c r="D56">
-        <v>218</v>
+        <v>100</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>160-169</t>
+          <t>170-179</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>170-179</t>
+          <t>190-199</t>
         </is>
       </c>
       <c r="C57">
-        <v>119</v>
+        <v>41</v>
       </c>
       <c r="D57">
-        <v>119</v>
+        <v>41</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>160-169</t>
+          <t>170-179</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>180-189</t>
+          <t>200-209</t>
         </is>
       </c>
       <c r="C58">
-        <v>36</v>
+        <v>7</v>
       </c>
       <c r="D58">
-        <v>36</v>
+        <v>7</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>160-169</t>
+          <t>170-179</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>190-199</t>
+          <t>210-219</t>
         </is>
       </c>
       <c r="C59">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="D59">
-        <v>9</v>
+        <v>2</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>160-169</t>
+          <t>180-189</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>200-209</t>
+          <t>140-149</t>
         </is>
       </c>
       <c r="C60">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="D60">
-        <v>2</v>
+        <v>9</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>160-169</t>
+          <t>180-189</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>220-229</t>
+          <t>150-159</t>
         </is>
       </c>
       <c r="C61">
-        <v>2</v>
+        <v>66</v>
       </c>
       <c r="D61">
-        <v>2</v>
+        <v>66</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>170-179</t>
+          <t>180-189</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>130-139</t>
+          <t>160-169</t>
         </is>
       </c>
       <c r="C62">
-        <v>11</v>
+        <v>163</v>
       </c>
       <c r="D62">
-        <v>11</v>
+        <v>163</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
+          <t>180-189</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
           <t>170-179</t>
         </is>
       </c>
-      <c r="B63" t="inlineStr">
-        <is>
-          <t>140-149</t>
-        </is>
-      </c>
       <c r="C63">
-        <v>44</v>
+        <v>169</v>
       </c>
       <c r="D63">
-        <v>44</v>
+        <v>169</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>170-179</t>
+          <t>180-189</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>150-159</t>
+          <t>180-189</t>
         </is>
       </c>
       <c r="C64">
-        <v>140</v>
+        <v>110</v>
       </c>
       <c r="D64">
-        <v>140</v>
+        <v>110</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>170-179</t>
+          <t>180-189</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>160-169</t>
+          <t>190-199</t>
         </is>
       </c>
       <c r="C65">
-        <v>176</v>
+        <v>60</v>
       </c>
       <c r="D65">
-        <v>176</v>
+        <v>60</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>170-179</t>
+          <t>180-189</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>170-179</t>
+          <t>200-209</t>
         </is>
       </c>
       <c r="C66">
-        <v>130</v>
+        <v>14</v>
       </c>
       <c r="D66">
-        <v>130</v>
+        <v>14</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>170-179</t>
+          <t>180-189</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>180-189</t>
+          <t>210-219</t>
         </is>
       </c>
       <c r="C67">
-        <v>60</v>
+        <v>5</v>
       </c>
       <c r="D67">
-        <v>60</v>
+        <v>5</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>170-179</t>
+          <t>180-189</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>190-199</t>
+          <t>220-229</t>
         </is>
       </c>
       <c r="C68">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="D68">
-        <v>20</v>
+        <v>1</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>170-179</t>
+          <t>190-199</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>200-209</t>
+          <t>140-149</t>
         </is>
       </c>
       <c r="C69">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D69">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>170-179</t>
+          <t>190-199</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>220-229</t>
+          <t>150-159</t>
         </is>
       </c>
       <c r="C70">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="D70">
-        <v>1</v>
+        <v>17</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>180-189</t>
+          <t>190-199</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>130-139</t>
+          <t>160-169</t>
         </is>
       </c>
       <c r="C71">
-        <v>1</v>
+        <v>63</v>
       </c>
       <c r="D71">
-        <v>1</v>
+        <v>63</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>180-189</t>
+          <t>190-199</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>140-149</t>
+          <t>170-179</t>
         </is>
       </c>
       <c r="C72">
-        <v>19</v>
+        <v>100</v>
       </c>
       <c r="D72">
-        <v>19</v>
+        <v>100</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
+          <t>190-199</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
           <t>180-189</t>
         </is>
       </c>
-      <c r="B73" t="inlineStr">
-        <is>
-          <t>150-159</t>
-        </is>
-      </c>
       <c r="C73">
-        <v>45</v>
+        <v>83</v>
       </c>
       <c r="D73">
-        <v>45</v>
+        <v>83</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>180-189</t>
+          <t>190-199</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>160-169</t>
+          <t>190-199</t>
         </is>
       </c>
       <c r="C74">
-        <v>93</v>
+        <v>61</v>
       </c>
       <c r="D74">
-        <v>93</v>
+        <v>61</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>180-189</t>
+          <t>190-199</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>170-179</t>
+          <t>200-209</t>
         </is>
       </c>
       <c r="C75">
-        <v>83</v>
+        <v>28</v>
       </c>
       <c r="D75">
-        <v>83</v>
+        <v>28</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>180-189</t>
+          <t>190-199</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>180-189</t>
+          <t>210-219</t>
         </is>
       </c>
       <c r="C76">
-        <v>57</v>
+        <v>11</v>
       </c>
       <c r="D76">
-        <v>57</v>
+        <v>11</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>180-189</t>
+          <t>190-199</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>190-199</t>
+          <t>220-229</t>
         </is>
       </c>
       <c r="C77">
-        <v>33</v>
+        <v>2</v>
       </c>
       <c r="D77">
-        <v>33</v>
+        <v>2</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>180-189</t>
+          <t>190-199</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>200-209</t>
+          <t>260-269</t>
         </is>
       </c>
       <c r="C78">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="D78">
-        <v>12</v>
+        <v>1</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>180-189</t>
+          <t>200-209</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>210-219</t>
+          <t>150-159</t>
         </is>
       </c>
       <c r="C79">
@@ -1783,583 +1783,583 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>180-189</t>
+          <t>200-209</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>220-229</t>
+          <t>160-169</t>
         </is>
       </c>
       <c r="C80">
-        <v>2</v>
+        <v>22</v>
       </c>
       <c r="D80">
-        <v>2</v>
+        <v>22</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>180-189</t>
+          <t>200-209</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>240-249</t>
+          <t>170-179</t>
         </is>
       </c>
       <c r="C81">
-        <v>1</v>
+        <v>54</v>
       </c>
       <c r="D81">
-        <v>1</v>
+        <v>54</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
+          <t>200-209</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
           <t>180-189</t>
         </is>
       </c>
-      <c r="B82" t="inlineStr">
-        <is>
-          <t>250-259</t>
-        </is>
-      </c>
       <c r="C82">
-        <v>1</v>
+        <v>49</v>
       </c>
       <c r="D82">
-        <v>1</v>
+        <v>49</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
+          <t>200-209</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
           <t>190-199</t>
         </is>
       </c>
-      <c r="B83" t="inlineStr">
-        <is>
-          <t>140-149</t>
-        </is>
-      </c>
       <c r="C83">
-        <v>3</v>
+        <v>49</v>
       </c>
       <c r="D83">
-        <v>3</v>
+        <v>49</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>190-199</t>
+          <t>200-209</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>150-159</t>
+          <t>200-209</t>
         </is>
       </c>
       <c r="C84">
-        <v>16</v>
+        <v>38</v>
       </c>
       <c r="D84">
-        <v>16</v>
+        <v>38</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>190-199</t>
+          <t>200-209</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>160-169</t>
+          <t>210-219</t>
         </is>
       </c>
       <c r="C85">
-        <v>41</v>
+        <v>12</v>
       </c>
       <c r="D85">
-        <v>41</v>
+        <v>12</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>190-199</t>
+          <t>200-209</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>170-179</t>
+          <t>220-229</t>
         </is>
       </c>
       <c r="C86">
-        <v>51</v>
+        <v>2</v>
       </c>
       <c r="D86">
-        <v>51</v>
+        <v>2</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>190-199</t>
+          <t>200-209</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>180-189</t>
+          <t>230-239</t>
         </is>
       </c>
       <c r="C87">
-        <v>52</v>
+        <v>2</v>
       </c>
       <c r="D87">
-        <v>52</v>
+        <v>2</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>190-199</t>
+          <t>200-209</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>190-199</t>
+          <t>240-249</t>
         </is>
       </c>
       <c r="C88">
-        <v>42</v>
+        <v>1</v>
       </c>
       <c r="D88">
-        <v>42</v>
+        <v>1</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>190-199</t>
+          <t>210-219</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>200-209</t>
+          <t>150-159</t>
         </is>
       </c>
       <c r="C89">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="D89">
-        <v>20</v>
+        <v>1</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>190-199</t>
+          <t>210-219</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>210-219</t>
+          <t>160-169</t>
         </is>
       </c>
       <c r="C90">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="D90">
-        <v>9</v>
+        <v>6</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>190-199</t>
+          <t>210-219</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>220-229</t>
+          <t>170-179</t>
         </is>
       </c>
       <c r="C91">
-        <v>2</v>
+        <v>25</v>
       </c>
       <c r="D91">
-        <v>2</v>
+        <v>25</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>190-199</t>
+          <t>210-219</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>230-239</t>
+          <t>180-189</t>
         </is>
       </c>
       <c r="C92">
-        <v>2</v>
+        <v>33</v>
       </c>
       <c r="D92">
-        <v>2</v>
+        <v>33</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>200-209</t>
+          <t>210-219</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>150-159</t>
+          <t>190-199</t>
         </is>
       </c>
       <c r="C93">
-        <v>6</v>
+        <v>33</v>
       </c>
       <c r="D93">
-        <v>6</v>
+        <v>33</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
+          <t>210-219</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
           <t>200-209</t>
         </is>
       </c>
-      <c r="B94" t="inlineStr">
-        <is>
-          <t>160-169</t>
-        </is>
-      </c>
       <c r="C94">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="D94">
-        <v>17</v>
+        <v>29</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>200-209</t>
+          <t>210-219</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>170-179</t>
+          <t>210-219</t>
         </is>
       </c>
       <c r="C95">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="D95">
-        <v>29</v>
+        <v>25</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>200-209</t>
+          <t>210-219</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>180-189</t>
+          <t>220-229</t>
         </is>
       </c>
       <c r="C96">
-        <v>27</v>
+        <v>15</v>
       </c>
       <c r="D96">
-        <v>27</v>
+        <v>15</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>200-209</t>
+          <t>210-219</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>190-199</t>
+          <t>230-239</t>
         </is>
       </c>
       <c r="C97">
-        <v>38</v>
+        <v>5</v>
       </c>
       <c r="D97">
-        <v>38</v>
+        <v>5</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>200-209</t>
+          <t>210-219</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>200-209</t>
+          <t>240-249</t>
         </is>
       </c>
       <c r="C98">
-        <v>26</v>
+        <v>2</v>
       </c>
       <c r="D98">
-        <v>26</v>
+        <v>2</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>200-209</t>
+          <t>210-219</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>210-219</t>
+          <t>260-269</t>
         </is>
       </c>
       <c r="C99">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="D99">
-        <v>11</v>
+        <v>1</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>200-209</t>
+          <t>210-219</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>220-229</t>
+          <t>280-289</t>
         </is>
       </c>
       <c r="C100">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D100">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>200-209</t>
+          <t>220-229</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>230-239</t>
+          <t>170-179</t>
         </is>
       </c>
       <c r="C101">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="D101">
-        <v>2</v>
+        <v>8</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>210-219</t>
+          <t>220-229</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>150-159</t>
+          <t>180-189</t>
         </is>
       </c>
       <c r="C102">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="D102">
-        <v>2</v>
+        <v>10</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>210-219</t>
+          <t>220-229</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>160-169</t>
+          <t>190-199</t>
         </is>
       </c>
       <c r="C103">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="D103">
-        <v>8</v>
+        <v>20</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>210-219</t>
+          <t>220-229</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>170-179</t>
+          <t>200-209</t>
         </is>
       </c>
       <c r="C104">
-        <v>8</v>
+        <v>28</v>
       </c>
       <c r="D104">
-        <v>8</v>
+        <v>28</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
+          <t>220-229</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
           <t>210-219</t>
         </is>
       </c>
-      <c r="B105" t="inlineStr">
-        <is>
-          <t>180-189</t>
-        </is>
-      </c>
       <c r="C105">
-        <v>15</v>
+        <v>34</v>
       </c>
       <c r="D105">
-        <v>15</v>
+        <v>34</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>210-219</t>
+          <t>220-229</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>190-199</t>
+          <t>220-229</t>
         </is>
       </c>
       <c r="C106">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="D106">
-        <v>27</v>
+        <v>12</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>210-219</t>
+          <t>220-229</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>200-209</t>
+          <t>230-239</t>
         </is>
       </c>
       <c r="C107">
-        <v>29</v>
+        <v>6</v>
       </c>
       <c r="D107">
-        <v>29</v>
+        <v>6</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>210-219</t>
+          <t>220-229</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>210-219</t>
+          <t>240-249</t>
         </is>
       </c>
       <c r="C108">
-        <v>18</v>
+        <v>3</v>
       </c>
       <c r="D108">
-        <v>18</v>
+        <v>3</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>210-219</t>
+          <t>220-229</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>220-229</t>
+          <t>250-259</t>
         </is>
       </c>
       <c r="C109">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="D109">
-        <v>9</v>
+        <v>1</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>210-219</t>
+          <t>220-229</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>230-239</t>
+          <t>260-269</t>
         </is>
       </c>
       <c r="C110">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="D110">
-        <v>8</v>
+        <v>1</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>210-219</t>
+          <t>230-239</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>240-249</t>
+          <t>160-169</t>
         </is>
       </c>
       <c r="C111">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D111">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>220-229</t>
+          <t>230-239</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -2377,7 +2377,7 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>220-229</t>
+          <t>230-239</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -2386,16 +2386,16 @@
         </is>
       </c>
       <c r="C113">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="D113">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>220-229</t>
+          <t>230-239</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -2404,16 +2404,16 @@
         </is>
       </c>
       <c r="C114">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="D114">
-        <v>13</v>
+        <v>8</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>220-229</t>
+          <t>230-239</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -2422,16 +2422,16 @@
         </is>
       </c>
       <c r="C115">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="D115">
-        <v>18</v>
+        <v>15</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>220-229</t>
+          <t>230-239</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -2440,34 +2440,34 @@
         </is>
       </c>
       <c r="C116">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="D116">
-        <v>16</v>
+        <v>5</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
+          <t>230-239</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
           <t>220-229</t>
         </is>
       </c>
-      <c r="B117" t="inlineStr">
-        <is>
-          <t>220-229</t>
-        </is>
-      </c>
       <c r="C117">
-        <v>12</v>
+        <v>25</v>
       </c>
       <c r="D117">
-        <v>12</v>
+        <v>25</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>220-229</t>
+          <t>230-239</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -2476,16 +2476,16 @@
         </is>
       </c>
       <c r="C118">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D118">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>220-229</t>
+          <t>230-239</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -2494,16 +2494,16 @@
         </is>
       </c>
       <c r="C119">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D119">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>220-229</t>
+          <t>230-239</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -2512,21 +2512,21 @@
         </is>
       </c>
       <c r="C120">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D120">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>220-229</t>
+          <t>240-249</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>270-279</t>
+          <t>180-189</t>
         </is>
       </c>
       <c r="C121">
@@ -2539,12 +2539,12 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>220-229</t>
+          <t>240-249</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>330-339</t>
+          <t>190-199</t>
         </is>
       </c>
       <c r="C122">
@@ -2557,336 +2557,336 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>230-239</t>
+          <t>240-249</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>160-169</t>
+          <t>200-209</t>
         </is>
       </c>
       <c r="C123">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D123">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>230-239</t>
+          <t>240-249</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>170-179</t>
+          <t>210-219</t>
         </is>
       </c>
       <c r="C124">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="D124">
-        <v>1</v>
+        <v>16</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>230-239</t>
+          <t>240-249</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>180-189</t>
+          <t>220-229</t>
         </is>
       </c>
       <c r="C125">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="D125">
-        <v>4</v>
+        <v>19</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
+          <t>240-249</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
           <t>230-239</t>
         </is>
       </c>
-      <c r="B126" t="inlineStr">
-        <is>
-          <t>190-199</t>
-        </is>
-      </c>
       <c r="C126">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="D126">
-        <v>6</v>
+        <v>12</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>230-239</t>
+          <t>240-249</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>200-209</t>
+          <t>240-249</t>
         </is>
       </c>
       <c r="C127">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="D127">
-        <v>11</v>
+        <v>8</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>230-239</t>
+          <t>240-249</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>210-219</t>
+          <t>250-259</t>
         </is>
       </c>
       <c r="C128">
-        <v>21</v>
+        <v>2</v>
       </c>
       <c r="D128">
-        <v>21</v>
+        <v>2</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>230-239</t>
+          <t>240-249</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>220-229</t>
+          <t>260-269</t>
         </is>
       </c>
       <c r="C129">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="D129">
-        <v>9</v>
+        <v>1</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>230-239</t>
+          <t>240-249</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>230-239</t>
+          <t>290-299</t>
         </is>
       </c>
       <c r="C130">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="D130">
-        <v>8</v>
+        <v>1</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>230-239</t>
+          <t>250-259</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>240-249</t>
+          <t>190-199</t>
         </is>
       </c>
       <c r="C131">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D131">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>230-239</t>
+          <t>250-259</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>250-259</t>
+          <t>200-209</t>
         </is>
       </c>
       <c r="C132">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D132">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>240-249</t>
+          <t>250-259</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>180-189</t>
+          <t>210-219</t>
         </is>
       </c>
       <c r="C133">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="D133">
-        <v>1</v>
+        <v>9</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>240-249</t>
+          <t>250-259</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>190-199</t>
+          <t>220-229</t>
         </is>
       </c>
       <c r="C134">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="D134">
-        <v>2</v>
+        <v>12</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>240-249</t>
+          <t>250-259</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>200-209</t>
+          <t>230-239</t>
         </is>
       </c>
       <c r="C135">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="D135">
-        <v>6</v>
+        <v>21</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
+          <t>250-259</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
           <t>240-249</t>
         </is>
       </c>
-      <c r="B136" t="inlineStr">
-        <is>
-          <t>210-219</t>
-        </is>
-      </c>
       <c r="C136">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="D136">
-        <v>16</v>
+        <v>7</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>240-249</t>
+          <t>250-259</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>220-229</t>
+          <t>250-259</t>
         </is>
       </c>
       <c r="C137">
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="D137">
-        <v>17</v>
+        <v>1</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>240-249</t>
+          <t>250-259</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>230-239</t>
+          <t>260-269</t>
         </is>
       </c>
       <c r="C138">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="D138">
-        <v>11</v>
+        <v>2</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>240-249</t>
+          <t>250-259</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>240-249</t>
+          <t>270-279</t>
         </is>
       </c>
       <c r="C139">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D139">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>240-249</t>
+          <t>260-269</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>250-259</t>
+          <t>180-189</t>
         </is>
       </c>
       <c r="C140">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D140">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>240-249</t>
+          <t>260-269</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>260-269</t>
+          <t>200-209</t>
         </is>
       </c>
       <c r="C141">
@@ -2899,138 +2899,138 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>240-249</t>
+          <t>260-269</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>280-289</t>
+          <t>210-219</t>
         </is>
       </c>
       <c r="C142">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D142">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>250-259</t>
+          <t>260-269</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>190-199</t>
+          <t>220-229</t>
         </is>
       </c>
       <c r="C143">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D143">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>250-259</t>
+          <t>260-269</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>200-209</t>
+          <t>230-239</t>
         </is>
       </c>
       <c r="C144">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D144">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>250-259</t>
+          <t>260-269</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>210-219</t>
+          <t>240-249</t>
         </is>
       </c>
       <c r="C145">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D145">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
+          <t>260-269</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
           <t>250-259</t>
         </is>
       </c>
-      <c r="B146" t="inlineStr">
-        <is>
-          <t>220-229</t>
-        </is>
-      </c>
       <c r="C146">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="D146">
-        <v>13</v>
+        <v>9</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>250-259</t>
+          <t>260-269</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>230-239</t>
+          <t>260-269</t>
         </is>
       </c>
       <c r="C147">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D147">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>250-259</t>
+          <t>260-269</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>240-249</t>
+          <t>270-279</t>
         </is>
       </c>
       <c r="C148">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="D148">
-        <v>8</v>
+        <v>2</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>250-259</t>
+          <t>260-269</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>250-259</t>
+          <t>290-299</t>
         </is>
       </c>
       <c r="C149">
@@ -3043,30 +3043,30 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>250-259</t>
+          <t>260-269</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>260-269</t>
+          <t>310-319</t>
         </is>
       </c>
       <c r="C150">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D150">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>250-259</t>
+          <t>270-279</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>270-279</t>
+          <t>180-189</t>
         </is>
       </c>
       <c r="C151">
@@ -3079,84 +3079,84 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>250-259</t>
+          <t>270-279</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>280-289</t>
+          <t>210-219</t>
         </is>
       </c>
       <c r="C152">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D152">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>260-269</t>
+          <t>270-279</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>170-179</t>
+          <t>220-229</t>
         </is>
       </c>
       <c r="C153">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D153">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>260-269</t>
+          <t>270-279</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>200-209</t>
+          <t>230-239</t>
         </is>
       </c>
       <c r="C154">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="D154">
-        <v>1</v>
+        <v>9</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>260-269</t>
+          <t>270-279</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>210-219</t>
+          <t>240-249</t>
         </is>
       </c>
       <c r="C155">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="D155">
-        <v>4</v>
+        <v>11</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>260-269</t>
+          <t>270-279</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>220-229</t>
+          <t>250-259</t>
         </is>
       </c>
       <c r="C156">
@@ -3169,84 +3169,84 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
+          <t>270-279</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
           <t>260-269</t>
         </is>
       </c>
-      <c r="B157" t="inlineStr">
-        <is>
-          <t>230-239</t>
-        </is>
-      </c>
       <c r="C157">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="D157">
-        <v>15</v>
+        <v>10</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>260-269</t>
+          <t>270-279</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>240-249</t>
+          <t>270-279</t>
         </is>
       </c>
       <c r="C158">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="D158">
-        <v>9</v>
+        <v>6</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>260-269</t>
+          <t>270-279</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>250-259</t>
+          <t>290-299</t>
         </is>
       </c>
       <c r="C159">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="D159">
-        <v>8</v>
+        <v>2</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>260-269</t>
+          <t>270-279</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>260-269</t>
+          <t>300-309</t>
         </is>
       </c>
       <c r="C160">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D160">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>260-269</t>
+          <t>280-289</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>270-279</t>
+          <t>210-219</t>
         </is>
       </c>
       <c r="C161">
@@ -3259,84 +3259,84 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>260-269</t>
+          <t>280-289</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>290-299</t>
+          <t>220-229</t>
         </is>
       </c>
       <c r="C162">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="D162">
-        <v>1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>270-279</t>
+          <t>280-289</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>200-209</t>
+          <t>230-239</t>
         </is>
       </c>
       <c r="C163">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="D163">
-        <v>2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>270-279</t>
+          <t>280-289</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>210-219</t>
+          <t>240-249</t>
         </is>
       </c>
       <c r="C164">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="D164">
-        <v>1</v>
+        <v>9</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>270-279</t>
+          <t>280-289</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>220-229</t>
+          <t>250-259</t>
         </is>
       </c>
       <c r="C165">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="D165">
-        <v>8</v>
+        <v>13</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>270-279</t>
+          <t>280-289</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>230-239</t>
+          <t>260-269</t>
         </is>
       </c>
       <c r="C166">
@@ -3349,84 +3349,84 @@
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
+          <t>280-289</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
           <t>270-279</t>
         </is>
       </c>
-      <c r="B167" t="inlineStr">
-        <is>
-          <t>240-249</t>
-        </is>
-      </c>
       <c r="C167">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="D167">
-        <v>8</v>
+        <v>1</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>270-279</t>
+          <t>280-289</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>250-259</t>
+          <t>280-289</t>
         </is>
       </c>
       <c r="C168">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D168">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>270-279</t>
+          <t>280-289</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>260-269</t>
+          <t>290-299</t>
         </is>
       </c>
       <c r="C169">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="D169">
-        <v>7</v>
+        <v>3</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>270-279</t>
+          <t>290-299</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>270-279</t>
+          <t>210-219</t>
         </is>
       </c>
       <c r="C170">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D170">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>270-279</t>
+          <t>290-299</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>290-299</t>
+          <t>220-229</t>
         </is>
       </c>
       <c r="C171">
@@ -3439,12 +3439,12 @@
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>270-279</t>
+          <t>290-299</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>300-309</t>
+          <t>230-239</t>
         </is>
       </c>
       <c r="C172">
@@ -3457,120 +3457,120 @@
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>270-279</t>
+          <t>290-299</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>330-339</t>
+          <t>240-249</t>
         </is>
       </c>
       <c r="C173">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D173">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>280-289</t>
+          <t>290-299</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>220-229</t>
+          <t>250-259</t>
         </is>
       </c>
       <c r="C174">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D174">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>280-289</t>
+          <t>290-299</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>230-239</t>
+          <t>260-269</t>
         </is>
       </c>
       <c r="C175">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D175">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>280-289</t>
+          <t>290-299</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>240-249</t>
+          <t>270-279</t>
         </is>
       </c>
       <c r="C176">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="D176">
-        <v>9</v>
+        <v>3</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
+          <t>290-299</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
           <t>280-289</t>
         </is>
       </c>
-      <c r="B177" t="inlineStr">
-        <is>
-          <t>250-259</t>
-        </is>
-      </c>
       <c r="C177">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="D177">
-        <v>6</v>
+        <v>9</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>280-289</t>
+          <t>290-299</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>260-269</t>
+          <t>290-299</t>
         </is>
       </c>
       <c r="C178">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="D178">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>280-289</t>
+          <t>290-299</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>270-279</t>
+          <t>310-319</t>
         </is>
       </c>
       <c r="C179">
@@ -3583,30 +3583,30 @@
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>280-289</t>
+          <t>290-299</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>280-289</t>
+          <t>320-329</t>
         </is>
       </c>
       <c r="C180">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D180">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>280-289</t>
+          <t>300-309</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>290-299</t>
+          <t>230-239</t>
         </is>
       </c>
       <c r="C181">
@@ -3619,48 +3619,48 @@
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>290-299</t>
+          <t>300-309</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>210-219</t>
+          <t>240-249</t>
         </is>
       </c>
       <c r="C182">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D182">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>290-299</t>
+          <t>300-309</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>220-229</t>
+          <t>250-259</t>
         </is>
       </c>
       <c r="C183">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D183">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>290-299</t>
+          <t>300-309</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>230-239</t>
+          <t>270-279</t>
         </is>
       </c>
       <c r="C184">
@@ -3673,48 +3673,48 @@
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>290-299</t>
+          <t>300-309</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>240-249</t>
+          <t>280-289</t>
         </is>
       </c>
       <c r="C185">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D185">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
+          <t>300-309</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
           <t>290-299</t>
         </is>
       </c>
-      <c r="B186" t="inlineStr">
-        <is>
-          <t>250-259</t>
-        </is>
-      </c>
       <c r="C186">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D186">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>290-299</t>
+          <t>300-309</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>260-269</t>
+          <t>300-309</t>
         </is>
       </c>
       <c r="C187">
@@ -3727,48 +3727,48 @@
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>290-299</t>
+          <t>300-309</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>270-279</t>
+          <t>310-319</t>
         </is>
       </c>
       <c r="C188">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D188">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>290-299</t>
+          <t>310-319</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>280-289</t>
+          <t>220-229</t>
         </is>
       </c>
       <c r="C189">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D189">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>290-299</t>
+          <t>310-319</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>290-299</t>
+          <t>240-249</t>
         </is>
       </c>
       <c r="C190">
@@ -3781,138 +3781,138 @@
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>290-299</t>
+          <t>310-319</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>400-409</t>
+          <t>260-269</t>
         </is>
       </c>
       <c r="C191">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D191">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>290-299</t>
+          <t>310-319</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>440-449</t>
+          <t>270-279</t>
         </is>
       </c>
       <c r="C192">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D192">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>300-309</t>
+          <t>310-319</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>220-229</t>
+          <t>280-289</t>
         </is>
       </c>
       <c r="C193">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D193">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>300-309</t>
+          <t>310-319</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>230-239</t>
+          <t>290-299</t>
         </is>
       </c>
       <c r="C194">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D194">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
+          <t>310-319</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
           <t>300-309</t>
         </is>
       </c>
-      <c r="B195" t="inlineStr">
-        <is>
-          <t>240-249</t>
-        </is>
-      </c>
       <c r="C195">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D195">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>300-309</t>
+          <t>310-319</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>250-259</t>
+          <t>320-329</t>
         </is>
       </c>
       <c r="C196">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D196">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>300-309</t>
+          <t>320-329</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>260-269</t>
+          <t>240-249</t>
         </is>
       </c>
       <c r="C197">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D197">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>300-309</t>
+          <t>320-329</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>270-279</t>
+          <t>250-259</t>
         </is>
       </c>
       <c r="C198">
@@ -3925,174 +3925,174 @@
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>300-309</t>
+          <t>320-329</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>280-289</t>
+          <t>260-269</t>
         </is>
       </c>
       <c r="C199">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D199">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>300-309</t>
+          <t>320-329</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>290-299</t>
+          <t>270-279</t>
         </is>
       </c>
       <c r="C200">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D200">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>300-309</t>
+          <t>320-329</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>300-309</t>
+          <t>280-289</t>
         </is>
       </c>
       <c r="C201">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="D201">
-        <v>1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>310-319</t>
+          <t>320-329</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>250-259</t>
+          <t>290-299</t>
         </is>
       </c>
       <c r="C202">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D202">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>310-319</t>
+          <t>320-329</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>260-269</t>
+          <t>300-309</t>
         </is>
       </c>
       <c r="C203">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D203">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
+          <t>320-329</t>
+        </is>
+      </c>
+      <c r="B204" t="inlineStr">
+        <is>
           <t>310-319</t>
         </is>
       </c>
-      <c r="B204" t="inlineStr">
-        <is>
-          <t>270-279</t>
-        </is>
-      </c>
       <c r="C204">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D204">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>310-319</t>
+          <t>320-329</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>280-289</t>
+          <t>320-329</t>
         </is>
       </c>
       <c r="C205">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D205">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>310-319</t>
+          <t>320-329</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>290-299</t>
+          <t>340-349</t>
         </is>
       </c>
       <c r="C206">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D206">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>310-319</t>
+          <t>330-339</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>300-309</t>
+          <t>230-239</t>
         </is>
       </c>
       <c r="C207">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D207">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>310-319</t>
+          <t>330-339</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>310-319</t>
+          <t>260-269</t>
         </is>
       </c>
       <c r="C208">
@@ -4105,30 +4105,30 @@
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>310-319</t>
+          <t>330-339</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>320-329</t>
+          <t>270-279</t>
         </is>
       </c>
       <c r="C209">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D209">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>310-319</t>
+          <t>330-339</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>330-339</t>
+          <t>280-289</t>
         </is>
       </c>
       <c r="C210">
@@ -4141,390 +4141,390 @@
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>320-329</t>
+          <t>330-339</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>240-249</t>
+          <t>290-299</t>
         </is>
       </c>
       <c r="C211">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D211">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>320-329</t>
+          <t>330-339</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>250-259</t>
+          <t>300-309</t>
         </is>
       </c>
       <c r="C212">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D212">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>320-329</t>
+          <t>330-339</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>260-269</t>
+          <t>310-319</t>
         </is>
       </c>
       <c r="C213">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="D213">
-        <v>2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
+          <t>330-339</t>
+        </is>
+      </c>
+      <c r="B214" t="inlineStr">
+        <is>
           <t>320-329</t>
         </is>
       </c>
-      <c r="B214" t="inlineStr">
-        <is>
-          <t>270-279</t>
-        </is>
-      </c>
       <c r="C214">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D214">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>320-329</t>
+          <t>330-339</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>280-289</t>
+          <t>330-339</t>
         </is>
       </c>
       <c r="C215">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D215">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>320-329</t>
+          <t>330-339</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>290-299</t>
+          <t>380-389</t>
         </is>
       </c>
       <c r="C216">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D216">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>320-329</t>
+          <t>340-349</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>300-309</t>
+          <t>250-259</t>
         </is>
       </c>
       <c r="C217">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D217">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>320-329</t>
+          <t>340-349</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>310-319</t>
+          <t>260-269</t>
         </is>
       </c>
       <c r="C218">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D218">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>320-329</t>
+          <t>340-349</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>320-329</t>
+          <t>270-279</t>
         </is>
       </c>
       <c r="C219">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D219">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>320-329</t>
+          <t>340-349</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>330-339</t>
+          <t>280-289</t>
         </is>
       </c>
       <c r="C220">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D220">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>320-329</t>
+          <t>340-349</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>360-369</t>
+          <t>290-299</t>
         </is>
       </c>
       <c r="C221">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D221">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>330-339</t>
+          <t>340-349</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>250-259</t>
+          <t>300-309</t>
         </is>
       </c>
       <c r="C222">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D222">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>330-339</t>
+          <t>340-349</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>260-269</t>
+          <t>310-319</t>
         </is>
       </c>
       <c r="C223">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="D223">
-        <v>3</v>
+        <v>7</v>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>330-339</t>
+          <t>340-349</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>270-279</t>
+          <t>320-329</t>
         </is>
       </c>
       <c r="C224">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D224">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
+          <t>340-349</t>
+        </is>
+      </c>
+      <c r="B225" t="inlineStr">
+        <is>
           <t>330-339</t>
         </is>
       </c>
-      <c r="B225" t="inlineStr">
-        <is>
-          <t>280-289</t>
-        </is>
-      </c>
       <c r="C225">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D225">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>330-339</t>
+          <t>340-349</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>290-299</t>
+          <t>340-349</t>
         </is>
       </c>
       <c r="C226">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="D226">
-        <v>10</v>
+        <v>2</v>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>330-339</t>
+          <t>340-349</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>300-309</t>
+          <t>360-369</t>
         </is>
       </c>
       <c r="C227">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D227">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>330-339</t>
+          <t>350-359</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>310-319</t>
+          <t>260-269</t>
         </is>
       </c>
       <c r="C228">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D228">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>330-339</t>
+          <t>350-359</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>320-329</t>
+          <t>280-289</t>
         </is>
       </c>
       <c r="C229">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D229">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>330-339</t>
+          <t>350-359</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>380-389</t>
+          <t>290-299</t>
         </is>
       </c>
       <c r="C230">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="D230">
-        <v>1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>340-349</t>
+          <t>350-359</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>260-269</t>
+          <t>300-309</t>
         </is>
       </c>
       <c r="C231">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D231">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>340-349</t>
+          <t>350-359</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>270-279</t>
+          <t>310-319</t>
         </is>
       </c>
       <c r="C232">
@@ -4537,102 +4537,102 @@
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>340-349</t>
+          <t>350-359</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>280-289</t>
+          <t>320-329</t>
         </is>
       </c>
       <c r="C233">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D233">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
+          <t>350-359</t>
+        </is>
+      </c>
+      <c r="B234" t="inlineStr">
+        <is>
           <t>340-349</t>
         </is>
       </c>
-      <c r="B234" t="inlineStr">
-        <is>
-          <t>290-299</t>
-        </is>
-      </c>
       <c r="C234">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D234">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>340-349</t>
+          <t>350-359</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>300-309</t>
+          <t>360-369</t>
         </is>
       </c>
       <c r="C235">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D235">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>340-349</t>
+          <t>350-359</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>310-319</t>
+          <t>390-399</t>
         </is>
       </c>
       <c r="C236">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D236">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>340-349</t>
+          <t>360-369</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>320-329</t>
+          <t>280-289</t>
         </is>
       </c>
       <c r="C237">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D237">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>340-349</t>
+          <t>360-369</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>330-339</t>
+          <t>290-299</t>
         </is>
       </c>
       <c r="C238">
@@ -4645,102 +4645,102 @@
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>350-359</t>
+          <t>360-369</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>270-279</t>
+          <t>300-309</t>
         </is>
       </c>
       <c r="C239">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D239">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>350-359</t>
+          <t>360-369</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>280-289</t>
+          <t>310-319</t>
         </is>
       </c>
       <c r="C240">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D240">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>350-359</t>
+          <t>360-369</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>290-299</t>
+          <t>320-329</t>
         </is>
       </c>
       <c r="C241">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D241">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>350-359</t>
+          <t>360-369</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>300-309</t>
+          <t>330-339</t>
         </is>
       </c>
       <c r="C242">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="D242">
-        <v>8</v>
+        <v>1</v>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>350-359</t>
+          <t>360-369</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>310-319</t>
+          <t>340-349</t>
         </is>
       </c>
       <c r="C243">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D243">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
+          <t>360-369</t>
+        </is>
+      </c>
+      <c r="B244" t="inlineStr">
+        <is>
           <t>350-359</t>
-        </is>
-      </c>
-      <c r="B244" t="inlineStr">
-        <is>
-          <t>330-339</t>
         </is>
       </c>
       <c r="C244">
@@ -4753,19 +4753,19 @@
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>350-359</t>
+          <t>360-369</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>340-349</t>
+          <t>360-369</t>
         </is>
       </c>
       <c r="C245">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D245">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="246">
@@ -4776,7 +4776,7 @@
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>270-279</t>
+          <t>400-409</t>
         </is>
       </c>
       <c r="C246">
@@ -4789,7 +4789,7 @@
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>360-369</t>
+          <t>370-379</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
@@ -4798,16 +4798,16 @@
         </is>
       </c>
       <c r="C247">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D247">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>360-369</t>
+          <t>370-379</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
@@ -4816,16 +4816,16 @@
         </is>
       </c>
       <c r="C248">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D248">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>360-369</t>
+          <t>370-379</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
@@ -4843,7 +4843,7 @@
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>360-369</t>
+          <t>370-379</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
@@ -4852,16 +4852,16 @@
         </is>
       </c>
       <c r="C250">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D250">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>360-369</t>
+          <t>370-379</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
@@ -4870,16 +4870,16 @@
         </is>
       </c>
       <c r="C251">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D251">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>360-369</t>
+          <t>370-379</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
@@ -4888,39 +4888,39 @@
         </is>
       </c>
       <c r="C252">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D252">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>360-369</t>
+          <t>370-379</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>350-359</t>
+          <t>340-349</t>
         </is>
       </c>
       <c r="C253">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D253">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>360-369</t>
+          <t>370-379</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>400-409</t>
+          <t>350-359</t>
         </is>
       </c>
       <c r="C254">
@@ -4933,6 +4933,11 @@
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
+          <t>370-379</t>
+        </is>
+      </c>
+      <c r="B255" t="inlineStr">
+        <is>
           <t>360-369</t>
         </is>
       </c>
@@ -4951,7 +4956,7 @@
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>270-279</t>
+          <t>420-429</t>
         </is>
       </c>
       <c r="C256">
@@ -4967,22 +4972,17 @@
           <t>370-379</t>
         </is>
       </c>
-      <c r="B257" t="inlineStr">
-        <is>
-          <t>290-299</t>
-        </is>
-      </c>
       <c r="C257">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D257">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>370-379</t>
+          <t>380-389</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
@@ -4991,52 +4991,52 @@
         </is>
       </c>
       <c r="C258">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D258">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>370-379</t>
+          <t>380-389</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>320-329</t>
+          <t>310-319</t>
         </is>
       </c>
       <c r="C259">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D259">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>370-379</t>
+          <t>380-389</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>330-339</t>
+          <t>320-329</t>
         </is>
       </c>
       <c r="C260">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D260">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>370-379</t>
+          <t>380-389</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
@@ -5045,16 +5045,16 @@
         </is>
       </c>
       <c r="C261">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D261">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>370-379</t>
+          <t>380-389</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
@@ -5072,30 +5072,25 @@
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>370-379</t>
-        </is>
-      </c>
-      <c r="B263" t="inlineStr">
-        <is>
-          <t>410-419</t>
+          <t>380-389</t>
         </is>
       </c>
       <c r="C263">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D263">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>380-389</t>
+          <t>390-399</t>
         </is>
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>270-279</t>
+          <t>310-319</t>
         </is>
       </c>
       <c r="C264">
@@ -5108,55 +5103,55 @@
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>380-389</t>
+          <t>390-399</t>
         </is>
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>310-319</t>
+          <t>320-329</t>
         </is>
       </c>
       <c r="C265">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D265">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>380-389</t>
+          <t>390-399</t>
         </is>
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>330-339</t>
+          <t>340-349</t>
         </is>
       </c>
       <c r="C266">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D266">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>380-389</t>
+          <t>390-399</t>
         </is>
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>340-349</t>
+          <t>350-359</t>
         </is>
       </c>
       <c r="C267">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D267">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="268">
@@ -5167,25 +5162,25 @@
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>310-319</t>
+          <t>360-369</t>
         </is>
       </c>
       <c r="C268">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D268">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>390-399</t>
+          <t>400-409</t>
         </is>
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>320-329</t>
+          <t>340-349</t>
         </is>
       </c>
       <c r="C269">
@@ -5198,522 +5193,31 @@
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>390-399</t>
+          <t>400-409</t>
         </is>
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>330-339</t>
+          <t>360-369</t>
         </is>
       </c>
       <c r="C270">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D270">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>390-399</t>
-        </is>
-      </c>
-      <c r="B271" t="inlineStr">
-        <is>
-          <t>340-349</t>
+          <t>400-409</t>
         </is>
       </c>
       <c r="C271">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D271">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="272">
-      <c r="A272" t="inlineStr">
-        <is>
-          <t>390-399</t>
-        </is>
-      </c>
-      <c r="B272" t="inlineStr">
-        <is>
-          <t>360-369</t>
-        </is>
-      </c>
-      <c r="C272">
-        <v>1</v>
-      </c>
-      <c r="D272">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="273">
-      <c r="A273" t="inlineStr">
-        <is>
-          <t>390-399</t>
-        </is>
-      </c>
-      <c r="B273" t="inlineStr">
-        <is>
-          <t>390-399</t>
-        </is>
-      </c>
-      <c r="C273">
-        <v>1</v>
-      </c>
-      <c r="D273">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="274">
-      <c r="A274" t="inlineStr">
-        <is>
-          <t>390-399</t>
-        </is>
-      </c>
-      <c r="B274" t="inlineStr">
-        <is>
-          <t>420-429</t>
-        </is>
-      </c>
-      <c r="C274">
-        <v>1</v>
-      </c>
-      <c r="D274">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="275">
-      <c r="A275" t="inlineStr">
-        <is>
-          <t>400-409</t>
-        </is>
-      </c>
-      <c r="B275" t="inlineStr">
-        <is>
-          <t>300-309</t>
-        </is>
-      </c>
-      <c r="C275">
-        <v>2</v>
-      </c>
-      <c r="D275">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="276">
-      <c r="A276" t="inlineStr">
-        <is>
-          <t>400-409</t>
-        </is>
-      </c>
-      <c r="B276" t="inlineStr">
-        <is>
-          <t>310-319</t>
-        </is>
-      </c>
-      <c r="C276">
-        <v>1</v>
-      </c>
-      <c r="D276">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="277">
-      <c r="A277" t="inlineStr">
-        <is>
-          <t>400-409</t>
-        </is>
-      </c>
-      <c r="B277" t="inlineStr">
-        <is>
-          <t>330-339</t>
-        </is>
-      </c>
-      <c r="C277">
-        <v>2</v>
-      </c>
-      <c r="D277">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="278">
-      <c r="A278" t="inlineStr">
-        <is>
-          <t>400-409</t>
-        </is>
-      </c>
-      <c r="B278" t="inlineStr">
-        <is>
-          <t>340-349</t>
-        </is>
-      </c>
-      <c r="C278">
-        <v>1</v>
-      </c>
-      <c r="D278">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="279">
-      <c r="A279" t="inlineStr">
-        <is>
-          <t>400-409</t>
-        </is>
-      </c>
-      <c r="B279" t="inlineStr">
-        <is>
-          <t>360-369</t>
-        </is>
-      </c>
-      <c r="C279">
-        <v>1</v>
-      </c>
-      <c r="D279">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="280">
-      <c r="A280" t="inlineStr">
-        <is>
-          <t>400-409</t>
-        </is>
-      </c>
-      <c r="B280" t="inlineStr">
-        <is>
-          <t>370-379</t>
-        </is>
-      </c>
-      <c r="C280">
-        <v>1</v>
-      </c>
-      <c r="D280">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="281">
-      <c r="A281" t="inlineStr">
-        <is>
-          <t>410-419</t>
-        </is>
-      </c>
-      <c r="B281" t="inlineStr">
-        <is>
-          <t>310-319</t>
-        </is>
-      </c>
-      <c r="C281">
-        <v>2</v>
-      </c>
-      <c r="D281">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="282">
-      <c r="A282" t="inlineStr">
-        <is>
-          <t>410-419</t>
-        </is>
-      </c>
-      <c r="B282" t="inlineStr">
-        <is>
-          <t>330-339</t>
-        </is>
-      </c>
-      <c r="C282">
-        <v>1</v>
-      </c>
-      <c r="D282">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="283">
-      <c r="A283" t="inlineStr">
-        <is>
-          <t>410-419</t>
-        </is>
-      </c>
-      <c r="B283" t="inlineStr">
-        <is>
-          <t>340-349</t>
-        </is>
-      </c>
-      <c r="C283">
-        <v>1</v>
-      </c>
-      <c r="D283">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="284">
-      <c r="A284" t="inlineStr">
-        <is>
-          <t>410-419</t>
-        </is>
-      </c>
-      <c r="B284" t="inlineStr">
-        <is>
-          <t>350-359</t>
-        </is>
-      </c>
-      <c r="C284">
-        <v>1</v>
-      </c>
-      <c r="D284">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="285">
-      <c r="A285" t="inlineStr">
-        <is>
-          <t>410-419</t>
-        </is>
-      </c>
-      <c r="B285" t="inlineStr">
-        <is>
-          <t>360-369</t>
-        </is>
-      </c>
-      <c r="C285">
-        <v>1</v>
-      </c>
-      <c r="D285">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="286">
-      <c r="A286" t="inlineStr">
-        <is>
-          <t>410-419</t>
-        </is>
-      </c>
-      <c r="B286" t="inlineStr">
-        <is>
-          <t>390-399</t>
-        </is>
-      </c>
-      <c r="C286">
-        <v>2</v>
-      </c>
-      <c r="D286">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="287">
-      <c r="A287" t="inlineStr">
-        <is>
-          <t>420-429</t>
-        </is>
-      </c>
-      <c r="B287" t="inlineStr">
-        <is>
-          <t>330-339</t>
-        </is>
-      </c>
-      <c r="C287">
-        <v>1</v>
-      </c>
-      <c r="D287">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="288">
-      <c r="A288" t="inlineStr">
-        <is>
-          <t>420-429</t>
-        </is>
-      </c>
-      <c r="B288" t="inlineStr">
-        <is>
-          <t>340-349</t>
-        </is>
-      </c>
-      <c r="C288">
-        <v>2</v>
-      </c>
-      <c r="D288">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="289">
-      <c r="A289" t="inlineStr">
-        <is>
-          <t>420-429</t>
-        </is>
-      </c>
-      <c r="B289" t="inlineStr">
-        <is>
-          <t>350-359</t>
-        </is>
-      </c>
-      <c r="C289">
-        <v>2</v>
-      </c>
-      <c r="D289">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="290">
-      <c r="A290" t="inlineStr">
-        <is>
-          <t>420-429</t>
-        </is>
-      </c>
-      <c r="B290" t="inlineStr">
-        <is>
-          <t>370-379</t>
-        </is>
-      </c>
-      <c r="C290">
-        <v>1</v>
-      </c>
-      <c r="D290">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="291">
-      <c r="A291" t="inlineStr">
-        <is>
-          <t>430-439</t>
-        </is>
-      </c>
-      <c r="B291" t="inlineStr">
-        <is>
-          <t>350-359</t>
-        </is>
-      </c>
-      <c r="C291">
-        <v>1</v>
-      </c>
-      <c r="D291">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="292">
-      <c r="A292" t="inlineStr">
-        <is>
-          <t>430-439</t>
-        </is>
-      </c>
-      <c r="B292" t="inlineStr">
-        <is>
-          <t>360-369</t>
-        </is>
-      </c>
-      <c r="C292">
-        <v>1</v>
-      </c>
-      <c r="D292">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="293">
-      <c r="A293" t="inlineStr">
-        <is>
-          <t>430-439</t>
-        </is>
-      </c>
-      <c r="B293" t="inlineStr">
-        <is>
-          <t>380-389</t>
-        </is>
-      </c>
-      <c r="C293">
-        <v>1</v>
-      </c>
-      <c r="D293">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="294">
-      <c r="A294" t="inlineStr">
-        <is>
-          <t>440-449</t>
-        </is>
-      </c>
-      <c r="B294" t="inlineStr">
-        <is>
-          <t>340-349</t>
-        </is>
-      </c>
-      <c r="C294">
-        <v>1</v>
-      </c>
-      <c r="D294">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="295">
-      <c r="A295" t="inlineStr">
-        <is>
-          <t>440-449</t>
-        </is>
-      </c>
-      <c r="B295" t="inlineStr">
-        <is>
-          <t>360-369</t>
-        </is>
-      </c>
-      <c r="C295">
-        <v>1</v>
-      </c>
-      <c r="D295">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="296">
-      <c r="A296" t="inlineStr">
-        <is>
-          <t>450-459</t>
-        </is>
-      </c>
-      <c r="B296" t="inlineStr">
-        <is>
-          <t>340-349</t>
-        </is>
-      </c>
-      <c r="C296">
-        <v>1</v>
-      </c>
-      <c r="D296">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="297">
-      <c r="A297" t="inlineStr">
-        <is>
-          <t>450-459</t>
-        </is>
-      </c>
-      <c r="B297" t="inlineStr">
-        <is>
-          <t>360-369</t>
-        </is>
-      </c>
-      <c r="C297">
-        <v>1</v>
-      </c>
-      <c r="D297">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="298">
-      <c r="A298" t="inlineStr">
-        <is>
-          <t>450-459</t>
-        </is>
-      </c>
-      <c r="B298" t="inlineStr">
-        <is>
-          <t>380-389</t>
-        </is>
-      </c>
-      <c r="C298">
-        <v>1</v>
-      </c>
-      <c r="D298">
         <v>1</v>
       </c>
     </row>
